--- a/Anexo 1 Reporte de Incidente.xlsx
+++ b/Anexo 1 Reporte de Incidente.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nissangroupnam-my.sharepoint.com/personal/isauramariel_medinarodriguez_nissan_com_mx/Documents/Documents/RIS/backend/src/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nissangroupnam-my.sharepoint.com/personal/isauramariel_medinarodriguez_nissan_com_mx/Documents/Documents/RIS/backend_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{1EADD85F-4936-4B16-8E18-B7E19714BE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0319A0B-7BB4-42A9-8E6E-46257BAAC4F5}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{1EADD85F-4936-4B16-8E18-B7E19714BE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3768FC77-4098-4DC9-8A4F-303C02281CD1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8E93A84E-A9D4-49D4-9959-2315A2D9559B}"/>
   </bookViews>
@@ -1638,471 +1638,107 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="48" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="2" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2111,72 +1747,436 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="2" borderId="48" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="48" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2186,6 +2186,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFE4C9AE"/>
+      <color rgb="FFEF986D"/>
+      <color rgb="FFAA4512"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2584,7 +2591,7 @@
               </a:solidFill>
               <a:latin typeface="Verdana"/>
             </a:rPr>
-            <a:t>FACTOR</a:t>
+            <a:t>PUNTO DE CONTROL</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2593,16 +2600,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>136094</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>9497</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>24969</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>184122</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>54</xdr:col>
-      <xdr:colOff>101843</xdr:colOff>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>54218</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>133354</xdr:rowOff>
+      <xdr:rowOff>117479</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2619,7 +2626,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9248344" y="9605935"/>
+          <a:off x="9502344" y="9590060"/>
           <a:ext cx="1426249" cy="774732"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartAlternateProcess">
@@ -2658,7 +2665,7 @@
               </a:solidFill>
               <a:latin typeface="Verdana"/>
             </a:rPr>
-            <a:t>FACTOR</a:t>
+            <a:t>COMENTARIOS</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2732,7 +2739,7 @@
               </a:solidFill>
               <a:latin typeface="Verdana"/>
             </a:rPr>
-            <a:t>FACTOR</a:t>
+            <a:t>REAL</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2806,7 +2813,7 @@
               </a:solidFill>
               <a:latin typeface="Verdana"/>
             </a:rPr>
-            <a:t>FACTOR</a:t>
+            <a:t>NORMA</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3129,6 +3136,9 @@
         <a:prstGeom prst="flowChartAlternateProcess">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
         <a:ln>
           <a:headEnd/>
           <a:tailEnd/>
@@ -3176,7 +3186,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>POLICONTUNDIDO</a:t>
+            <a:t>LESION</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900">
             <a:effectLst/>
@@ -3221,9 +3231,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
+          <a:srgbClr val="E4C9AE"/>
         </a:solidFill>
         <a:ln w="9525" algn="ctr">
           <a:solidFill>
@@ -3269,8 +3277,101 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>METODO</a:t>
+            <a:t>4M</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="900">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>159962</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>777240</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 405">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0A8DB96-9E61-428A-8071-93751C681968}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1420813" y="10437813"/>
+          <a:ext cx="1461712" cy="777240"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="A3C4FF"/>
+            </a:gs>
+            <a:gs pos="35001">
+              <a:srgbClr val="BFD5FF"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="E5EEFF"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:ln w="9525" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="4A7EBB"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="37999"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="0" i="0" baseline="0">
               <a:effectLst/>
@@ -3278,11 +3379,529 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> </a:t>
+            <a:t> ESTANDAR DE OPERACIÓN</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="900">
+          <a:endParaRPr lang="en-US" sz="1000">
             <a:effectLst/>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>106364</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>11113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>226638</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>788353</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 405">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B9672F6-FAE0-4370-A969-269655BB2A1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3011489" y="10448926"/>
+          <a:ext cx="1461712" cy="777240"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="A3C4FF"/>
+            </a:gs>
+            <a:gs pos="35001">
+              <a:srgbClr val="BFD5FF"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="E5EEFF"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:ln w="9525" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="4A7EBB"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="37999"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" baseline="0">
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> ESTANDAR DE OPERACIÓN</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>52388</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>187325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>29787</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>774065</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="AutoShape 405">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68F0789D-182A-4FA8-8BDC-22AB1D9DEDB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4576763" y="10434638"/>
+          <a:ext cx="1461712" cy="777240"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="A3C4FF"/>
+            </a:gs>
+            <a:gs pos="35001">
+              <a:srgbClr val="BFD5FF"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="E5EEFF"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:ln w="9525" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="4A7EBB"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="37999"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" baseline="0">
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> ESTANDAR DE OPERACIÓN</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>173038</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>182187</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>759778</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="AutoShape 405">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{560311DD-6A25-4F33-B9E6-0EE5B9B1923A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6189663" y="10420351"/>
+          <a:ext cx="1461712" cy="777240"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:srgbClr val="A3C4FF"/>
+            </a:gs>
+            <a:gs pos="35001">
+              <a:srgbClr val="BFD5FF"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:srgbClr val="E5EEFF"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:ln w="9525" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="4A7EBB"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="37999"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" baseline="0">
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> ESTANDAR DE OPERACIÓN</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>149454</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>541677</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Donut 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C791219-3878-4A00-983C-66448F4522FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8032750" y="10612438"/>
+          <a:ext cx="316142" cy="367052"/>
+        </a:xfrm>
+        <a:prstGeom prst="donut">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 2946"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000"/>
+            <a:t>V</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>33054</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>675334</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Multiplication Sign 32957">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CCB82C0-6014-49B5-BD18-08FBA66C1471}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8588375" y="10533063"/>
+          <a:ext cx="374367" cy="580084"/>
+        </a:xfrm>
+        <a:prstGeom prst="mathMultiply">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>166689</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>182563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>323895</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>935351</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="AutoShape 351">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2E7EA1F-56D1-48BB-8468-FDE27B0AA249}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9278939" y="10429876"/>
+          <a:ext cx="1919331" cy="943288"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="4A7EBB"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw dist="20000" dir="5400000" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="37999"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana"/>
+              <a:ea typeface="Verdana"/>
+              <a:cs typeface="Verdana"/>
+            </a:rPr>
+            <a:t>SE DEBE IDENTIFICAR PUNTOS CRITICOS DE SEGURIDAD AL INGRESO Y SALIDA DE LA PLATAFORMA</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4334,42 +4953,42 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="270" t="s">
+      <c r="N2" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="270"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="270"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="270"/>
-      <c r="U2" s="270"/>
-      <c r="V2" s="270"/>
-      <c r="W2" s="270"/>
-      <c r="X2" s="270"/>
-      <c r="Y2" s="270"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="270"/>
-      <c r="AB2" s="270"/>
-      <c r="AC2" s="270"/>
-      <c r="AD2" s="270"/>
-      <c r="AE2" s="270"/>
-      <c r="AF2" s="270"/>
-      <c r="AG2" s="270"/>
-      <c r="AH2" s="270"/>
-      <c r="AI2" s="270"/>
-      <c r="AJ2" s="270"/>
-      <c r="AK2" s="270"/>
-      <c r="AL2" s="270"/>
-      <c r="AM2" s="270"/>
-      <c r="AN2" s="270"/>
-      <c r="AO2" s="270"/>
-      <c r="AP2" s="270"/>
-      <c r="AQ2" s="270"/>
-      <c r="AR2" s="270"/>
-      <c r="AS2" s="270"/>
-      <c r="AT2" s="270"/>
-      <c r="AU2" s="270"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
+      <c r="U2" s="121"/>
+      <c r="V2" s="121"/>
+      <c r="W2" s="121"/>
+      <c r="X2" s="121"/>
+      <c r="Y2" s="121"/>
+      <c r="Z2" s="121"/>
+      <c r="AA2" s="121"/>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="121"/>
+      <c r="AF2" s="121"/>
+      <c r="AG2" s="121"/>
+      <c r="AH2" s="121"/>
+      <c r="AI2" s="121"/>
+      <c r="AJ2" s="121"/>
+      <c r="AK2" s="121"/>
+      <c r="AL2" s="121"/>
+      <c r="AM2" s="121"/>
+      <c r="AN2" s="121"/>
+      <c r="AO2" s="121"/>
+      <c r="AP2" s="121"/>
+      <c r="AQ2" s="121"/>
+      <c r="AR2" s="121"/>
+      <c r="AS2" s="121"/>
+      <c r="AT2" s="121"/>
+      <c r="AU2" s="121"/>
       <c r="AV2" s="3"/>
       <c r="AW2" s="3"/>
       <c r="AX2" s="3"/>
@@ -4392,40 +5011,40 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="271"/>
-      <c r="O3" s="271"/>
-      <c r="P3" s="271"/>
-      <c r="Q3" s="271"/>
-      <c r="R3" s="271"/>
-      <c r="S3" s="271"/>
-      <c r="T3" s="271"/>
-      <c r="U3" s="271"/>
-      <c r="V3" s="271"/>
-      <c r="W3" s="271"/>
-      <c r="X3" s="271"/>
-      <c r="Y3" s="271"/>
-      <c r="Z3" s="271"/>
-      <c r="AA3" s="271"/>
-      <c r="AB3" s="271"/>
-      <c r="AC3" s="271"/>
-      <c r="AD3" s="271"/>
-      <c r="AE3" s="271"/>
-      <c r="AF3" s="271"/>
-      <c r="AG3" s="271"/>
-      <c r="AH3" s="271"/>
-      <c r="AI3" s="271"/>
-      <c r="AJ3" s="271"/>
-      <c r="AK3" s="271"/>
-      <c r="AL3" s="271"/>
-      <c r="AM3" s="271"/>
-      <c r="AN3" s="271"/>
-      <c r="AO3" s="271"/>
-      <c r="AP3" s="271"/>
-      <c r="AQ3" s="271"/>
-      <c r="AR3" s="271"/>
-      <c r="AS3" s="271"/>
-      <c r="AT3" s="271"/>
-      <c r="AU3" s="271"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="122"/>
+      <c r="W3" s="122"/>
+      <c r="X3" s="122"/>
+      <c r="Y3" s="122"/>
+      <c r="Z3" s="122"/>
+      <c r="AA3" s="122"/>
+      <c r="AB3" s="122"/>
+      <c r="AC3" s="122"/>
+      <c r="AD3" s="122"/>
+      <c r="AE3" s="122"/>
+      <c r="AF3" s="122"/>
+      <c r="AG3" s="122"/>
+      <c r="AH3" s="122"/>
+      <c r="AI3" s="122"/>
+      <c r="AJ3" s="122"/>
+      <c r="AK3" s="122"/>
+      <c r="AL3" s="122"/>
+      <c r="AM3" s="122"/>
+      <c r="AN3" s="122"/>
+      <c r="AO3" s="122"/>
+      <c r="AP3" s="122"/>
+      <c r="AQ3" s="122"/>
+      <c r="AR3" s="122"/>
+      <c r="AS3" s="122"/>
+      <c r="AT3" s="122"/>
+      <c r="AU3" s="122"/>
       <c r="AV3" s="7"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
@@ -4442,82 +5061,82 @@
         <v>1</v>
       </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="263"/>
-      <c r="H4" s="263"/>
-      <c r="I4" s="263"/>
-      <c r="J4" s="263"/>
-      <c r="K4" s="263"/>
-      <c r="L4" s="263"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
-      <c r="O4" s="273" t="s">
+      <c r="O4" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="P4" s="273"/>
-      <c r="Q4" s="273"/>
-      <c r="R4" s="273"/>
-      <c r="S4" s="273"/>
-      <c r="T4" s="273"/>
-      <c r="U4" s="273"/>
-      <c r="V4" s="273"/>
-      <c r="W4" s="273"/>
-      <c r="X4" s="273"/>
-      <c r="Y4" s="273"/>
-      <c r="Z4" s="273"/>
-      <c r="AA4" s="273"/>
-      <c r="AB4" s="274" t="s">
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="274" t="s">
+      <c r="AC4" s="126"/>
+      <c r="AD4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="AE4" s="275"/>
-      <c r="AF4" s="274" t="s">
+      <c r="AE4" s="126"/>
+      <c r="AF4" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="AG4" s="276"/>
-      <c r="AH4" s="277" t="s">
+      <c r="AG4" s="127"/>
+      <c r="AH4" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="AI4" s="278"/>
-      <c r="AJ4" s="277" t="s">
+      <c r="AI4" s="129"/>
+      <c r="AJ4" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="AK4" s="278"/>
-      <c r="AL4" s="274" t="s">
+      <c r="AK4" s="129"/>
+      <c r="AL4" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="AM4" s="279"/>
-      <c r="AN4" s="280"/>
-      <c r="AO4" s="281"/>
-      <c r="AP4" s="281"/>
-      <c r="AQ4" s="281"/>
-      <c r="AR4" s="281"/>
-      <c r="AS4" s="281"/>
-      <c r="AT4" s="281"/>
-      <c r="AU4" s="281"/>
-      <c r="AV4" s="281"/>
-      <c r="AW4" s="281"/>
-      <c r="AX4" s="281"/>
-      <c r="AY4" s="281"/>
-      <c r="AZ4" s="281"/>
-      <c r="BA4" s="281"/>
-      <c r="BB4" s="281"/>
-      <c r="BC4" s="281"/>
-      <c r="BD4" s="282"/>
+      <c r="AM4" s="130"/>
+      <c r="AN4" s="131"/>
+      <c r="AO4" s="132"/>
+      <c r="AP4" s="132"/>
+      <c r="AQ4" s="132"/>
+      <c r="AR4" s="132"/>
+      <c r="AS4" s="132"/>
+      <c r="AT4" s="132"/>
+      <c r="AU4" s="132"/>
+      <c r="AV4" s="132"/>
+      <c r="AW4" s="132"/>
+      <c r="AX4" s="132"/>
+      <c r="AY4" s="132"/>
+      <c r="AZ4" s="132"/>
+      <c r="BA4" s="132"/>
+      <c r="BB4" s="132"/>
+      <c r="BC4" s="132"/>
+      <c r="BD4" s="133"/>
     </row>
     <row r="5" spans="3:56" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="263"/>
-      <c r="G5" s="263"/>
-      <c r="H5" s="263"/>
-      <c r="I5" s="263"/>
-      <c r="J5" s="263"/>
-      <c r="K5" s="263"/>
-      <c r="L5" s="263"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>
       <c r="O5" s="14"/>
@@ -4622,60 +5241,60 @@
       <c r="BD6" s="19"/>
     </row>
     <row r="7" spans="3:56" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="264"/>
-      <c r="D7" s="265"/>
-      <c r="E7" s="265"/>
-      <c r="F7" s="265"/>
-      <c r="G7" s="265"/>
-      <c r="H7" s="265"/>
-      <c r="I7" s="265"/>
-      <c r="J7" s="265"/>
-      <c r="K7" s="265"/>
-      <c r="L7" s="265"/>
-      <c r="M7" s="265"/>
-      <c r="N7" s="265"/>
-      <c r="O7" s="265"/>
-      <c r="P7" s="265"/>
-      <c r="Q7" s="265"/>
-      <c r="R7" s="265"/>
-      <c r="S7" s="265"/>
-      <c r="T7" s="265"/>
-      <c r="U7" s="265"/>
-      <c r="V7" s="265"/>
-      <c r="W7" s="265"/>
-      <c r="X7" s="265"/>
-      <c r="Y7" s="265"/>
-      <c r="Z7" s="265"/>
-      <c r="AA7" s="265"/>
-      <c r="AB7" s="265"/>
-      <c r="AC7" s="265"/>
-      <c r="AD7" s="265"/>
-      <c r="AE7" s="265"/>
-      <c r="AF7" s="265"/>
-      <c r="AG7" s="265"/>
-      <c r="AH7" s="265"/>
-      <c r="AI7" s="265"/>
-      <c r="AJ7" s="265"/>
-      <c r="AK7" s="265"/>
-      <c r="AL7" s="265"/>
-      <c r="AM7" s="265"/>
-      <c r="AN7" s="265"/>
-      <c r="AO7" s="265"/>
-      <c r="AP7" s="265"/>
-      <c r="AQ7" s="265"/>
-      <c r="AR7" s="265"/>
-      <c r="AS7" s="265"/>
-      <c r="AT7" s="265"/>
-      <c r="AU7" s="265"/>
-      <c r="AV7" s="265"/>
-      <c r="AW7" s="265"/>
-      <c r="AX7" s="265"/>
-      <c r="AY7" s="265"/>
-      <c r="AZ7" s="265"/>
-      <c r="BA7" s="265"/>
-      <c r="BB7" s="265"/>
-      <c r="BC7" s="265"/>
-      <c r="BD7" s="266"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="110"/>
+      <c r="U7" s="110"/>
+      <c r="V7" s="110"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="110"/>
+      <c r="Y7" s="110"/>
+      <c r="Z7" s="110"/>
+      <c r="AA7" s="110"/>
+      <c r="AB7" s="110"/>
+      <c r="AC7" s="110"/>
+      <c r="AD7" s="110"/>
+      <c r="AE7" s="110"/>
+      <c r="AF7" s="110"/>
+      <c r="AG7" s="110"/>
+      <c r="AH7" s="110"/>
+      <c r="AI7" s="110"/>
+      <c r="AJ7" s="110"/>
+      <c r="AK7" s="110"/>
+      <c r="AL7" s="110"/>
+      <c r="AM7" s="110"/>
+      <c r="AN7" s="110"/>
+      <c r="AO7" s="110"/>
+      <c r="AP7" s="110"/>
+      <c r="AQ7" s="110"/>
+      <c r="AR7" s="110"/>
+      <c r="AS7" s="110"/>
+      <c r="AT7" s="110"/>
+      <c r="AU7" s="110"/>
+      <c r="AV7" s="110"/>
+      <c r="AW7" s="110"/>
+      <c r="AX7" s="110"/>
+      <c r="AY7" s="110"/>
+      <c r="AZ7" s="110"/>
+      <c r="BA7" s="110"/>
+      <c r="BB7" s="110"/>
+      <c r="BC7" s="110"/>
+      <c r="BD7" s="111"/>
     </row>
     <row r="8" spans="3:56" ht="3.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="20"/>
@@ -4738,54 +5357,54 @@
       <c r="D9" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="267"/>
-      <c r="H9" s="268"/>
-      <c r="I9" s="268"/>
-      <c r="J9" s="268"/>
-      <c r="K9" s="268"/>
-      <c r="L9" s="268"/>
-      <c r="M9" s="268"/>
-      <c r="N9" s="268"/>
-      <c r="O9" s="268"/>
-      <c r="P9" s="268"/>
-      <c r="Q9" s="268"/>
-      <c r="R9" s="268"/>
-      <c r="S9" s="268"/>
-      <c r="T9" s="268"/>
-      <c r="U9" s="268"/>
-      <c r="V9" s="268"/>
-      <c r="W9" s="268"/>
-      <c r="X9" s="268"/>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
-      <c r="AA9" s="268"/>
-      <c r="AB9" s="268"/>
-      <c r="AC9" s="268"/>
-      <c r="AD9" s="268"/>
-      <c r="AE9" s="268"/>
-      <c r="AF9" s="268"/>
-      <c r="AG9" s="268"/>
-      <c r="AH9" s="268"/>
-      <c r="AI9" s="268"/>
-      <c r="AJ9" s="268"/>
-      <c r="AK9" s="268"/>
-      <c r="AL9" s="268"/>
-      <c r="AM9" s="268"/>
-      <c r="AN9" s="268"/>
-      <c r="AO9" s="268"/>
-      <c r="AP9" s="268"/>
-      <c r="AQ9" s="268"/>
-      <c r="AR9" s="268"/>
-      <c r="AS9" s="268"/>
-      <c r="AT9" s="268"/>
-      <c r="AU9" s="268"/>
-      <c r="AV9" s="268"/>
-      <c r="AW9" s="268"/>
-      <c r="AX9" s="268"/>
-      <c r="AY9" s="268"/>
-      <c r="AZ9" s="268"/>
-      <c r="BA9" s="268"/>
-      <c r="BB9" s="269"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="113"/>
+      <c r="W9" s="113"/>
+      <c r="X9" s="113"/>
+      <c r="Y9" s="113"/>
+      <c r="Z9" s="113"/>
+      <c r="AA9" s="113"/>
+      <c r="AB9" s="113"/>
+      <c r="AC9" s="113"/>
+      <c r="AD9" s="113"/>
+      <c r="AE9" s="113"/>
+      <c r="AF9" s="113"/>
+      <c r="AG9" s="113"/>
+      <c r="AH9" s="113"/>
+      <c r="AI9" s="113"/>
+      <c r="AJ9" s="113"/>
+      <c r="AK9" s="113"/>
+      <c r="AL9" s="113"/>
+      <c r="AM9" s="113"/>
+      <c r="AN9" s="113"/>
+      <c r="AO9" s="113"/>
+      <c r="AP9" s="113"/>
+      <c r="AQ9" s="113"/>
+      <c r="AR9" s="113"/>
+      <c r="AS9" s="113"/>
+      <c r="AT9" s="113"/>
+      <c r="AU9" s="113"/>
+      <c r="AV9" s="113"/>
+      <c r="AW9" s="113"/>
+      <c r="AX9" s="113"/>
+      <c r="AY9" s="113"/>
+      <c r="AZ9" s="113"/>
+      <c r="BA9" s="113"/>
+      <c r="BB9" s="114"/>
       <c r="BD9" s="25"/>
     </row>
     <row r="10" spans="3:56" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4824,49 +5443,49 @@
       <c r="D13" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="258"/>
-      <c r="J13" s="259"/>
-      <c r="K13" s="259"/>
-      <c r="L13" s="259"/>
-      <c r="M13" s="259"/>
-      <c r="N13" s="259"/>
-      <c r="O13" s="259"/>
-      <c r="P13" s="259"/>
-      <c r="Q13" s="259"/>
-      <c r="R13" s="259"/>
-      <c r="S13" s="259"/>
-      <c r="T13" s="259"/>
-      <c r="U13" s="259"/>
-      <c r="V13" s="259"/>
-      <c r="W13" s="259"/>
-      <c r="X13" s="259"/>
-      <c r="Y13" s="260"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="116"/>
+      <c r="N13" s="116"/>
+      <c r="O13" s="116"/>
+      <c r="P13" s="116"/>
+      <c r="Q13" s="116"/>
+      <c r="R13" s="116"/>
+      <c r="S13" s="116"/>
+      <c r="T13" s="116"/>
+      <c r="U13" s="116"/>
+      <c r="V13" s="116"/>
+      <c r="W13" s="116"/>
+      <c r="X13" s="116"/>
+      <c r="Y13" s="117"/>
       <c r="Z13" s="28"/>
       <c r="AA13" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AC13" s="258"/>
-      <c r="AD13" s="259"/>
-      <c r="AE13" s="260"/>
+      <c r="AC13" s="115"/>
+      <c r="AD13" s="116"/>
+      <c r="AE13" s="117"/>
       <c r="AG13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="AL13" s="255"/>
-      <c r="AM13" s="256"/>
-      <c r="AN13" s="256"/>
-      <c r="AO13" s="256"/>
-      <c r="AP13" s="256"/>
-      <c r="AQ13" s="257"/>
+      <c r="AL13" s="118"/>
+      <c r="AM13" s="119"/>
+      <c r="AN13" s="119"/>
+      <c r="AO13" s="119"/>
+      <c r="AP13" s="119"/>
+      <c r="AQ13" s="120"/>
       <c r="AU13" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="AV13" s="255"/>
-      <c r="AW13" s="256"/>
-      <c r="AX13" s="256"/>
-      <c r="AY13" s="256"/>
-      <c r="AZ13" s="256"/>
-      <c r="BA13" s="256"/>
-      <c r="BB13" s="257"/>
+      <c r="AV13" s="118"/>
+      <c r="AW13" s="119"/>
+      <c r="AX13" s="119"/>
+      <c r="AY13" s="119"/>
+      <c r="AZ13" s="119"/>
+      <c r="BA13" s="119"/>
+      <c r="BB13" s="120"/>
       <c r="BD13" s="25"/>
     </row>
     <row r="14" spans="3:56" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -4880,47 +5499,47 @@
       <c r="D15" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="255"/>
-      <c r="J15" s="256"/>
-      <c r="K15" s="256"/>
-      <c r="L15" s="256"/>
-      <c r="M15" s="256"/>
-      <c r="N15" s="257"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="119"/>
+      <c r="N15" s="120"/>
       <c r="S15" s="29"/>
       <c r="T15" s="29" t="s">
         <v>1</v>
       </c>
       <c r="U15" s="29"/>
-      <c r="V15" s="258"/>
-      <c r="W15" s="259"/>
-      <c r="X15" s="259"/>
-      <c r="Y15" s="259"/>
-      <c r="Z15" s="259"/>
-      <c r="AA15" s="259"/>
-      <c r="AB15" s="259"/>
-      <c r="AC15" s="259"/>
-      <c r="AD15" s="259"/>
-      <c r="AE15" s="260"/>
+      <c r="V15" s="115"/>
+      <c r="W15" s="116"/>
+      <c r="X15" s="116"/>
+      <c r="Y15" s="116"/>
+      <c r="Z15" s="116"/>
+      <c r="AA15" s="116"/>
+      <c r="AB15" s="116"/>
+      <c r="AC15" s="116"/>
+      <c r="AD15" s="116"/>
+      <c r="AE15" s="117"/>
       <c r="AG15" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="AL15" s="255"/>
-      <c r="AM15" s="256"/>
-      <c r="AN15" s="256"/>
-      <c r="AO15" s="256"/>
-      <c r="AP15" s="256"/>
-      <c r="AQ15" s="256"/>
-      <c r="AR15" s="256"/>
-      <c r="AS15" s="256"/>
-      <c r="AT15" s="256"/>
-      <c r="AU15" s="256"/>
-      <c r="AV15" s="256"/>
-      <c r="AW15" s="256"/>
-      <c r="AX15" s="256"/>
-      <c r="AY15" s="256"/>
-      <c r="AZ15" s="256"/>
-      <c r="BA15" s="256"/>
-      <c r="BB15" s="257"/>
+      <c r="AL15" s="118"/>
+      <c r="AM15" s="119"/>
+      <c r="AN15" s="119"/>
+      <c r="AO15" s="119"/>
+      <c r="AP15" s="119"/>
+      <c r="AQ15" s="119"/>
+      <c r="AR15" s="119"/>
+      <c r="AS15" s="119"/>
+      <c r="AT15" s="119"/>
+      <c r="AU15" s="119"/>
+      <c r="AV15" s="119"/>
+      <c r="AW15" s="119"/>
+      <c r="AX15" s="119"/>
+      <c r="AY15" s="119"/>
+      <c r="AZ15" s="119"/>
+      <c r="BA15" s="119"/>
+      <c r="BB15" s="120"/>
       <c r="BC15" s="31"/>
       <c r="BD15" s="25"/>
     </row>
@@ -4939,19 +5558,19 @@
       <c r="F17" s="34"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
-      <c r="I17" s="239"/>
-      <c r="J17" s="241"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="135"/>
       <c r="K17" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="L17" s="239"/>
-      <c r="M17" s="241"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="135"/>
       <c r="N17" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="O17" s="239"/>
-      <c r="P17" s="240"/>
-      <c r="Q17" s="241"/>
+      <c r="O17" s="134"/>
+      <c r="P17" s="136"/>
+      <c r="Q17" s="135"/>
       <c r="R17" s="34"/>
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
@@ -4964,8 +5583,8 @@
       <c r="AA17" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="AB17" s="261"/>
-      <c r="AC17" s="262"/>
+      <c r="AB17" s="137"/>
+      <c r="AC17" s="138"/>
       <c r="AD17" s="34" t="s">
         <v>21</v>
       </c>
@@ -4978,11 +5597,11 @@
       <c r="AI17" s="34"/>
       <c r="AJ17" s="34"/>
       <c r="AK17" s="34"/>
-      <c r="AL17" s="239"/>
-      <c r="AM17" s="240"/>
-      <c r="AN17" s="240"/>
-      <c r="AO17" s="240"/>
-      <c r="AP17" s="241"/>
+      <c r="AL17" s="134"/>
+      <c r="AM17" s="136"/>
+      <c r="AN17" s="136"/>
+      <c r="AO17" s="136"/>
+      <c r="AP17" s="135"/>
       <c r="AQ17" s="34"/>
       <c r="AR17" s="33" t="s">
         <v>23</v>
@@ -4992,11 +5611,11 @@
       <c r="AU17" s="34"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="34"/>
-      <c r="AX17" s="247"/>
-      <c r="AY17" s="248"/>
-      <c r="AZ17" s="248"/>
-      <c r="BA17" s="248"/>
-      <c r="BB17" s="249"/>
+      <c r="AX17" s="139"/>
+      <c r="AY17" s="140"/>
+      <c r="AZ17" s="140"/>
+      <c r="BA17" s="140"/>
+      <c r="BB17" s="141"/>
       <c r="BD17" s="25"/>
     </row>
     <row r="18" spans="3:56" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -5063,16 +5682,16 @@
       <c r="F19" s="34"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
-      <c r="I19" s="239"/>
-      <c r="J19" s="240"/>
-      <c r="K19" s="240"/>
-      <c r="L19" s="240"/>
-      <c r="M19" s="240"/>
-      <c r="N19" s="240"/>
-      <c r="O19" s="240"/>
-      <c r="P19" s="240"/>
-      <c r="Q19" s="240"/>
-      <c r="R19" s="240"/>
+      <c r="I19" s="134"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
+      <c r="R19" s="136"/>
       <c r="S19" s="40"/>
       <c r="T19" s="33" t="s">
         <v>25</v>
@@ -5080,25 +5699,25 @@
       <c r="U19" s="34"/>
       <c r="V19" s="34"/>
       <c r="W19" s="34"/>
-      <c r="X19" s="250"/>
-      <c r="Y19" s="251"/>
-      <c r="Z19" s="251"/>
-      <c r="AA19" s="251"/>
-      <c r="AB19" s="251"/>
-      <c r="AC19" s="251"/>
-      <c r="AD19" s="251"/>
-      <c r="AE19" s="251"/>
-      <c r="AF19" s="251"/>
-      <c r="AG19" s="252"/>
-      <c r="AH19" s="253" t="s">
+      <c r="X19" s="147"/>
+      <c r="Y19" s="148"/>
+      <c r="Z19" s="148"/>
+      <c r="AA19" s="148"/>
+      <c r="AB19" s="148"/>
+      <c r="AC19" s="148"/>
+      <c r="AD19" s="148"/>
+      <c r="AE19" s="148"/>
+      <c r="AF19" s="148"/>
+      <c r="AG19" s="149"/>
+      <c r="AH19" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="AI19" s="254"/>
-      <c r="AJ19" s="254"/>
-      <c r="AK19" s="254"/>
-      <c r="AL19" s="254"/>
-      <c r="AM19" s="254"/>
-      <c r="AN19" s="254"/>
+      <c r="AI19" s="151"/>
+      <c r="AJ19" s="151"/>
+      <c r="AK19" s="151"/>
+      <c r="AL19" s="151"/>
+      <c r="AM19" s="151"/>
+      <c r="AN19" s="151"/>
       <c r="AO19" s="33" t="s">
         <v>27</v>
       </c>
@@ -5184,18 +5803,18 @@
       <c r="F21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
-      <c r="I21" s="239"/>
-      <c r="J21" s="240"/>
-      <c r="K21" s="240"/>
-      <c r="L21" s="240"/>
-      <c r="M21" s="240"/>
-      <c r="N21" s="240"/>
-      <c r="O21" s="240"/>
-      <c r="P21" s="240"/>
-      <c r="Q21" s="240"/>
-      <c r="R21" s="240"/>
-      <c r="S21" s="240"/>
-      <c r="T21" s="240"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+      <c r="N21" s="136"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="136"/>
+      <c r="Q21" s="136"/>
+      <c r="R21" s="136"/>
+      <c r="S21" s="136"/>
+      <c r="T21" s="136"/>
       <c r="U21" s="40"/>
       <c r="V21" s="33" t="s">
         <v>30</v>
@@ -5203,19 +5822,19 @@
       <c r="W21" s="34"/>
       <c r="X21" s="42"/>
       <c r="Y21" s="42"/>
-      <c r="Z21" s="239"/>
-      <c r="AA21" s="240"/>
-      <c r="AB21" s="240"/>
-      <c r="AC21" s="240"/>
-      <c r="AD21" s="240"/>
-      <c r="AE21" s="240"/>
-      <c r="AF21" s="240"/>
-      <c r="AG21" s="240"/>
-      <c r="AH21" s="240"/>
-      <c r="AI21" s="240"/>
-      <c r="AJ21" s="240"/>
-      <c r="AK21" s="240"/>
-      <c r="AL21" s="240"/>
+      <c r="Z21" s="134"/>
+      <c r="AA21" s="136"/>
+      <c r="AB21" s="136"/>
+      <c r="AC21" s="136"/>
+      <c r="AD21" s="136"/>
+      <c r="AE21" s="136"/>
+      <c r="AF21" s="136"/>
+      <c r="AG21" s="136"/>
+      <c r="AH21" s="136"/>
+      <c r="AI21" s="136"/>
+      <c r="AJ21" s="136"/>
+      <c r="AK21" s="136"/>
+      <c r="AL21" s="136"/>
       <c r="AM21" s="45"/>
       <c r="AN21" s="33" t="s">
         <v>31</v>
@@ -5224,16 +5843,16 @@
       <c r="AP21" s="34"/>
       <c r="AQ21" s="44"/>
       <c r="AR21" s="44"/>
-      <c r="AS21" s="250"/>
-      <c r="AT21" s="251"/>
-      <c r="AU21" s="251"/>
-      <c r="AV21" s="251"/>
-      <c r="AW21" s="251"/>
-      <c r="AX21" s="251"/>
-      <c r="AY21" s="251"/>
-      <c r="AZ21" s="251"/>
-      <c r="BA21" s="251"/>
-      <c r="BB21" s="252"/>
+      <c r="AS21" s="147"/>
+      <c r="AT21" s="148"/>
+      <c r="AU21" s="148"/>
+      <c r="AV21" s="148"/>
+      <c r="AW21" s="148"/>
+      <c r="AX21" s="148"/>
+      <c r="AY21" s="148"/>
+      <c r="AZ21" s="148"/>
+      <c r="BA21" s="148"/>
+      <c r="BB21" s="149"/>
       <c r="BD21" s="25"/>
     </row>
     <row r="22" spans="3:56" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -5300,14 +5919,14 @@
       <c r="F23" s="34"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
-      <c r="I23" s="239"/>
-      <c r="J23" s="240"/>
-      <c r="K23" s="240"/>
-      <c r="L23" s="240"/>
-      <c r="M23" s="240"/>
-      <c r="N23" s="240"/>
-      <c r="O23" s="240"/>
-      <c r="P23" s="241"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="136"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="135"/>
       <c r="T23" s="33" t="s">
         <v>33</v>
       </c>
@@ -5316,33 +5935,33 @@
       <c r="Y23" s="48"/>
       <c r="Z23" s="42"/>
       <c r="AB23" s="49"/>
-      <c r="AC23" s="240"/>
-      <c r="AD23" s="240"/>
-      <c r="AE23" s="240"/>
-      <c r="AF23" s="240"/>
-      <c r="AG23" s="240"/>
-      <c r="AH23" s="240"/>
-      <c r="AI23" s="240"/>
-      <c r="AJ23" s="240"/>
-      <c r="AK23" s="240"/>
-      <c r="AL23" s="241"/>
-      <c r="AN23" s="242" t="s">
+      <c r="AC23" s="136"/>
+      <c r="AD23" s="136"/>
+      <c r="AE23" s="136"/>
+      <c r="AF23" s="136"/>
+      <c r="AG23" s="136"/>
+      <c r="AH23" s="136"/>
+      <c r="AI23" s="136"/>
+      <c r="AJ23" s="136"/>
+      <c r="AK23" s="136"/>
+      <c r="AL23" s="135"/>
+      <c r="AN23" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="AO23" s="242"/>
-      <c r="AP23" s="242"/>
-      <c r="AQ23" s="242"/>
-      <c r="AR23" s="242"/>
-      <c r="AS23" s="242"/>
-      <c r="AT23" s="242"/>
-      <c r="AU23" s="242"/>
-      <c r="AV23" s="243"/>
-      <c r="AW23" s="244"/>
-      <c r="AX23" s="245"/>
-      <c r="AY23" s="245"/>
-      <c r="AZ23" s="245"/>
-      <c r="BA23" s="245"/>
-      <c r="BB23" s="246"/>
+      <c r="AO23" s="142"/>
+      <c r="AP23" s="142"/>
+      <c r="AQ23" s="142"/>
+      <c r="AR23" s="142"/>
+      <c r="AS23" s="142"/>
+      <c r="AT23" s="142"/>
+      <c r="AU23" s="142"/>
+      <c r="AV23" s="143"/>
+      <c r="AW23" s="144"/>
+      <c r="AX23" s="145"/>
+      <c r="AY23" s="145"/>
+      <c r="AZ23" s="145"/>
+      <c r="BA23" s="145"/>
+      <c r="BB23" s="146"/>
       <c r="BD23" s="25"/>
     </row>
     <row r="24" spans="3:56" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -5411,17 +6030,17 @@
       <c r="H25" s="34"/>
       <c r="I25" s="42"/>
       <c r="J25" s="42"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="240"/>
-      <c r="M25" s="240"/>
-      <c r="N25" s="240"/>
-      <c r="O25" s="240"/>
-      <c r="P25" s="240"/>
-      <c r="Q25" s="240"/>
-      <c r="R25" s="240"/>
-      <c r="S25" s="240"/>
-      <c r="T25" s="240"/>
-      <c r="U25" s="241"/>
+      <c r="K25" s="134"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="136"/>
+      <c r="R25" s="136"/>
+      <c r="S25" s="136"/>
+      <c r="T25" s="136"/>
+      <c r="U25" s="135"/>
       <c r="V25" s="42"/>
       <c r="W25" s="33" t="s">
         <v>36</v>
@@ -5435,28 +6054,28 @@
       <c r="AD25" s="34"/>
       <c r="AE25" s="34"/>
       <c r="AF25" s="34"/>
-      <c r="AG25" s="247"/>
-      <c r="AH25" s="248"/>
-      <c r="AI25" s="248"/>
-      <c r="AJ25" s="248"/>
-      <c r="AK25" s="248"/>
-      <c r="AL25" s="248"/>
-      <c r="AM25" s="248"/>
-      <c r="AN25" s="248"/>
-      <c r="AO25" s="248"/>
-      <c r="AP25" s="248"/>
-      <c r="AQ25" s="248"/>
-      <c r="AR25" s="248"/>
-      <c r="AS25" s="248"/>
-      <c r="AT25" s="248"/>
-      <c r="AU25" s="248"/>
-      <c r="AV25" s="248"/>
-      <c r="AW25" s="248"/>
-      <c r="AX25" s="248"/>
-      <c r="AY25" s="248"/>
-      <c r="AZ25" s="248"/>
-      <c r="BA25" s="248"/>
-      <c r="BB25" s="249"/>
+      <c r="AG25" s="139"/>
+      <c r="AH25" s="140"/>
+      <c r="AI25" s="140"/>
+      <c r="AJ25" s="140"/>
+      <c r="AK25" s="140"/>
+      <c r="AL25" s="140"/>
+      <c r="AM25" s="140"/>
+      <c r="AN25" s="140"/>
+      <c r="AO25" s="140"/>
+      <c r="AP25" s="140"/>
+      <c r="AQ25" s="140"/>
+      <c r="AR25" s="140"/>
+      <c r="AS25" s="140"/>
+      <c r="AT25" s="140"/>
+      <c r="AU25" s="140"/>
+      <c r="AV25" s="140"/>
+      <c r="AW25" s="140"/>
+      <c r="AX25" s="140"/>
+      <c r="AY25" s="140"/>
+      <c r="AZ25" s="140"/>
+      <c r="BA25" s="140"/>
+      <c r="BB25" s="141"/>
       <c r="BD25" s="25"/>
     </row>
     <row r="26" spans="3:56" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5523,228 +6142,228 @@
       <c r="BD27" s="55"/>
     </row>
     <row r="28" spans="3:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="219"/>
-      <c r="D28" s="220"/>
-      <c r="E28" s="220"/>
-      <c r="F28" s="220"/>
-      <c r="G28" s="220"/>
-      <c r="H28" s="220"/>
-      <c r="I28" s="220"/>
-      <c r="J28" s="220"/>
-      <c r="K28" s="220"/>
-      <c r="L28" s="220"/>
-      <c r="M28" s="220"/>
-      <c r="N28" s="220"/>
-      <c r="O28" s="220"/>
-      <c r="P28" s="220"/>
-      <c r="Q28" s="220"/>
-      <c r="R28" s="220"/>
-      <c r="S28" s="220"/>
-      <c r="T28" s="220"/>
-      <c r="U28" s="220"/>
-      <c r="V28" s="220"/>
-      <c r="W28" s="220"/>
-      <c r="X28" s="220"/>
-      <c r="Y28" s="220"/>
-      <c r="Z28" s="220"/>
-      <c r="AA28" s="220"/>
-      <c r="AB28" s="220"/>
-      <c r="AC28" s="220"/>
-      <c r="AD28" s="220"/>
-      <c r="AE28" s="220"/>
-      <c r="AF28" s="220"/>
-      <c r="AG28" s="220"/>
-      <c r="AH28" s="220"/>
-      <c r="AI28" s="220"/>
-      <c r="AJ28" s="220"/>
-      <c r="AK28" s="220"/>
-      <c r="AL28" s="220"/>
-      <c r="AM28" s="220"/>
-      <c r="AN28" s="220"/>
-      <c r="AO28" s="220"/>
-      <c r="AP28" s="220"/>
-      <c r="AQ28" s="220"/>
-      <c r="AR28" s="220"/>
-      <c r="AS28" s="220"/>
-      <c r="AT28" s="220"/>
-      <c r="AU28" s="220"/>
-      <c r="AV28" s="220"/>
-      <c r="AW28" s="220"/>
-      <c r="AX28" s="220"/>
-      <c r="AY28" s="220"/>
-      <c r="AZ28" s="220"/>
-      <c r="BA28" s="220"/>
-      <c r="BB28" s="220"/>
-      <c r="BC28" s="220"/>
-      <c r="BD28" s="221"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="153"/>
+      <c r="I28" s="153"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="153"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="153"/>
+      <c r="N28" s="153"/>
+      <c r="O28" s="153"/>
+      <c r="P28" s="153"/>
+      <c r="Q28" s="153"/>
+      <c r="R28" s="153"/>
+      <c r="S28" s="153"/>
+      <c r="T28" s="153"/>
+      <c r="U28" s="153"/>
+      <c r="V28" s="153"/>
+      <c r="W28" s="153"/>
+      <c r="X28" s="153"/>
+      <c r="Y28" s="153"/>
+      <c r="Z28" s="153"/>
+      <c r="AA28" s="153"/>
+      <c r="AB28" s="153"/>
+      <c r="AC28" s="153"/>
+      <c r="AD28" s="153"/>
+      <c r="AE28" s="153"/>
+      <c r="AF28" s="153"/>
+      <c r="AG28" s="153"/>
+      <c r="AH28" s="153"/>
+      <c r="AI28" s="153"/>
+      <c r="AJ28" s="153"/>
+      <c r="AK28" s="153"/>
+      <c r="AL28" s="153"/>
+      <c r="AM28" s="153"/>
+      <c r="AN28" s="153"/>
+      <c r="AO28" s="153"/>
+      <c r="AP28" s="153"/>
+      <c r="AQ28" s="153"/>
+      <c r="AR28" s="153"/>
+      <c r="AS28" s="153"/>
+      <c r="AT28" s="153"/>
+      <c r="AU28" s="153"/>
+      <c r="AV28" s="153"/>
+      <c r="AW28" s="153"/>
+      <c r="AX28" s="153"/>
+      <c r="AY28" s="153"/>
+      <c r="AZ28" s="153"/>
+      <c r="BA28" s="153"/>
+      <c r="BB28" s="153"/>
+      <c r="BC28" s="153"/>
+      <c r="BD28" s="154"/>
     </row>
     <row r="29" spans="3:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="219"/>
-      <c r="D29" s="220"/>
-      <c r="E29" s="220"/>
-      <c r="F29" s="220"/>
-      <c r="G29" s="220"/>
-      <c r="H29" s="220"/>
-      <c r="I29" s="220"/>
-      <c r="J29" s="220"/>
-      <c r="K29" s="220"/>
-      <c r="L29" s="220"/>
-      <c r="M29" s="220"/>
-      <c r="N29" s="220"/>
-      <c r="O29" s="220"/>
-      <c r="P29" s="220"/>
-      <c r="Q29" s="220"/>
-      <c r="R29" s="220"/>
-      <c r="S29" s="220"/>
-      <c r="T29" s="220"/>
-      <c r="U29" s="220"/>
-      <c r="V29" s="220"/>
-      <c r="W29" s="220"/>
-      <c r="X29" s="220"/>
-      <c r="Y29" s="220"/>
-      <c r="Z29" s="220"/>
-      <c r="AA29" s="220"/>
-      <c r="AB29" s="220"/>
-      <c r="AC29" s="220"/>
-      <c r="AD29" s="220"/>
-      <c r="AE29" s="220"/>
-      <c r="AF29" s="220"/>
-      <c r="AG29" s="220"/>
-      <c r="AH29" s="220"/>
-      <c r="AI29" s="220"/>
-      <c r="AJ29" s="220"/>
-      <c r="AK29" s="220"/>
-      <c r="AL29" s="220"/>
-      <c r="AM29" s="220"/>
-      <c r="AN29" s="220"/>
-      <c r="AO29" s="220"/>
-      <c r="AP29" s="220"/>
-      <c r="AQ29" s="220"/>
-      <c r="AR29" s="220"/>
-      <c r="AS29" s="220"/>
-      <c r="AT29" s="220"/>
-      <c r="AU29" s="220"/>
-      <c r="AV29" s="220"/>
-      <c r="AW29" s="220"/>
-      <c r="AX29" s="220"/>
-      <c r="AY29" s="220"/>
-      <c r="AZ29" s="220"/>
-      <c r="BA29" s="220"/>
-      <c r="BB29" s="220"/>
-      <c r="BC29" s="220"/>
-      <c r="BD29" s="221"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="153"/>
+      <c r="I29" s="153"/>
+      <c r="J29" s="153"/>
+      <c r="K29" s="153"/>
+      <c r="L29" s="153"/>
+      <c r="M29" s="153"/>
+      <c r="N29" s="153"/>
+      <c r="O29" s="153"/>
+      <c r="P29" s="153"/>
+      <c r="Q29" s="153"/>
+      <c r="R29" s="153"/>
+      <c r="S29" s="153"/>
+      <c r="T29" s="153"/>
+      <c r="U29" s="153"/>
+      <c r="V29" s="153"/>
+      <c r="W29" s="153"/>
+      <c r="X29" s="153"/>
+      <c r="Y29" s="153"/>
+      <c r="Z29" s="153"/>
+      <c r="AA29" s="153"/>
+      <c r="AB29" s="153"/>
+      <c r="AC29" s="153"/>
+      <c r="AD29" s="153"/>
+      <c r="AE29" s="153"/>
+      <c r="AF29" s="153"/>
+      <c r="AG29" s="153"/>
+      <c r="AH29" s="153"/>
+      <c r="AI29" s="153"/>
+      <c r="AJ29" s="153"/>
+      <c r="AK29" s="153"/>
+      <c r="AL29" s="153"/>
+      <c r="AM29" s="153"/>
+      <c r="AN29" s="153"/>
+      <c r="AO29" s="153"/>
+      <c r="AP29" s="153"/>
+      <c r="AQ29" s="153"/>
+      <c r="AR29" s="153"/>
+      <c r="AS29" s="153"/>
+      <c r="AT29" s="153"/>
+      <c r="AU29" s="153"/>
+      <c r="AV29" s="153"/>
+      <c r="AW29" s="153"/>
+      <c r="AX29" s="153"/>
+      <c r="AY29" s="153"/>
+      <c r="AZ29" s="153"/>
+      <c r="BA29" s="153"/>
+      <c r="BB29" s="153"/>
+      <c r="BC29" s="153"/>
+      <c r="BD29" s="154"/>
     </row>
     <row r="30" spans="3:56" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="219"/>
-      <c r="D30" s="220"/>
-      <c r="E30" s="220"/>
-      <c r="F30" s="220"/>
-      <c r="G30" s="220"/>
-      <c r="H30" s="220"/>
-      <c r="I30" s="220"/>
-      <c r="J30" s="220"/>
-      <c r="K30" s="220"/>
-      <c r="L30" s="220"/>
-      <c r="M30" s="220"/>
-      <c r="N30" s="220"/>
-      <c r="O30" s="220"/>
-      <c r="P30" s="220"/>
-      <c r="Q30" s="220"/>
-      <c r="R30" s="220"/>
-      <c r="S30" s="220"/>
-      <c r="T30" s="220"/>
-      <c r="U30" s="220"/>
-      <c r="V30" s="220"/>
-      <c r="W30" s="220"/>
-      <c r="X30" s="220"/>
-      <c r="Y30" s="220"/>
-      <c r="Z30" s="220"/>
-      <c r="AA30" s="220"/>
-      <c r="AB30" s="220"/>
-      <c r="AC30" s="220"/>
-      <c r="AD30" s="220"/>
-      <c r="AE30" s="220"/>
-      <c r="AF30" s="220"/>
-      <c r="AG30" s="220"/>
-      <c r="AH30" s="220"/>
-      <c r="AI30" s="220"/>
-      <c r="AJ30" s="220"/>
-      <c r="AK30" s="220"/>
-      <c r="AL30" s="220"/>
-      <c r="AM30" s="220"/>
-      <c r="AN30" s="220"/>
-      <c r="AO30" s="220"/>
-      <c r="AP30" s="220"/>
-      <c r="AQ30" s="220"/>
-      <c r="AR30" s="220"/>
-      <c r="AS30" s="220"/>
-      <c r="AT30" s="220"/>
-      <c r="AU30" s="220"/>
-      <c r="AV30" s="220"/>
-      <c r="AW30" s="220"/>
-      <c r="AX30" s="220"/>
-      <c r="AY30" s="220"/>
-      <c r="AZ30" s="220"/>
-      <c r="BA30" s="220"/>
-      <c r="BB30" s="220"/>
-      <c r="BC30" s="220"/>
-      <c r="BD30" s="221"/>
+      <c r="C30" s="152"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="153"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="153"/>
+      <c r="N30" s="153"/>
+      <c r="O30" s="153"/>
+      <c r="P30" s="153"/>
+      <c r="Q30" s="153"/>
+      <c r="R30" s="153"/>
+      <c r="S30" s="153"/>
+      <c r="T30" s="153"/>
+      <c r="U30" s="153"/>
+      <c r="V30" s="153"/>
+      <c r="W30" s="153"/>
+      <c r="X30" s="153"/>
+      <c r="Y30" s="153"/>
+      <c r="Z30" s="153"/>
+      <c r="AA30" s="153"/>
+      <c r="AB30" s="153"/>
+      <c r="AC30" s="153"/>
+      <c r="AD30" s="153"/>
+      <c r="AE30" s="153"/>
+      <c r="AF30" s="153"/>
+      <c r="AG30" s="153"/>
+      <c r="AH30" s="153"/>
+      <c r="AI30" s="153"/>
+      <c r="AJ30" s="153"/>
+      <c r="AK30" s="153"/>
+      <c r="AL30" s="153"/>
+      <c r="AM30" s="153"/>
+      <c r="AN30" s="153"/>
+      <c r="AO30" s="153"/>
+      <c r="AP30" s="153"/>
+      <c r="AQ30" s="153"/>
+      <c r="AR30" s="153"/>
+      <c r="AS30" s="153"/>
+      <c r="AT30" s="153"/>
+      <c r="AU30" s="153"/>
+      <c r="AV30" s="153"/>
+      <c r="AW30" s="153"/>
+      <c r="AX30" s="153"/>
+      <c r="AY30" s="153"/>
+      <c r="AZ30" s="153"/>
+      <c r="BA30" s="153"/>
+      <c r="BB30" s="153"/>
+      <c r="BC30" s="153"/>
+      <c r="BD30" s="154"/>
     </row>
     <row r="31" spans="3:56" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="222"/>
-      <c r="D31" s="223"/>
-      <c r="E31" s="223"/>
-      <c r="F31" s="223"/>
-      <c r="G31" s="223"/>
-      <c r="H31" s="223"/>
-      <c r="I31" s="223"/>
-      <c r="J31" s="223"/>
-      <c r="K31" s="223"/>
-      <c r="L31" s="223"/>
-      <c r="M31" s="223"/>
-      <c r="N31" s="223"/>
-      <c r="O31" s="223"/>
-      <c r="P31" s="223"/>
-      <c r="Q31" s="223"/>
-      <c r="R31" s="223"/>
-      <c r="S31" s="223"/>
-      <c r="T31" s="223"/>
-      <c r="U31" s="223"/>
-      <c r="V31" s="223"/>
-      <c r="W31" s="223"/>
-      <c r="X31" s="223"/>
-      <c r="Y31" s="223"/>
-      <c r="Z31" s="223"/>
-      <c r="AA31" s="223"/>
-      <c r="AB31" s="223"/>
-      <c r="AC31" s="223"/>
-      <c r="AD31" s="223"/>
-      <c r="AE31" s="223"/>
-      <c r="AF31" s="223"/>
-      <c r="AG31" s="223"/>
-      <c r="AH31" s="223"/>
-      <c r="AI31" s="223"/>
-      <c r="AJ31" s="223"/>
-      <c r="AK31" s="223"/>
-      <c r="AL31" s="223"/>
-      <c r="AM31" s="223"/>
-      <c r="AN31" s="223"/>
-      <c r="AO31" s="223"/>
-      <c r="AP31" s="223"/>
-      <c r="AQ31" s="223"/>
-      <c r="AR31" s="223"/>
-      <c r="AS31" s="223"/>
-      <c r="AT31" s="223"/>
-      <c r="AU31" s="223"/>
-      <c r="AV31" s="223"/>
-      <c r="AW31" s="223"/>
-      <c r="AX31" s="223"/>
-      <c r="AY31" s="223"/>
-      <c r="AZ31" s="223"/>
-      <c r="BA31" s="223"/>
-      <c r="BB31" s="223"/>
-      <c r="BC31" s="223"/>
-      <c r="BD31" s="224"/>
+      <c r="C31" s="155"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="156"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="156"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="156"/>
+      <c r="O31" s="156"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="156"/>
+      <c r="R31" s="156"/>
+      <c r="S31" s="156"/>
+      <c r="T31" s="156"/>
+      <c r="U31" s="156"/>
+      <c r="V31" s="156"/>
+      <c r="W31" s="156"/>
+      <c r="X31" s="156"/>
+      <c r="Y31" s="156"/>
+      <c r="Z31" s="156"/>
+      <c r="AA31" s="156"/>
+      <c r="AB31" s="156"/>
+      <c r="AC31" s="156"/>
+      <c r="AD31" s="156"/>
+      <c r="AE31" s="156"/>
+      <c r="AF31" s="156"/>
+      <c r="AG31" s="156"/>
+      <c r="AH31" s="156"/>
+      <c r="AI31" s="156"/>
+      <c r="AJ31" s="156"/>
+      <c r="AK31" s="156"/>
+      <c r="AL31" s="156"/>
+      <c r="AM31" s="156"/>
+      <c r="AN31" s="156"/>
+      <c r="AO31" s="156"/>
+      <c r="AP31" s="156"/>
+      <c r="AQ31" s="156"/>
+      <c r="AR31" s="156"/>
+      <c r="AS31" s="156"/>
+      <c r="AT31" s="156"/>
+      <c r="AU31" s="156"/>
+      <c r="AV31" s="156"/>
+      <c r="AW31" s="156"/>
+      <c r="AX31" s="156"/>
+      <c r="AY31" s="156"/>
+      <c r="AZ31" s="156"/>
+      <c r="BA31" s="156"/>
+      <c r="BB31" s="156"/>
+      <c r="BC31" s="156"/>
+      <c r="BD31" s="157"/>
     </row>
     <row r="32" spans="3:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="52"/>
@@ -5916,7 +6535,8 @@
       <c r="BD35" s="55"/>
     </row>
     <row r="36" spans="3:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="23"/>
+      <c r="C36" s="137"/>
+      <c r="D36" s="138"/>
       <c r="BD36" s="25"/>
     </row>
     <row r="37" spans="3:56" ht="36.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -6204,290 +6824,290 @@
       <c r="BD54" s="55"/>
     </row>
     <row r="55" spans="3:62" ht="12.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="225" t="s">
+      <c r="C55" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="226"/>
-      <c r="E55" s="226"/>
-      <c r="F55" s="226"/>
-      <c r="G55" s="226"/>
-      <c r="H55" s="226"/>
-      <c r="I55" s="226"/>
-      <c r="J55" s="226"/>
-      <c r="K55" s="226"/>
-      <c r="L55" s="226"/>
-      <c r="M55" s="226"/>
-      <c r="N55" s="226"/>
-      <c r="O55" s="226"/>
-      <c r="P55" s="226"/>
-      <c r="Q55" s="226"/>
-      <c r="R55" s="226"/>
-      <c r="S55" s="226"/>
-      <c r="T55" s="226"/>
-      <c r="U55" s="226"/>
-      <c r="V55" s="226"/>
-      <c r="W55" s="226"/>
-      <c r="X55" s="226"/>
-      <c r="Y55" s="226"/>
-      <c r="Z55" s="226"/>
-      <c r="AA55" s="226"/>
-      <c r="AB55" s="226"/>
-      <c r="AC55" s="226"/>
-      <c r="AD55" s="226"/>
-      <c r="AE55" s="226"/>
-      <c r="AF55" s="226"/>
-      <c r="AG55" s="226"/>
-      <c r="AH55" s="226"/>
-      <c r="AI55" s="226"/>
-      <c r="AJ55" s="226"/>
-      <c r="AK55" s="226"/>
-      <c r="AL55" s="226"/>
-      <c r="AM55" s="226"/>
-      <c r="AN55" s="226"/>
-      <c r="AO55" s="226"/>
-      <c r="AP55" s="226"/>
-      <c r="AQ55" s="226"/>
-      <c r="AR55" s="226"/>
-      <c r="AS55" s="226"/>
-      <c r="AT55" s="226"/>
-      <c r="AU55" s="226"/>
-      <c r="AV55" s="226"/>
-      <c r="AW55" s="226"/>
-      <c r="AX55" s="226"/>
-      <c r="AY55" s="226"/>
-      <c r="AZ55" s="226"/>
-      <c r="BA55" s="226"/>
-      <c r="BB55" s="226"/>
-      <c r="BC55" s="226"/>
-      <c r="BD55" s="227"/>
+      <c r="D55" s="159"/>
+      <c r="E55" s="159"/>
+      <c r="F55" s="159"/>
+      <c r="G55" s="159"/>
+      <c r="H55" s="159"/>
+      <c r="I55" s="159"/>
+      <c r="J55" s="159"/>
+      <c r="K55" s="159"/>
+      <c r="L55" s="159"/>
+      <c r="M55" s="159"/>
+      <c r="N55" s="159"/>
+      <c r="O55" s="159"/>
+      <c r="P55" s="159"/>
+      <c r="Q55" s="159"/>
+      <c r="R55" s="159"/>
+      <c r="S55" s="159"/>
+      <c r="T55" s="159"/>
+      <c r="U55" s="159"/>
+      <c r="V55" s="159"/>
+      <c r="W55" s="159"/>
+      <c r="X55" s="159"/>
+      <c r="Y55" s="159"/>
+      <c r="Z55" s="159"/>
+      <c r="AA55" s="159"/>
+      <c r="AB55" s="159"/>
+      <c r="AC55" s="159"/>
+      <c r="AD55" s="159"/>
+      <c r="AE55" s="159"/>
+      <c r="AF55" s="159"/>
+      <c r="AG55" s="159"/>
+      <c r="AH55" s="159"/>
+      <c r="AI55" s="159"/>
+      <c r="AJ55" s="159"/>
+      <c r="AK55" s="159"/>
+      <c r="AL55" s="159"/>
+      <c r="AM55" s="159"/>
+      <c r="AN55" s="159"/>
+      <c r="AO55" s="159"/>
+      <c r="AP55" s="159"/>
+      <c r="AQ55" s="159"/>
+      <c r="AR55" s="159"/>
+      <c r="AS55" s="159"/>
+      <c r="AT55" s="159"/>
+      <c r="AU55" s="159"/>
+      <c r="AV55" s="159"/>
+      <c r="AW55" s="159"/>
+      <c r="AX55" s="159"/>
+      <c r="AY55" s="159"/>
+      <c r="AZ55" s="159"/>
+      <c r="BA55" s="159"/>
+      <c r="BB55" s="159"/>
+      <c r="BC55" s="159"/>
+      <c r="BD55" s="160"/>
     </row>
     <row r="56" spans="3:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="228"/>
-      <c r="D56" s="229"/>
-      <c r="E56" s="229"/>
-      <c r="F56" s="229"/>
-      <c r="G56" s="229"/>
-      <c r="H56" s="229"/>
-      <c r="I56" s="229"/>
-      <c r="J56" s="229"/>
-      <c r="K56" s="229"/>
-      <c r="L56" s="229"/>
-      <c r="M56" s="229"/>
-      <c r="N56" s="229"/>
-      <c r="O56" s="229"/>
-      <c r="P56" s="229"/>
-      <c r="Q56" s="229"/>
-      <c r="R56" s="229"/>
-      <c r="S56" s="229"/>
-      <c r="T56" s="229"/>
-      <c r="U56" s="229"/>
-      <c r="V56" s="229"/>
-      <c r="W56" s="229"/>
-      <c r="X56" s="229"/>
-      <c r="Y56" s="229"/>
-      <c r="Z56" s="229"/>
-      <c r="AA56" s="229"/>
-      <c r="AB56" s="229"/>
-      <c r="AC56" s="229"/>
-      <c r="AD56" s="229"/>
-      <c r="AE56" s="229"/>
-      <c r="AF56" s="229"/>
-      <c r="AG56" s="229"/>
-      <c r="AH56" s="229"/>
-      <c r="AI56" s="229"/>
-      <c r="AJ56" s="229"/>
-      <c r="AK56" s="229"/>
-      <c r="AL56" s="229"/>
-      <c r="AM56" s="229"/>
-      <c r="AN56" s="229"/>
-      <c r="AO56" s="229"/>
-      <c r="AP56" s="229"/>
-      <c r="AQ56" s="229"/>
-      <c r="AR56" s="229"/>
-      <c r="AS56" s="229"/>
-      <c r="AT56" s="229"/>
-      <c r="AU56" s="229"/>
-      <c r="AV56" s="229"/>
-      <c r="AW56" s="229"/>
-      <c r="AX56" s="229"/>
-      <c r="AY56" s="229"/>
-      <c r="AZ56" s="229"/>
-      <c r="BA56" s="229"/>
-      <c r="BB56" s="229"/>
-      <c r="BC56" s="229"/>
-      <c r="BD56" s="230"/>
+      <c r="C56" s="161"/>
+      <c r="D56" s="162"/>
+      <c r="E56" s="162"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="162"/>
+      <c r="K56" s="162"/>
+      <c r="L56" s="162"/>
+      <c r="M56" s="162"/>
+      <c r="N56" s="162"/>
+      <c r="O56" s="162"/>
+      <c r="P56" s="162"/>
+      <c r="Q56" s="162"/>
+      <c r="R56" s="162"/>
+      <c r="S56" s="162"/>
+      <c r="T56" s="162"/>
+      <c r="U56" s="162"/>
+      <c r="V56" s="162"/>
+      <c r="W56" s="162"/>
+      <c r="X56" s="162"/>
+      <c r="Y56" s="162"/>
+      <c r="Z56" s="162"/>
+      <c r="AA56" s="162"/>
+      <c r="AB56" s="162"/>
+      <c r="AC56" s="162"/>
+      <c r="AD56" s="162"/>
+      <c r="AE56" s="162"/>
+      <c r="AF56" s="162"/>
+      <c r="AG56" s="162"/>
+      <c r="AH56" s="162"/>
+      <c r="AI56" s="162"/>
+      <c r="AJ56" s="162"/>
+      <c r="AK56" s="162"/>
+      <c r="AL56" s="162"/>
+      <c r="AM56" s="162"/>
+      <c r="AN56" s="162"/>
+      <c r="AO56" s="162"/>
+      <c r="AP56" s="162"/>
+      <c r="AQ56" s="162"/>
+      <c r="AR56" s="162"/>
+      <c r="AS56" s="162"/>
+      <c r="AT56" s="162"/>
+      <c r="AU56" s="162"/>
+      <c r="AV56" s="162"/>
+      <c r="AW56" s="162"/>
+      <c r="AX56" s="162"/>
+      <c r="AY56" s="162"/>
+      <c r="AZ56" s="162"/>
+      <c r="BA56" s="162"/>
+      <c r="BB56" s="162"/>
+      <c r="BC56" s="162"/>
+      <c r="BD56" s="163"/>
     </row>
     <row r="57" spans="3:62" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="231"/>
-      <c r="D57" s="232"/>
-      <c r="E57" s="232"/>
-      <c r="F57" s="232"/>
-      <c r="G57" s="232"/>
-      <c r="H57" s="232"/>
-      <c r="I57" s="232"/>
-      <c r="J57" s="232"/>
-      <c r="K57" s="232"/>
-      <c r="L57" s="232"/>
-      <c r="M57" s="232"/>
-      <c r="N57" s="232"/>
-      <c r="O57" s="232"/>
-      <c r="P57" s="232"/>
-      <c r="Q57" s="232"/>
-      <c r="R57" s="232"/>
-      <c r="S57" s="232"/>
-      <c r="T57" s="232"/>
-      <c r="U57" s="232"/>
-      <c r="V57" s="232"/>
-      <c r="W57" s="232"/>
-      <c r="X57" s="232"/>
-      <c r="Y57" s="232"/>
-      <c r="Z57" s="232"/>
-      <c r="AA57" s="232"/>
-      <c r="AB57" s="232"/>
-      <c r="AC57" s="232"/>
-      <c r="AD57" s="232"/>
-      <c r="AE57" s="232"/>
-      <c r="AF57" s="232"/>
-      <c r="AG57" s="232"/>
-      <c r="AH57" s="232"/>
-      <c r="AI57" s="232"/>
-      <c r="AJ57" s="232"/>
-      <c r="AK57" s="232"/>
-      <c r="AL57" s="232"/>
-      <c r="AM57" s="232"/>
-      <c r="AN57" s="232"/>
-      <c r="AO57" s="232"/>
-      <c r="AP57" s="232"/>
-      <c r="AQ57" s="232"/>
-      <c r="AR57" s="232"/>
-      <c r="AS57" s="232"/>
-      <c r="AT57" s="232"/>
-      <c r="AU57" s="232"/>
-      <c r="AV57" s="232"/>
-      <c r="AW57" s="232"/>
-      <c r="AX57" s="232"/>
-      <c r="AY57" s="232"/>
-      <c r="AZ57" s="232"/>
-      <c r="BA57" s="232"/>
-      <c r="BB57" s="232"/>
-      <c r="BC57" s="232"/>
-      <c r="BD57" s="233"/>
+      <c r="C57" s="164"/>
+      <c r="D57" s="165"/>
+      <c r="E57" s="165"/>
+      <c r="F57" s="165"/>
+      <c r="G57" s="165"/>
+      <c r="H57" s="165"/>
+      <c r="I57" s="165"/>
+      <c r="J57" s="165"/>
+      <c r="K57" s="165"/>
+      <c r="L57" s="165"/>
+      <c r="M57" s="165"/>
+      <c r="N57" s="165"/>
+      <c r="O57" s="165"/>
+      <c r="P57" s="165"/>
+      <c r="Q57" s="165"/>
+      <c r="R57" s="165"/>
+      <c r="S57" s="165"/>
+      <c r="T57" s="165"/>
+      <c r="U57" s="165"/>
+      <c r="V57" s="165"/>
+      <c r="W57" s="165"/>
+      <c r="X57" s="165"/>
+      <c r="Y57" s="165"/>
+      <c r="Z57" s="165"/>
+      <c r="AA57" s="165"/>
+      <c r="AB57" s="165"/>
+      <c r="AC57" s="165"/>
+      <c r="AD57" s="165"/>
+      <c r="AE57" s="165"/>
+      <c r="AF57" s="165"/>
+      <c r="AG57" s="165"/>
+      <c r="AH57" s="165"/>
+      <c r="AI57" s="165"/>
+      <c r="AJ57" s="165"/>
+      <c r="AK57" s="165"/>
+      <c r="AL57" s="165"/>
+      <c r="AM57" s="165"/>
+      <c r="AN57" s="165"/>
+      <c r="AO57" s="165"/>
+      <c r="AP57" s="165"/>
+      <c r="AQ57" s="165"/>
+      <c r="AR57" s="165"/>
+      <c r="AS57" s="165"/>
+      <c r="AT57" s="165"/>
+      <c r="AU57" s="165"/>
+      <c r="AV57" s="165"/>
+      <c r="AW57" s="165"/>
+      <c r="AX57" s="165"/>
+      <c r="AY57" s="165"/>
+      <c r="AZ57" s="165"/>
+      <c r="BA57" s="165"/>
+      <c r="BB57" s="165"/>
+      <c r="BC57" s="165"/>
+      <c r="BD57" s="166"/>
     </row>
     <row r="58" spans="3:62" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="188" t="s">
+      <c r="C58" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="D58" s="189"/>
-      <c r="E58" s="189"/>
-      <c r="F58" s="189"/>
-      <c r="G58" s="189"/>
-      <c r="H58" s="189"/>
-      <c r="I58" s="189"/>
-      <c r="J58" s="189"/>
-      <c r="K58" s="189"/>
-      <c r="L58" s="189"/>
-      <c r="M58" s="189"/>
-      <c r="N58" s="189"/>
-      <c r="O58" s="189"/>
-      <c r="P58" s="189"/>
-      <c r="Q58" s="189"/>
-      <c r="R58" s="189"/>
-      <c r="S58" s="189"/>
-      <c r="T58" s="189"/>
-      <c r="U58" s="189"/>
-      <c r="V58" s="189"/>
-      <c r="W58" s="189"/>
-      <c r="X58" s="189"/>
-      <c r="Y58" s="189"/>
-      <c r="Z58" s="189"/>
-      <c r="AA58" s="189"/>
-      <c r="AB58" s="189"/>
-      <c r="AC58" s="189"/>
-      <c r="AD58" s="189"/>
-      <c r="AE58" s="189"/>
-      <c r="AF58" s="189"/>
-      <c r="AG58" s="189"/>
-      <c r="AH58" s="189"/>
-      <c r="AI58" s="189"/>
-      <c r="AJ58" s="189"/>
-      <c r="AK58" s="189"/>
-      <c r="AL58" s="189"/>
-      <c r="AM58" s="189"/>
-      <c r="AN58" s="189"/>
-      <c r="AO58" s="189"/>
-      <c r="AP58" s="189"/>
-      <c r="AQ58" s="189"/>
-      <c r="AR58" s="189"/>
-      <c r="AS58" s="189"/>
-      <c r="AT58" s="189"/>
-      <c r="AU58" s="189"/>
-      <c r="AV58" s="189"/>
-      <c r="AW58" s="189"/>
-      <c r="AX58" s="189"/>
-      <c r="AY58" s="189"/>
-      <c r="AZ58" s="189"/>
-      <c r="BA58" s="189"/>
-      <c r="BB58" s="189"/>
-      <c r="BC58" s="189"/>
-      <c r="BD58" s="234"/>
+      <c r="D58" s="168"/>
+      <c r="E58" s="168"/>
+      <c r="F58" s="168"/>
+      <c r="G58" s="168"/>
+      <c r="H58" s="168"/>
+      <c r="I58" s="168"/>
+      <c r="J58" s="168"/>
+      <c r="K58" s="168"/>
+      <c r="L58" s="168"/>
+      <c r="M58" s="168"/>
+      <c r="N58" s="168"/>
+      <c r="O58" s="168"/>
+      <c r="P58" s="168"/>
+      <c r="Q58" s="168"/>
+      <c r="R58" s="168"/>
+      <c r="S58" s="168"/>
+      <c r="T58" s="168"/>
+      <c r="U58" s="168"/>
+      <c r="V58" s="168"/>
+      <c r="W58" s="168"/>
+      <c r="X58" s="168"/>
+      <c r="Y58" s="168"/>
+      <c r="Z58" s="168"/>
+      <c r="AA58" s="168"/>
+      <c r="AB58" s="168"/>
+      <c r="AC58" s="168"/>
+      <c r="AD58" s="168"/>
+      <c r="AE58" s="168"/>
+      <c r="AF58" s="168"/>
+      <c r="AG58" s="168"/>
+      <c r="AH58" s="168"/>
+      <c r="AI58" s="168"/>
+      <c r="AJ58" s="168"/>
+      <c r="AK58" s="168"/>
+      <c r="AL58" s="168"/>
+      <c r="AM58" s="168"/>
+      <c r="AN58" s="168"/>
+      <c r="AO58" s="168"/>
+      <c r="AP58" s="168"/>
+      <c r="AQ58" s="168"/>
+      <c r="AR58" s="168"/>
+      <c r="AS58" s="168"/>
+      <c r="AT58" s="168"/>
+      <c r="AU58" s="168"/>
+      <c r="AV58" s="168"/>
+      <c r="AW58" s="168"/>
+      <c r="AX58" s="168"/>
+      <c r="AY58" s="168"/>
+      <c r="AZ58" s="168"/>
+      <c r="BA58" s="168"/>
+      <c r="BB58" s="168"/>
+      <c r="BC58" s="168"/>
+      <c r="BD58" s="169"/>
     </row>
     <row r="59" spans="3:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="235" t="s">
+      <c r="C59" s="170" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="236"/>
-      <c r="E59" s="236"/>
-      <c r="F59" s="236"/>
-      <c r="G59" s="236"/>
-      <c r="H59" s="236"/>
-      <c r="I59" s="236"/>
-      <c r="J59" s="236"/>
-      <c r="K59" s="236"/>
-      <c r="L59" s="236"/>
-      <c r="M59" s="236"/>
-      <c r="N59" s="236"/>
-      <c r="O59" s="236"/>
-      <c r="P59" s="236"/>
-      <c r="Q59" s="236"/>
-      <c r="R59" s="236"/>
-      <c r="S59" s="236"/>
-      <c r="T59" s="236"/>
-      <c r="U59" s="236"/>
-      <c r="V59" s="236"/>
-      <c r="W59" s="236"/>
-      <c r="X59" s="236"/>
-      <c r="Y59" s="236"/>
-      <c r="Z59" s="236"/>
-      <c r="AA59" s="236"/>
-      <c r="AB59" s="236"/>
-      <c r="AC59" s="236"/>
-      <c r="AD59" s="236"/>
-      <c r="AE59" s="236"/>
-      <c r="AF59" s="236"/>
-      <c r="AG59" s="236"/>
-      <c r="AH59" s="236"/>
-      <c r="AI59" s="236"/>
-      <c r="AJ59" s="236"/>
-      <c r="AK59" s="236"/>
-      <c r="AL59" s="236"/>
-      <c r="AM59" s="236"/>
-      <c r="AN59" s="236"/>
-      <c r="AO59" s="236"/>
-      <c r="AP59" s="236"/>
-      <c r="AQ59" s="236"/>
-      <c r="AR59" s="236"/>
-      <c r="AS59" s="236"/>
-      <c r="AT59" s="236"/>
-      <c r="AU59" s="236"/>
-      <c r="AV59" s="236"/>
-      <c r="AW59" s="236"/>
-      <c r="AX59" s="236"/>
-      <c r="AY59" s="236"/>
-      <c r="AZ59" s="236"/>
-      <c r="BA59" s="236"/>
-      <c r="BB59" s="236"/>
-      <c r="BC59" s="236"/>
-      <c r="BD59" s="237"/>
+      <c r="D59" s="171"/>
+      <c r="E59" s="171"/>
+      <c r="F59" s="171"/>
+      <c r="G59" s="171"/>
+      <c r="H59" s="171"/>
+      <c r="I59" s="171"/>
+      <c r="J59" s="171"/>
+      <c r="K59" s="171"/>
+      <c r="L59" s="171"/>
+      <c r="M59" s="171"/>
+      <c r="N59" s="171"/>
+      <c r="O59" s="171"/>
+      <c r="P59" s="171"/>
+      <c r="Q59" s="171"/>
+      <c r="R59" s="171"/>
+      <c r="S59" s="171"/>
+      <c r="T59" s="171"/>
+      <c r="U59" s="171"/>
+      <c r="V59" s="171"/>
+      <c r="W59" s="171"/>
+      <c r="X59" s="171"/>
+      <c r="Y59" s="171"/>
+      <c r="Z59" s="171"/>
+      <c r="AA59" s="171"/>
+      <c r="AB59" s="171"/>
+      <c r="AC59" s="171"/>
+      <c r="AD59" s="171"/>
+      <c r="AE59" s="171"/>
+      <c r="AF59" s="171"/>
+      <c r="AG59" s="171"/>
+      <c r="AH59" s="171"/>
+      <c r="AI59" s="171"/>
+      <c r="AJ59" s="171"/>
+      <c r="AK59" s="171"/>
+      <c r="AL59" s="171"/>
+      <c r="AM59" s="171"/>
+      <c r="AN59" s="171"/>
+      <c r="AO59" s="171"/>
+      <c r="AP59" s="171"/>
+      <c r="AQ59" s="171"/>
+      <c r="AR59" s="171"/>
+      <c r="AS59" s="171"/>
+      <c r="AT59" s="171"/>
+      <c r="AU59" s="171"/>
+      <c r="AV59" s="171"/>
+      <c r="AW59" s="171"/>
+      <c r="AX59" s="171"/>
+      <c r="AY59" s="171"/>
+      <c r="AZ59" s="171"/>
+      <c r="BA59" s="171"/>
+      <c r="BB59" s="171"/>
+      <c r="BC59" s="171"/>
+      <c r="BD59" s="172"/>
     </row>
     <row r="60" spans="3:62" ht="4.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C60" s="63"/>
@@ -6547,114 +7167,114 @@
     </row>
     <row r="61" spans="3:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="66"/>
-      <c r="D61" s="187" t="s">
+      <c r="D61" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="187"/>
-      <c r="F61" s="187"/>
+      <c r="E61" s="173"/>
+      <c r="F61" s="173"/>
       <c r="G61" s="68"/>
-      <c r="H61" s="200"/>
-      <c r="I61" s="201"/>
-      <c r="J61" s="202"/>
+      <c r="H61" s="174"/>
+      <c r="I61" s="175"/>
+      <c r="J61" s="176"/>
       <c r="K61" s="68"/>
       <c r="L61" s="68"/>
       <c r="M61" s="68"/>
-      <c r="N61" s="187" t="s">
+      <c r="N61" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="O61" s="187"/>
-      <c r="P61" s="187"/>
+      <c r="O61" s="173"/>
+      <c r="P61" s="173"/>
       <c r="Q61" s="68"/>
-      <c r="R61" s="181"/>
-      <c r="S61" s="182"/>
-      <c r="T61" s="183"/>
+      <c r="R61" s="180"/>
+      <c r="S61" s="181"/>
+      <c r="T61" s="182"/>
       <c r="U61" s="66"/>
       <c r="V61" s="68"/>
-      <c r="W61" s="212" t="s">
+      <c r="W61" s="186" t="s">
         <v>47</v>
       </c>
-      <c r="X61" s="212"/>
-      <c r="Y61" s="212"/>
-      <c r="Z61" s="212"/>
-      <c r="AA61" s="212"/>
-      <c r="AB61" s="212"/>
-      <c r="AC61" s="212"/>
-      <c r="AD61" s="212"/>
-      <c r="AE61" s="212"/>
-      <c r="AF61" s="212"/>
-      <c r="AG61" s="212"/>
-      <c r="AH61" s="212"/>
+      <c r="X61" s="186"/>
+      <c r="Y61" s="186"/>
+      <c r="Z61" s="186"/>
+      <c r="AA61" s="186"/>
+      <c r="AB61" s="186"/>
+      <c r="AC61" s="186"/>
+      <c r="AD61" s="186"/>
+      <c r="AE61" s="186"/>
+      <c r="AF61" s="186"/>
+      <c r="AG61" s="186"/>
+      <c r="AH61" s="186"/>
       <c r="AI61" s="70"/>
-      <c r="AJ61" s="187" t="s">
+      <c r="AJ61" s="173" t="s">
         <v>48</v>
       </c>
-      <c r="AK61" s="238"/>
-      <c r="AL61" s="181"/>
-      <c r="AM61" s="183"/>
+      <c r="AK61" s="187"/>
+      <c r="AL61" s="180"/>
+      <c r="AM61" s="182"/>
       <c r="AN61" s="68"/>
-      <c r="AO61" s="187" t="s">
+      <c r="AO61" s="173" t="s">
         <v>49</v>
       </c>
-      <c r="AP61" s="187"/>
-      <c r="AQ61" s="181"/>
-      <c r="AR61" s="183"/>
-      <c r="AT61" s="214" t="s">
+      <c r="AP61" s="173"/>
+      <c r="AQ61" s="180"/>
+      <c r="AR61" s="182"/>
+      <c r="AT61" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="AU61" s="214"/>
-      <c r="AV61" s="214"/>
-      <c r="AW61" s="214"/>
-      <c r="AX61" s="214"/>
-      <c r="AY61" s="214"/>
-      <c r="AZ61" s="214"/>
-      <c r="BA61" s="214"/>
-      <c r="BB61" s="214"/>
-      <c r="BC61" s="214"/>
+      <c r="AU61" s="188"/>
+      <c r="AV61" s="188"/>
+      <c r="AW61" s="188"/>
+      <c r="AX61" s="188"/>
+      <c r="AY61" s="188"/>
+      <c r="AZ61" s="188"/>
+      <c r="BA61" s="188"/>
+      <c r="BB61" s="188"/>
+      <c r="BC61" s="188"/>
       <c r="BD61" s="72"/>
     </row>
     <row r="62" spans="3:62" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C62" s="66"/>
-      <c r="D62" s="187"/>
-      <c r="E62" s="187"/>
-      <c r="F62" s="187"/>
+      <c r="D62" s="173"/>
+      <c r="E62" s="173"/>
+      <c r="F62" s="173"/>
       <c r="G62" s="68"/>
-      <c r="H62" s="203"/>
-      <c r="I62" s="204"/>
-      <c r="J62" s="205"/>
+      <c r="H62" s="177"/>
+      <c r="I62" s="178"/>
+      <c r="J62" s="179"/>
       <c r="K62" s="68"/>
       <c r="L62" s="68"/>
       <c r="M62" s="68"/>
-      <c r="N62" s="187"/>
-      <c r="O62" s="187"/>
-      <c r="P62" s="187"/>
+      <c r="N62" s="173"/>
+      <c r="O62" s="173"/>
+      <c r="P62" s="173"/>
       <c r="Q62" s="68"/>
-      <c r="R62" s="184"/>
-      <c r="S62" s="185"/>
-      <c r="T62" s="186"/>
+      <c r="R62" s="183"/>
+      <c r="S62" s="184"/>
+      <c r="T62" s="185"/>
       <c r="U62" s="66"/>
       <c r="V62" s="68"/>
-      <c r="W62" s="212"/>
-      <c r="X62" s="212"/>
-      <c r="Y62" s="212"/>
-      <c r="Z62" s="212"/>
-      <c r="AA62" s="212"/>
-      <c r="AB62" s="212"/>
-      <c r="AC62" s="212"/>
-      <c r="AD62" s="212"/>
-      <c r="AE62" s="212"/>
-      <c r="AF62" s="212"/>
-      <c r="AG62" s="212"/>
-      <c r="AH62" s="212"/>
+      <c r="W62" s="186"/>
+      <c r="X62" s="186"/>
+      <c r="Y62" s="186"/>
+      <c r="Z62" s="186"/>
+      <c r="AA62" s="186"/>
+      <c r="AB62" s="186"/>
+      <c r="AC62" s="186"/>
+      <c r="AD62" s="186"/>
+      <c r="AE62" s="186"/>
+      <c r="AF62" s="186"/>
+      <c r="AG62" s="186"/>
+      <c r="AH62" s="186"/>
       <c r="AI62" s="70"/>
-      <c r="AJ62" s="187"/>
-      <c r="AK62" s="238"/>
-      <c r="AL62" s="184"/>
-      <c r="AM62" s="186"/>
+      <c r="AJ62" s="173"/>
+      <c r="AK62" s="187"/>
+      <c r="AL62" s="183"/>
+      <c r="AM62" s="185"/>
       <c r="AN62" s="68"/>
-      <c r="AO62" s="187"/>
-      <c r="AP62" s="187"/>
-      <c r="AQ62" s="184"/>
-      <c r="AR62" s="186"/>
+      <c r="AO62" s="173"/>
+      <c r="AP62" s="173"/>
+      <c r="AQ62" s="183"/>
+      <c r="AR62" s="185"/>
       <c r="AT62" s="73"/>
       <c r="AU62" s="73"/>
       <c r="AV62" s="73"/>
@@ -6724,62 +7344,62 @@
       <c r="BD63" s="72"/>
     </row>
     <row r="64" spans="3:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="215" t="s">
+      <c r="C64" s="189" t="s">
         <v>51</v>
       </c>
-      <c r="D64" s="216"/>
-      <c r="E64" s="216"/>
-      <c r="F64" s="216"/>
-      <c r="G64" s="216"/>
-      <c r="H64" s="216"/>
-      <c r="I64" s="216"/>
-      <c r="J64" s="216"/>
-      <c r="K64" s="216"/>
-      <c r="L64" s="216"/>
-      <c r="M64" s="216"/>
-      <c r="N64" s="216"/>
-      <c r="O64" s="216"/>
-      <c r="P64" s="216"/>
-      <c r="Q64" s="216"/>
-      <c r="R64" s="216"/>
-      <c r="S64" s="216"/>
-      <c r="T64" s="216"/>
-      <c r="U64" s="216"/>
-      <c r="V64" s="216"/>
-      <c r="W64" s="216"/>
-      <c r="X64" s="216"/>
-      <c r="Y64" s="216"/>
-      <c r="Z64" s="216"/>
-      <c r="AA64" s="216"/>
-      <c r="AB64" s="216"/>
-      <c r="AC64" s="216"/>
-      <c r="AD64" s="216"/>
-      <c r="AE64" s="216"/>
-      <c r="AF64" s="216"/>
-      <c r="AG64" s="216"/>
-      <c r="AH64" s="216"/>
-      <c r="AI64" s="216"/>
-      <c r="AJ64" s="216"/>
-      <c r="AK64" s="216"/>
-      <c r="AL64" s="216"/>
-      <c r="AM64" s="216"/>
-      <c r="AN64" s="216"/>
-      <c r="AO64" s="216"/>
-      <c r="AP64" s="216"/>
-      <c r="AQ64" s="216"/>
-      <c r="AR64" s="216"/>
-      <c r="AS64" s="216"/>
-      <c r="AT64" s="216"/>
-      <c r="AU64" s="216"/>
-      <c r="AV64" s="216"/>
-      <c r="AW64" s="216"/>
-      <c r="AX64" s="216"/>
-      <c r="AY64" s="216"/>
-      <c r="AZ64" s="216"/>
-      <c r="BA64" s="216"/>
-      <c r="BB64" s="216"/>
-      <c r="BC64" s="216"/>
-      <c r="BD64" s="217"/>
+      <c r="D64" s="190"/>
+      <c r="E64" s="190"/>
+      <c r="F64" s="190"/>
+      <c r="G64" s="190"/>
+      <c r="H64" s="190"/>
+      <c r="I64" s="190"/>
+      <c r="J64" s="190"/>
+      <c r="K64" s="190"/>
+      <c r="L64" s="190"/>
+      <c r="M64" s="190"/>
+      <c r="N64" s="190"/>
+      <c r="O64" s="190"/>
+      <c r="P64" s="190"/>
+      <c r="Q64" s="190"/>
+      <c r="R64" s="190"/>
+      <c r="S64" s="190"/>
+      <c r="T64" s="190"/>
+      <c r="U64" s="190"/>
+      <c r="V64" s="190"/>
+      <c r="W64" s="190"/>
+      <c r="X64" s="190"/>
+      <c r="Y64" s="190"/>
+      <c r="Z64" s="190"/>
+      <c r="AA64" s="190"/>
+      <c r="AB64" s="190"/>
+      <c r="AC64" s="190"/>
+      <c r="AD64" s="190"/>
+      <c r="AE64" s="190"/>
+      <c r="AF64" s="190"/>
+      <c r="AG64" s="190"/>
+      <c r="AH64" s="190"/>
+      <c r="AI64" s="190"/>
+      <c r="AJ64" s="190"/>
+      <c r="AK64" s="190"/>
+      <c r="AL64" s="190"/>
+      <c r="AM64" s="190"/>
+      <c r="AN64" s="190"/>
+      <c r="AO64" s="190"/>
+      <c r="AP64" s="190"/>
+      <c r="AQ64" s="190"/>
+      <c r="AR64" s="190"/>
+      <c r="AS64" s="190"/>
+      <c r="AT64" s="190"/>
+      <c r="AU64" s="190"/>
+      <c r="AV64" s="190"/>
+      <c r="AW64" s="190"/>
+      <c r="AX64" s="190"/>
+      <c r="AY64" s="190"/>
+      <c r="AZ64" s="190"/>
+      <c r="BA64" s="190"/>
+      <c r="BB64" s="190"/>
+      <c r="BC64" s="190"/>
+      <c r="BD64" s="191"/>
       <c r="BJ64" s="70"/>
     </row>
     <row r="65" spans="3:56" ht="4.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6816,144 +7436,144 @@
       <c r="AG65" s="64"/>
       <c r="AH65" s="64"/>
       <c r="AI65" s="64"/>
-      <c r="AJ65" s="218"/>
-      <c r="AK65" s="218"/>
-      <c r="AL65" s="218"/>
-      <c r="AM65" s="218"/>
-      <c r="AN65" s="218"/>
-      <c r="AO65" s="218"/>
-      <c r="AP65" s="218"/>
-      <c r="AQ65" s="218"/>
-      <c r="AR65" s="218"/>
-      <c r="AS65" s="218"/>
-      <c r="AT65" s="218"/>
-      <c r="AU65" s="218"/>
-      <c r="AV65" s="218"/>
-      <c r="AW65" s="218"/>
-      <c r="AX65" s="218"/>
-      <c r="AY65" s="218"/>
-      <c r="AZ65" s="218"/>
-      <c r="BA65" s="218"/>
-      <c r="BB65" s="218"/>
-      <c r="BC65" s="218"/>
+      <c r="AJ65" s="192"/>
+      <c r="AK65" s="192"/>
+      <c r="AL65" s="192"/>
+      <c r="AM65" s="192"/>
+      <c r="AN65" s="192"/>
+      <c r="AO65" s="192"/>
+      <c r="AP65" s="192"/>
+      <c r="AQ65" s="192"/>
+      <c r="AR65" s="192"/>
+      <c r="AS65" s="192"/>
+      <c r="AT65" s="192"/>
+      <c r="AU65" s="192"/>
+      <c r="AV65" s="192"/>
+      <c r="AW65" s="192"/>
+      <c r="AX65" s="192"/>
+      <c r="AY65" s="192"/>
+      <c r="AZ65" s="192"/>
+      <c r="BA65" s="192"/>
+      <c r="BB65" s="192"/>
+      <c r="BC65" s="192"/>
       <c r="BD65" s="65"/>
     </row>
     <row r="66" spans="3:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="66"/>
-      <c r="D66" s="187" t="s">
+      <c r="D66" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="E66" s="187"/>
-      <c r="F66" s="187"/>
+      <c r="E66" s="173"/>
+      <c r="F66" s="173"/>
       <c r="G66" s="68"/>
-      <c r="H66" s="181"/>
-      <c r="I66" s="182"/>
-      <c r="J66" s="183"/>
+      <c r="H66" s="180"/>
+      <c r="I66" s="181"/>
+      <c r="J66" s="182"/>
       <c r="K66" s="68"/>
       <c r="L66" s="68"/>
       <c r="M66" s="68"/>
-      <c r="N66" s="187" t="s">
+      <c r="N66" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="187"/>
-      <c r="P66" s="187"/>
+      <c r="O66" s="173"/>
+      <c r="P66" s="173"/>
       <c r="Q66" s="68"/>
-      <c r="R66" s="200"/>
-      <c r="S66" s="201"/>
-      <c r="T66" s="202"/>
+      <c r="R66" s="174"/>
+      <c r="S66" s="175"/>
+      <c r="T66" s="176"/>
       <c r="U66" s="66"/>
       <c r="V66" s="68"/>
-      <c r="W66" s="212" t="s">
+      <c r="W66" s="186" t="s">
         <v>52</v>
       </c>
-      <c r="X66" s="212"/>
-      <c r="Y66" s="212"/>
-      <c r="Z66" s="212"/>
-      <c r="AA66" s="212"/>
-      <c r="AB66" s="212"/>
-      <c r="AC66" s="212"/>
-      <c r="AD66" s="212"/>
-      <c r="AE66" s="212"/>
-      <c r="AF66" s="212"/>
-      <c r="AG66" s="212"/>
-      <c r="AH66" s="212"/>
+      <c r="X66" s="186"/>
+      <c r="Y66" s="186"/>
+      <c r="Z66" s="186"/>
+      <c r="AA66" s="186"/>
+      <c r="AB66" s="186"/>
+      <c r="AC66" s="186"/>
+      <c r="AD66" s="186"/>
+      <c r="AE66" s="186"/>
+      <c r="AF66" s="186"/>
+      <c r="AG66" s="186"/>
+      <c r="AH66" s="186"/>
       <c r="AI66" s="70"/>
-      <c r="AJ66" s="198"/>
-      <c r="AK66" s="198"/>
-      <c r="AL66" s="198"/>
-      <c r="AM66" s="198"/>
-      <c r="AN66" s="198"/>
-      <c r="AO66" s="198"/>
-      <c r="AP66" s="198"/>
-      <c r="AQ66" s="198"/>
-      <c r="AR66" s="198"/>
-      <c r="AS66" s="198"/>
-      <c r="AT66" s="198"/>
-      <c r="AU66" s="198"/>
-      <c r="AV66" s="198"/>
-      <c r="AW66" s="198"/>
-      <c r="AX66" s="198"/>
-      <c r="AY66" s="198"/>
-      <c r="AZ66" s="198"/>
-      <c r="BA66" s="198"/>
-      <c r="BB66" s="198"/>
-      <c r="BC66" s="198"/>
+      <c r="AJ66" s="193"/>
+      <c r="AK66" s="193"/>
+      <c r="AL66" s="193"/>
+      <c r="AM66" s="193"/>
+      <c r="AN66" s="193"/>
+      <c r="AO66" s="193"/>
+      <c r="AP66" s="193"/>
+      <c r="AQ66" s="193"/>
+      <c r="AR66" s="193"/>
+      <c r="AS66" s="193"/>
+      <c r="AT66" s="193"/>
+      <c r="AU66" s="193"/>
+      <c r="AV66" s="193"/>
+      <c r="AW66" s="193"/>
+      <c r="AX66" s="193"/>
+      <c r="AY66" s="193"/>
+      <c r="AZ66" s="193"/>
+      <c r="BA66" s="193"/>
+      <c r="BB66" s="193"/>
+      <c r="BC66" s="193"/>
       <c r="BD66" s="72"/>
     </row>
     <row r="67" spans="3:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C67" s="66"/>
-      <c r="D67" s="187"/>
-      <c r="E67" s="187"/>
-      <c r="F67" s="187"/>
+      <c r="D67" s="173"/>
+      <c r="E67" s="173"/>
+      <c r="F67" s="173"/>
       <c r="G67" s="68"/>
-      <c r="H67" s="184"/>
-      <c r="I67" s="185"/>
-      <c r="J67" s="186"/>
+      <c r="H67" s="183"/>
+      <c r="I67" s="184"/>
+      <c r="J67" s="185"/>
       <c r="K67" s="68"/>
       <c r="L67" s="68"/>
       <c r="M67" s="68"/>
-      <c r="N67" s="187"/>
-      <c r="O67" s="187"/>
-      <c r="P67" s="187"/>
+      <c r="N67" s="173"/>
+      <c r="O67" s="173"/>
+      <c r="P67" s="173"/>
       <c r="Q67" s="68"/>
-      <c r="R67" s="203"/>
-      <c r="S67" s="204"/>
-      <c r="T67" s="205"/>
+      <c r="R67" s="177"/>
+      <c r="S67" s="178"/>
+      <c r="T67" s="179"/>
       <c r="U67" s="66"/>
       <c r="V67" s="68"/>
-      <c r="W67" s="212"/>
-      <c r="X67" s="212"/>
-      <c r="Y67" s="212"/>
-      <c r="Z67" s="212"/>
-      <c r="AA67" s="212"/>
-      <c r="AB67" s="212"/>
-      <c r="AC67" s="212"/>
-      <c r="AD67" s="212"/>
-      <c r="AE67" s="212"/>
-      <c r="AF67" s="212"/>
-      <c r="AG67" s="212"/>
-      <c r="AH67" s="212"/>
+      <c r="W67" s="186"/>
+      <c r="X67" s="186"/>
+      <c r="Y67" s="186"/>
+      <c r="Z67" s="186"/>
+      <c r="AA67" s="186"/>
+      <c r="AB67" s="186"/>
+      <c r="AC67" s="186"/>
+      <c r="AD67" s="186"/>
+      <c r="AE67" s="186"/>
+      <c r="AF67" s="186"/>
+      <c r="AG67" s="186"/>
+      <c r="AH67" s="186"/>
       <c r="AI67" s="70"/>
-      <c r="AJ67" s="213"/>
-      <c r="AK67" s="213"/>
-      <c r="AL67" s="213"/>
-      <c r="AM67" s="213"/>
-      <c r="AN67" s="213"/>
-      <c r="AO67" s="213"/>
-      <c r="AP67" s="213"/>
-      <c r="AQ67" s="213"/>
-      <c r="AR67" s="213"/>
-      <c r="AS67" s="213"/>
-      <c r="AT67" s="213"/>
-      <c r="AU67" s="213"/>
-      <c r="AV67" s="213"/>
-      <c r="AW67" s="213"/>
-      <c r="AX67" s="213"/>
-      <c r="AY67" s="213"/>
-      <c r="AZ67" s="213"/>
-      <c r="BA67" s="213"/>
-      <c r="BB67" s="213"/>
-      <c r="BC67" s="213"/>
+      <c r="AJ67" s="194"/>
+      <c r="AK67" s="194"/>
+      <c r="AL67" s="194"/>
+      <c r="AM67" s="194"/>
+      <c r="AN67" s="194"/>
+      <c r="AO67" s="194"/>
+      <c r="AP67" s="194"/>
+      <c r="AQ67" s="194"/>
+      <c r="AR67" s="194"/>
+      <c r="AS67" s="194"/>
+      <c r="AT67" s="194"/>
+      <c r="AU67" s="194"/>
+      <c r="AV67" s="194"/>
+      <c r="AW67" s="194"/>
+      <c r="AX67" s="194"/>
+      <c r="AY67" s="194"/>
+      <c r="AZ67" s="194"/>
+      <c r="BA67" s="194"/>
+      <c r="BB67" s="194"/>
+      <c r="BC67" s="194"/>
       <c r="BD67" s="72"/>
     </row>
     <row r="68" spans="3:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7038,39 +7658,39 @@
       <c r="W69" s="86"/>
       <c r="X69" s="86"/>
       <c r="Y69" s="86"/>
-      <c r="Z69" s="208" t="s">
+      <c r="Z69" s="195" t="s">
         <v>54</v>
       </c>
-      <c r="AA69" s="208"/>
-      <c r="AB69" s="208"/>
-      <c r="AC69" s="208"/>
-      <c r="AD69" s="208"/>
-      <c r="AE69" s="208"/>
-      <c r="AF69" s="208"/>
-      <c r="AG69" s="208"/>
-      <c r="AH69" s="208"/>
-      <c r="AI69" s="208"/>
-      <c r="AJ69" s="208"/>
-      <c r="AK69" s="208"/>
-      <c r="AL69" s="208"/>
-      <c r="AM69" s="208"/>
-      <c r="AN69" s="208"/>
-      <c r="AO69" s="208"/>
-      <c r="AP69" s="208"/>
-      <c r="AQ69" s="208"/>
-      <c r="AR69" s="208"/>
-      <c r="AS69" s="208"/>
-      <c r="AT69" s="208"/>
-      <c r="AU69" s="208"/>
-      <c r="AV69" s="208"/>
-      <c r="AW69" s="208"/>
-      <c r="AX69" s="208"/>
-      <c r="AY69" s="208"/>
-      <c r="AZ69" s="208"/>
-      <c r="BA69" s="208"/>
-      <c r="BB69" s="208"/>
-      <c r="BC69" s="208"/>
-      <c r="BD69" s="209"/>
+      <c r="AA69" s="195"/>
+      <c r="AB69" s="195"/>
+      <c r="AC69" s="195"/>
+      <c r="AD69" s="195"/>
+      <c r="AE69" s="195"/>
+      <c r="AF69" s="195"/>
+      <c r="AG69" s="195"/>
+      <c r="AH69" s="195"/>
+      <c r="AI69" s="195"/>
+      <c r="AJ69" s="195"/>
+      <c r="AK69" s="195"/>
+      <c r="AL69" s="195"/>
+      <c r="AM69" s="195"/>
+      <c r="AN69" s="195"/>
+      <c r="AO69" s="195"/>
+      <c r="AP69" s="195"/>
+      <c r="AQ69" s="195"/>
+      <c r="AR69" s="195"/>
+      <c r="AS69" s="195"/>
+      <c r="AT69" s="195"/>
+      <c r="AU69" s="195"/>
+      <c r="AV69" s="195"/>
+      <c r="AW69" s="195"/>
+      <c r="AX69" s="195"/>
+      <c r="AY69" s="195"/>
+      <c r="AZ69" s="195"/>
+      <c r="BA69" s="195"/>
+      <c r="BB69" s="195"/>
+      <c r="BC69" s="195"/>
+      <c r="BD69" s="196"/>
     </row>
     <row r="70" spans="3:56" ht="5.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C70" s="87"/>
@@ -7130,27 +7750,27 @@
     </row>
     <row r="71" spans="3:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="66"/>
-      <c r="D71" s="187" t="s">
+      <c r="D71" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="E71" s="187"/>
-      <c r="F71" s="187"/>
+      <c r="E71" s="173"/>
+      <c r="F71" s="173"/>
       <c r="G71" s="68"/>
-      <c r="H71" s="181"/>
-      <c r="I71" s="182"/>
-      <c r="J71" s="183"/>
+      <c r="H71" s="180"/>
+      <c r="I71" s="181"/>
+      <c r="J71" s="182"/>
       <c r="K71" s="68"/>
       <c r="L71" s="68"/>
       <c r="M71" s="68"/>
-      <c r="N71" s="187" t="s">
+      <c r="N71" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="O71" s="187"/>
-      <c r="P71" s="187"/>
+      <c r="O71" s="173"/>
+      <c r="P71" s="173"/>
       <c r="Q71" s="68"/>
-      <c r="R71" s="200"/>
-      <c r="S71" s="201"/>
-      <c r="T71" s="202"/>
+      <c r="R71" s="174"/>
+      <c r="S71" s="175"/>
+      <c r="T71" s="176"/>
       <c r="U71" s="68"/>
       <c r="V71" s="68"/>
       <c r="W71" s="69"/>
@@ -7165,27 +7785,27 @@
       <c r="AF71" s="69"/>
       <c r="AG71" s="69"/>
       <c r="AH71" s="68"/>
-      <c r="AI71" s="187" t="s">
+      <c r="AI71" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="AJ71" s="187"/>
-      <c r="AK71" s="187"/>
+      <c r="AJ71" s="173"/>
+      <c r="AK71" s="173"/>
       <c r="AL71" s="68"/>
-      <c r="AM71" s="200"/>
-      <c r="AN71" s="201"/>
-      <c r="AO71" s="202"/>
+      <c r="AM71" s="174"/>
+      <c r="AN71" s="175"/>
+      <c r="AO71" s="176"/>
       <c r="AP71" s="68"/>
       <c r="AQ71" s="68"/>
       <c r="AR71" s="68"/>
-      <c r="AS71" s="187" t="s">
+      <c r="AS71" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="AT71" s="187"/>
-      <c r="AU71" s="187"/>
+      <c r="AT71" s="173"/>
+      <c r="AU71" s="173"/>
       <c r="AV71" s="68"/>
-      <c r="AW71" s="181"/>
-      <c r="AX71" s="182"/>
-      <c r="AY71" s="183"/>
+      <c r="AW71" s="180"/>
+      <c r="AX71" s="181"/>
+      <c r="AY71" s="182"/>
       <c r="AZ71" s="68"/>
       <c r="BA71" s="68"/>
       <c r="BB71" s="69"/>
@@ -7194,23 +7814,23 @@
     </row>
     <row r="72" spans="3:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C72" s="66"/>
-      <c r="D72" s="187"/>
-      <c r="E72" s="187"/>
-      <c r="F72" s="187"/>
+      <c r="D72" s="173"/>
+      <c r="E72" s="173"/>
+      <c r="F72" s="173"/>
       <c r="G72" s="68"/>
-      <c r="H72" s="184"/>
-      <c r="I72" s="185"/>
-      <c r="J72" s="186"/>
+      <c r="H72" s="183"/>
+      <c r="I72" s="184"/>
+      <c r="J72" s="185"/>
       <c r="K72" s="68"/>
       <c r="L72" s="68"/>
       <c r="M72" s="68"/>
-      <c r="N72" s="187"/>
-      <c r="O72" s="187"/>
-      <c r="P72" s="187"/>
+      <c r="N72" s="173"/>
+      <c r="O72" s="173"/>
+      <c r="P72" s="173"/>
       <c r="Q72" s="68"/>
-      <c r="R72" s="203"/>
-      <c r="S72" s="204"/>
-      <c r="T72" s="205"/>
+      <c r="R72" s="177"/>
+      <c r="S72" s="178"/>
+      <c r="T72" s="179"/>
       <c r="U72" s="68"/>
       <c r="V72" s="68"/>
       <c r="W72" s="69"/>
@@ -7225,23 +7845,23 @@
       <c r="AF72" s="69"/>
       <c r="AG72" s="69"/>
       <c r="AH72" s="68"/>
-      <c r="AI72" s="187"/>
-      <c r="AJ72" s="187"/>
-      <c r="AK72" s="187"/>
+      <c r="AI72" s="173"/>
+      <c r="AJ72" s="173"/>
+      <c r="AK72" s="173"/>
       <c r="AL72" s="68"/>
-      <c r="AM72" s="203"/>
-      <c r="AN72" s="204"/>
-      <c r="AO72" s="205"/>
+      <c r="AM72" s="177"/>
+      <c r="AN72" s="178"/>
+      <c r="AO72" s="179"/>
       <c r="AP72" s="68"/>
       <c r="AQ72" s="68"/>
       <c r="AR72" s="68"/>
-      <c r="AS72" s="187"/>
-      <c r="AT72" s="187"/>
-      <c r="AU72" s="187"/>
+      <c r="AS72" s="173"/>
+      <c r="AT72" s="173"/>
+      <c r="AU72" s="173"/>
       <c r="AV72" s="68"/>
-      <c r="AW72" s="184"/>
-      <c r="AX72" s="185"/>
-      <c r="AY72" s="186"/>
+      <c r="AW72" s="183"/>
+      <c r="AX72" s="184"/>
+      <c r="AY72" s="185"/>
       <c r="AZ72" s="68"/>
       <c r="BA72" s="68"/>
       <c r="BB72" s="69"/>
@@ -7331,38 +7951,38 @@
       <c r="X74" s="86"/>
       <c r="Y74" s="86"/>
       <c r="Z74" s="86"/>
-      <c r="AA74" s="208" t="s">
+      <c r="AA74" s="195" t="s">
         <v>56</v>
       </c>
-      <c r="AB74" s="208"/>
-      <c r="AC74" s="208"/>
-      <c r="AD74" s="208"/>
-      <c r="AE74" s="208"/>
-      <c r="AF74" s="208"/>
-      <c r="AG74" s="208"/>
-      <c r="AH74" s="208"/>
-      <c r="AI74" s="208"/>
-      <c r="AJ74" s="208"/>
-      <c r="AK74" s="208"/>
-      <c r="AL74" s="208"/>
-      <c r="AM74" s="208"/>
-      <c r="AN74" s="208"/>
-      <c r="AO74" s="208"/>
-      <c r="AP74" s="208"/>
-      <c r="AQ74" s="208"/>
-      <c r="AR74" s="208"/>
-      <c r="AS74" s="208"/>
-      <c r="AT74" s="208"/>
-      <c r="AU74" s="208"/>
-      <c r="AV74" s="208"/>
-      <c r="AW74" s="208"/>
-      <c r="AX74" s="208"/>
-      <c r="AY74" s="208"/>
-      <c r="AZ74" s="208"/>
-      <c r="BA74" s="208"/>
-      <c r="BB74" s="208"/>
-      <c r="BC74" s="208"/>
-      <c r="BD74" s="209"/>
+      <c r="AB74" s="195"/>
+      <c r="AC74" s="195"/>
+      <c r="AD74" s="195"/>
+      <c r="AE74" s="195"/>
+      <c r="AF74" s="195"/>
+      <c r="AG74" s="195"/>
+      <c r="AH74" s="195"/>
+      <c r="AI74" s="195"/>
+      <c r="AJ74" s="195"/>
+      <c r="AK74" s="195"/>
+      <c r="AL74" s="195"/>
+      <c r="AM74" s="195"/>
+      <c r="AN74" s="195"/>
+      <c r="AO74" s="195"/>
+      <c r="AP74" s="195"/>
+      <c r="AQ74" s="195"/>
+      <c r="AR74" s="195"/>
+      <c r="AS74" s="195"/>
+      <c r="AT74" s="195"/>
+      <c r="AU74" s="195"/>
+      <c r="AV74" s="195"/>
+      <c r="AW74" s="195"/>
+      <c r="AX74" s="195"/>
+      <c r="AY74" s="195"/>
+      <c r="AZ74" s="195"/>
+      <c r="BA74" s="195"/>
+      <c r="BB74" s="195"/>
+      <c r="BC74" s="195"/>
+      <c r="BD74" s="196"/>
     </row>
     <row r="75" spans="3:56" s="34" customFormat="1" ht="5.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C75" s="91"/>
@@ -7422,11 +8042,11 @@
     </row>
     <row r="76" spans="3:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="66"/>
-      <c r="D76" s="187" t="s">
+      <c r="D76" s="173" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="187"/>
-      <c r="F76" s="187"/>
+      <c r="E76" s="173"/>
+      <c r="F76" s="173"/>
       <c r="G76" s="68"/>
       <c r="H76" s="68"/>
       <c r="I76" s="68"/>
@@ -7434,15 +8054,15 @@
       <c r="K76" s="68"/>
       <c r="L76" s="68"/>
       <c r="M76" s="68"/>
-      <c r="N76" s="187" t="s">
+      <c r="N76" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="O76" s="187"/>
-      <c r="P76" s="187"/>
+      <c r="O76" s="173"/>
+      <c r="P76" s="173"/>
       <c r="Q76" s="68"/>
-      <c r="R76" s="181"/>
-      <c r="S76" s="182"/>
-      <c r="T76" s="183"/>
+      <c r="R76" s="180"/>
+      <c r="S76" s="181"/>
+      <c r="T76" s="182"/>
       <c r="U76" s="68"/>
       <c r="V76" s="68"/>
       <c r="W76" s="69"/>
@@ -7450,59 +8070,59 @@
       <c r="Y76" s="69"/>
       <c r="Z76" s="69"/>
       <c r="AA76" s="34"/>
-      <c r="AB76" s="187" t="s">
+      <c r="AB76" s="173" t="s">
         <v>58</v>
       </c>
-      <c r="AC76" s="187"/>
-      <c r="AD76" s="187"/>
-      <c r="AE76" s="187"/>
-      <c r="AF76" s="187"/>
-      <c r="AG76" s="187"/>
-      <c r="AH76" s="187"/>
-      <c r="AI76" s="181"/>
-      <c r="AJ76" s="182"/>
-      <c r="AK76" s="182"/>
-      <c r="AL76" s="182"/>
-      <c r="AM76" s="182"/>
-      <c r="AN76" s="182"/>
-      <c r="AO76" s="210"/>
-      <c r="AP76" s="181"/>
-      <c r="AQ76" s="182"/>
-      <c r="AR76" s="182"/>
-      <c r="AS76" s="182"/>
-      <c r="AT76" s="182"/>
-      <c r="AU76" s="182"/>
-      <c r="AV76" s="183"/>
-      <c r="AW76" s="187" t="s">
+      <c r="AC76" s="173"/>
+      <c r="AD76" s="173"/>
+      <c r="AE76" s="173"/>
+      <c r="AF76" s="173"/>
+      <c r="AG76" s="173"/>
+      <c r="AH76" s="173"/>
+      <c r="AI76" s="180"/>
+      <c r="AJ76" s="181"/>
+      <c r="AK76" s="181"/>
+      <c r="AL76" s="181"/>
+      <c r="AM76" s="181"/>
+      <c r="AN76" s="181"/>
+      <c r="AO76" s="197"/>
+      <c r="AP76" s="180"/>
+      <c r="AQ76" s="181"/>
+      <c r="AR76" s="181"/>
+      <c r="AS76" s="181"/>
+      <c r="AT76" s="181"/>
+      <c r="AU76" s="181"/>
+      <c r="AV76" s="182"/>
+      <c r="AW76" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="AX76" s="187"/>
-      <c r="AY76" s="187"/>
+      <c r="AX76" s="173"/>
+      <c r="AY76" s="173"/>
       <c r="AZ76" s="68"/>
-      <c r="BA76" s="181"/>
-      <c r="BB76" s="182"/>
-      <c r="BC76" s="183"/>
+      <c r="BA76" s="180"/>
+      <c r="BB76" s="181"/>
+      <c r="BC76" s="182"/>
       <c r="BD76" s="72"/>
     </row>
     <row r="77" spans="3:56" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C77" s="66"/>
-      <c r="D77" s="187"/>
-      <c r="E77" s="187"/>
-      <c r="F77" s="187"/>
+      <c r="D77" s="173"/>
+      <c r="E77" s="173"/>
+      <c r="F77" s="173"/>
       <c r="G77" s="95"/>
-      <c r="H77" s="198"/>
-      <c r="I77" s="198"/>
-      <c r="J77" s="198"/>
-      <c r="K77" s="198"/>
-      <c r="L77" s="198"/>
-      <c r="M77" s="198"/>
-      <c r="N77" s="187"/>
-      <c r="O77" s="187"/>
-      <c r="P77" s="187"/>
+      <c r="H77" s="193"/>
+      <c r="I77" s="193"/>
+      <c r="J77" s="193"/>
+      <c r="K77" s="193"/>
+      <c r="L77" s="193"/>
+      <c r="M77" s="193"/>
+      <c r="N77" s="173"/>
+      <c r="O77" s="173"/>
+      <c r="P77" s="173"/>
       <c r="Q77" s="68"/>
-      <c r="R77" s="184"/>
-      <c r="S77" s="185"/>
-      <c r="T77" s="186"/>
+      <c r="R77" s="183"/>
+      <c r="S77" s="184"/>
+      <c r="T77" s="185"/>
       <c r="U77" s="68"/>
       <c r="V77" s="68"/>
       <c r="W77" s="69"/>
@@ -7510,34 +8130,34 @@
       <c r="Y77" s="69"/>
       <c r="Z77" s="69"/>
       <c r="AA77" s="34"/>
-      <c r="AB77" s="187"/>
-      <c r="AC77" s="187"/>
-      <c r="AD77" s="187"/>
-      <c r="AE77" s="187"/>
-      <c r="AF77" s="187"/>
-      <c r="AG77" s="187"/>
-      <c r="AH77" s="187"/>
-      <c r="AI77" s="184"/>
-      <c r="AJ77" s="185"/>
-      <c r="AK77" s="185"/>
-      <c r="AL77" s="185"/>
-      <c r="AM77" s="185"/>
-      <c r="AN77" s="185"/>
-      <c r="AO77" s="211"/>
-      <c r="AP77" s="184"/>
-      <c r="AQ77" s="185"/>
-      <c r="AR77" s="185"/>
-      <c r="AS77" s="185"/>
-      <c r="AT77" s="185"/>
-      <c r="AU77" s="185"/>
-      <c r="AV77" s="186"/>
-      <c r="AW77" s="187"/>
-      <c r="AX77" s="187"/>
-      <c r="AY77" s="187"/>
+      <c r="AB77" s="173"/>
+      <c r="AC77" s="173"/>
+      <c r="AD77" s="173"/>
+      <c r="AE77" s="173"/>
+      <c r="AF77" s="173"/>
+      <c r="AG77" s="173"/>
+      <c r="AH77" s="173"/>
+      <c r="AI77" s="183"/>
+      <c r="AJ77" s="184"/>
+      <c r="AK77" s="184"/>
+      <c r="AL77" s="184"/>
+      <c r="AM77" s="184"/>
+      <c r="AN77" s="184"/>
+      <c r="AO77" s="198"/>
+      <c r="AP77" s="183"/>
+      <c r="AQ77" s="184"/>
+      <c r="AR77" s="184"/>
+      <c r="AS77" s="184"/>
+      <c r="AT77" s="184"/>
+      <c r="AU77" s="184"/>
+      <c r="AV77" s="185"/>
+      <c r="AW77" s="173"/>
+      <c r="AX77" s="173"/>
+      <c r="AY77" s="173"/>
       <c r="AZ77" s="68"/>
-      <c r="BA77" s="184"/>
-      <c r="BB77" s="185"/>
-      <c r="BC77" s="186"/>
+      <c r="BA77" s="183"/>
+      <c r="BB77" s="184"/>
+      <c r="BC77" s="185"/>
       <c r="BD77" s="72"/>
     </row>
     <row r="78" spans="3:56" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7618,44 +8238,44 @@
       <c r="S79" s="92"/>
       <c r="T79" s="92"/>
       <c r="U79" s="92"/>
-      <c r="V79" s="199" t="s">
+      <c r="V79" s="207" t="s">
         <v>60</v>
       </c>
-      <c r="W79" s="199"/>
-      <c r="X79" s="199"/>
-      <c r="Y79" s="199"/>
-      <c r="Z79" s="199"/>
-      <c r="AA79" s="199"/>
-      <c r="AB79" s="199"/>
-      <c r="AC79" s="199"/>
-      <c r="AD79" s="199"/>
-      <c r="AE79" s="199"/>
-      <c r="AF79" s="199"/>
-      <c r="AG79" s="199"/>
-      <c r="AH79" s="199"/>
-      <c r="AI79" s="199"/>
-      <c r="AJ79" s="199"/>
-      <c r="AK79" s="199"/>
+      <c r="W79" s="207"/>
+      <c r="X79" s="207"/>
+      <c r="Y79" s="207"/>
+      <c r="Z79" s="207"/>
+      <c r="AA79" s="207"/>
+      <c r="AB79" s="207"/>
+      <c r="AC79" s="207"/>
+      <c r="AD79" s="207"/>
+      <c r="AE79" s="207"/>
+      <c r="AF79" s="207"/>
+      <c r="AG79" s="207"/>
+      <c r="AH79" s="207"/>
+      <c r="AI79" s="207"/>
+      <c r="AJ79" s="207"/>
+      <c r="AK79" s="207"/>
       <c r="AL79" s="92"/>
       <c r="AM79" s="92"/>
-      <c r="AN79" s="199" t="s">
+      <c r="AN79" s="207" t="s">
         <v>61</v>
       </c>
-      <c r="AO79" s="199"/>
-      <c r="AP79" s="199"/>
-      <c r="AQ79" s="199"/>
-      <c r="AR79" s="199"/>
-      <c r="AS79" s="199"/>
-      <c r="AT79" s="199"/>
-      <c r="AU79" s="199"/>
-      <c r="AV79" s="199"/>
-      <c r="AW79" s="199"/>
-      <c r="AX79" s="199"/>
-      <c r="AY79" s="199"/>
-      <c r="AZ79" s="199"/>
-      <c r="BA79" s="199"/>
-      <c r="BB79" s="199"/>
-      <c r="BC79" s="199"/>
+      <c r="AO79" s="207"/>
+      <c r="AP79" s="207"/>
+      <c r="AQ79" s="207"/>
+      <c r="AR79" s="207"/>
+      <c r="AS79" s="207"/>
+      <c r="AT79" s="207"/>
+      <c r="AU79" s="207"/>
+      <c r="AV79" s="207"/>
+      <c r="AW79" s="207"/>
+      <c r="AX79" s="207"/>
+      <c r="AY79" s="207"/>
+      <c r="AZ79" s="207"/>
+      <c r="BA79" s="207"/>
+      <c r="BB79" s="207"/>
+      <c r="BC79" s="207"/>
       <c r="BD79" s="96"/>
     </row>
     <row r="80" spans="3:56" ht="5.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7716,126 +8336,126 @@
     </row>
     <row r="81" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="66"/>
-      <c r="D81" s="187" t="s">
+      <c r="D81" s="173" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="187"/>
-      <c r="F81" s="187"/>
+      <c r="E81" s="173"/>
+      <c r="F81" s="173"/>
       <c r="G81" s="68"/>
-      <c r="H81" s="200"/>
-      <c r="I81" s="201"/>
-      <c r="J81" s="202"/>
+      <c r="H81" s="174"/>
+      <c r="I81" s="175"/>
+      <c r="J81" s="176"/>
       <c r="K81" s="68"/>
-      <c r="L81" s="206" t="s">
+      <c r="L81" s="208" t="s">
         <v>63</v>
       </c>
-      <c r="M81" s="206"/>
-      <c r="N81" s="206"/>
-      <c r="O81" s="206"/>
-      <c r="P81" s="206"/>
+      <c r="M81" s="208"/>
+      <c r="N81" s="208"/>
+      <c r="O81" s="208"/>
+      <c r="P81" s="208"/>
       <c r="Q81" s="68"/>
-      <c r="R81" s="181"/>
-      <c r="S81" s="182"/>
-      <c r="T81" s="183"/>
+      <c r="R81" s="180"/>
+      <c r="S81" s="181"/>
+      <c r="T81" s="182"/>
       <c r="U81" s="68"/>
-      <c r="V81" s="207" t="s">
+      <c r="V81" s="209" t="s">
         <v>64</v>
       </c>
-      <c r="W81" s="207"/>
-      <c r="X81" s="207"/>
-      <c r="Y81" s="207"/>
-      <c r="Z81" s="181"/>
-      <c r="AA81" s="182"/>
-      <c r="AB81" s="183"/>
+      <c r="W81" s="209"/>
+      <c r="X81" s="209"/>
+      <c r="Y81" s="209"/>
+      <c r="Z81" s="180"/>
+      <c r="AA81" s="181"/>
+      <c r="AB81" s="182"/>
       <c r="AC81" s="34"/>
-      <c r="AD81" s="207" t="s">
+      <c r="AD81" s="209" t="s">
         <v>65</v>
       </c>
-      <c r="AE81" s="207"/>
-      <c r="AF81" s="207"/>
-      <c r="AG81" s="207"/>
-      <c r="AH81" s="207"/>
-      <c r="AI81" s="181"/>
-      <c r="AJ81" s="182"/>
-      <c r="AK81" s="183"/>
+      <c r="AE81" s="209"/>
+      <c r="AF81" s="209"/>
+      <c r="AG81" s="209"/>
+      <c r="AH81" s="209"/>
+      <c r="AI81" s="180"/>
+      <c r="AJ81" s="181"/>
+      <c r="AK81" s="182"/>
       <c r="AL81" s="34"/>
       <c r="AM81" s="34"/>
-      <c r="AN81" s="187" t="s">
+      <c r="AN81" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="AO81" s="187"/>
-      <c r="AP81" s="187"/>
+      <c r="AO81" s="173"/>
+      <c r="AP81" s="173"/>
       <c r="AQ81" s="68"/>
-      <c r="AR81" s="181"/>
-      <c r="AS81" s="182"/>
-      <c r="AT81" s="183"/>
+      <c r="AR81" s="180"/>
+      <c r="AS81" s="181"/>
+      <c r="AT81" s="182"/>
       <c r="AU81" s="68"/>
       <c r="AV81" s="68"/>
-      <c r="AW81" s="187" t="s">
+      <c r="AW81" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="AX81" s="187"/>
-      <c r="AY81" s="187"/>
+      <c r="AX81" s="173"/>
+      <c r="AY81" s="173"/>
       <c r="AZ81" s="68"/>
-      <c r="BA81" s="181"/>
-      <c r="BB81" s="182"/>
-      <c r="BC81" s="183"/>
+      <c r="BA81" s="180"/>
+      <c r="BB81" s="181"/>
+      <c r="BC81" s="182"/>
       <c r="BD81" s="72"/>
     </row>
     <row r="82" spans="2:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C82" s="66"/>
-      <c r="D82" s="187"/>
-      <c r="E82" s="187"/>
-      <c r="F82" s="187"/>
+      <c r="D82" s="173"/>
+      <c r="E82" s="173"/>
+      <c r="F82" s="173"/>
       <c r="G82" s="68"/>
-      <c r="H82" s="203"/>
-      <c r="I82" s="204"/>
-      <c r="J82" s="205"/>
+      <c r="H82" s="177"/>
+      <c r="I82" s="178"/>
+      <c r="J82" s="179"/>
       <c r="K82" s="68"/>
-      <c r="L82" s="206"/>
-      <c r="M82" s="206"/>
-      <c r="N82" s="206"/>
-      <c r="O82" s="206"/>
-      <c r="P82" s="206"/>
+      <c r="L82" s="208"/>
+      <c r="M82" s="208"/>
+      <c r="N82" s="208"/>
+      <c r="O82" s="208"/>
+      <c r="P82" s="208"/>
       <c r="Q82" s="68"/>
-      <c r="R82" s="184"/>
-      <c r="S82" s="185"/>
-      <c r="T82" s="186"/>
+      <c r="R82" s="183"/>
+      <c r="S82" s="184"/>
+      <c r="T82" s="185"/>
       <c r="U82" s="68"/>
-      <c r="V82" s="207"/>
-      <c r="W82" s="207"/>
-      <c r="X82" s="207"/>
-      <c r="Y82" s="207"/>
-      <c r="Z82" s="184"/>
-      <c r="AA82" s="185"/>
-      <c r="AB82" s="186"/>
+      <c r="V82" s="209"/>
+      <c r="W82" s="209"/>
+      <c r="X82" s="209"/>
+      <c r="Y82" s="209"/>
+      <c r="Z82" s="183"/>
+      <c r="AA82" s="184"/>
+      <c r="AB82" s="185"/>
       <c r="AC82" s="34"/>
-      <c r="AD82" s="207"/>
-      <c r="AE82" s="207"/>
-      <c r="AF82" s="207"/>
-      <c r="AG82" s="207"/>
-      <c r="AH82" s="207"/>
-      <c r="AI82" s="184"/>
-      <c r="AJ82" s="185"/>
-      <c r="AK82" s="186"/>
+      <c r="AD82" s="209"/>
+      <c r="AE82" s="209"/>
+      <c r="AF82" s="209"/>
+      <c r="AG82" s="209"/>
+      <c r="AH82" s="209"/>
+      <c r="AI82" s="183"/>
+      <c r="AJ82" s="184"/>
+      <c r="AK82" s="185"/>
       <c r="AL82" s="34"/>
       <c r="AM82" s="34"/>
-      <c r="AN82" s="187"/>
-      <c r="AO82" s="187"/>
-      <c r="AP82" s="187"/>
+      <c r="AN82" s="173"/>
+      <c r="AO82" s="173"/>
+      <c r="AP82" s="173"/>
       <c r="AQ82" s="68"/>
-      <c r="AR82" s="184"/>
-      <c r="AS82" s="185"/>
-      <c r="AT82" s="186"/>
+      <c r="AR82" s="183"/>
+      <c r="AS82" s="184"/>
+      <c r="AT82" s="185"/>
       <c r="AU82" s="68"/>
       <c r="AV82" s="68"/>
-      <c r="AW82" s="187"/>
-      <c r="AX82" s="187"/>
-      <c r="AY82" s="187"/>
+      <c r="AW82" s="173"/>
+      <c r="AX82" s="173"/>
+      <c r="AY82" s="173"/>
       <c r="AZ82" s="68"/>
-      <c r="BA82" s="184"/>
-      <c r="BB82" s="185"/>
-      <c r="BC82" s="186"/>
+      <c r="BA82" s="183"/>
+      <c r="BB82" s="184"/>
+      <c r="BC82" s="185"/>
       <c r="BD82" s="72"/>
     </row>
     <row r="83" spans="2:56" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7895,301 +8515,301 @@
       <c r="BD83" s="72"/>
     </row>
     <row r="84" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C84" s="188" t="s">
+      <c r="C84" s="167" t="s">
         <v>66</v>
       </c>
-      <c r="D84" s="189"/>
-      <c r="E84" s="189"/>
-      <c r="F84" s="189"/>
-      <c r="G84" s="189"/>
-      <c r="H84" s="189"/>
-      <c r="I84" s="189"/>
-      <c r="J84" s="189"/>
-      <c r="K84" s="189"/>
-      <c r="L84" s="189"/>
-      <c r="M84" s="189"/>
-      <c r="N84" s="189"/>
-      <c r="O84" s="189"/>
-      <c r="P84" s="189"/>
-      <c r="Q84" s="189"/>
-      <c r="R84" s="189"/>
-      <c r="S84" s="189"/>
-      <c r="T84" s="189"/>
-      <c r="U84" s="189"/>
-      <c r="V84" s="189"/>
-      <c r="W84" s="189"/>
-      <c r="X84" s="189"/>
-      <c r="Y84" s="189"/>
-      <c r="Z84" s="189"/>
-      <c r="AA84" s="189"/>
-      <c r="AB84" s="189"/>
-      <c r="AC84" s="189"/>
-      <c r="AD84" s="189"/>
-      <c r="AE84" s="189"/>
-      <c r="AF84" s="189"/>
-      <c r="AG84" s="189"/>
-      <c r="AH84" s="189"/>
-      <c r="AI84" s="189"/>
-      <c r="AJ84" s="189"/>
-      <c r="AK84" s="189"/>
-      <c r="AL84" s="192" t="s">
+      <c r="D84" s="168"/>
+      <c r="E84" s="168"/>
+      <c r="F84" s="168"/>
+      <c r="G84" s="168"/>
+      <c r="H84" s="168"/>
+      <c r="I84" s="168"/>
+      <c r="J84" s="168"/>
+      <c r="K84" s="168"/>
+      <c r="L84" s="168"/>
+      <c r="M84" s="168"/>
+      <c r="N84" s="168"/>
+      <c r="O84" s="168"/>
+      <c r="P84" s="168"/>
+      <c r="Q84" s="168"/>
+      <c r="R84" s="168"/>
+      <c r="S84" s="168"/>
+      <c r="T84" s="168"/>
+      <c r="U84" s="168"/>
+      <c r="V84" s="168"/>
+      <c r="W84" s="168"/>
+      <c r="X84" s="168"/>
+      <c r="Y84" s="168"/>
+      <c r="Z84" s="168"/>
+      <c r="AA84" s="168"/>
+      <c r="AB84" s="168"/>
+      <c r="AC84" s="168"/>
+      <c r="AD84" s="168"/>
+      <c r="AE84" s="168"/>
+      <c r="AF84" s="168"/>
+      <c r="AG84" s="168"/>
+      <c r="AH84" s="168"/>
+      <c r="AI84" s="168"/>
+      <c r="AJ84" s="168"/>
+      <c r="AK84" s="168"/>
+      <c r="AL84" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="AM84" s="193"/>
-      <c r="AN84" s="193"/>
-      <c r="AO84" s="193"/>
-      <c r="AP84" s="193"/>
-      <c r="AQ84" s="193"/>
-      <c r="AR84" s="193"/>
-      <c r="AS84" s="193"/>
-      <c r="AT84" s="193"/>
-      <c r="AU84" s="193"/>
-      <c r="AV84" s="193"/>
-      <c r="AW84" s="193"/>
-      <c r="AX84" s="193"/>
-      <c r="AY84" s="193"/>
-      <c r="AZ84" s="193"/>
-      <c r="BA84" s="193"/>
-      <c r="BB84" s="193"/>
-      <c r="BC84" s="193"/>
-      <c r="BD84" s="194"/>
+      <c r="AM84" s="202"/>
+      <c r="AN84" s="202"/>
+      <c r="AO84" s="202"/>
+      <c r="AP84" s="202"/>
+      <c r="AQ84" s="202"/>
+      <c r="AR84" s="202"/>
+      <c r="AS84" s="202"/>
+      <c r="AT84" s="202"/>
+      <c r="AU84" s="202"/>
+      <c r="AV84" s="202"/>
+      <c r="AW84" s="202"/>
+      <c r="AX84" s="202"/>
+      <c r="AY84" s="202"/>
+      <c r="AZ84" s="202"/>
+      <c r="BA84" s="202"/>
+      <c r="BB84" s="202"/>
+      <c r="BC84" s="202"/>
+      <c r="BD84" s="203"/>
     </row>
     <row r="85" spans="2:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C85" s="190"/>
-      <c r="D85" s="191"/>
-      <c r="E85" s="191"/>
-      <c r="F85" s="191"/>
-      <c r="G85" s="191"/>
-      <c r="H85" s="191"/>
-      <c r="I85" s="191"/>
-      <c r="J85" s="191"/>
-      <c r="K85" s="191"/>
-      <c r="L85" s="191"/>
-      <c r="M85" s="191"/>
-      <c r="N85" s="191"/>
-      <c r="O85" s="191"/>
-      <c r="P85" s="191"/>
-      <c r="Q85" s="191"/>
-      <c r="R85" s="191"/>
-      <c r="S85" s="191"/>
-      <c r="T85" s="191"/>
-      <c r="U85" s="191"/>
-      <c r="V85" s="191"/>
-      <c r="W85" s="191"/>
-      <c r="X85" s="191"/>
-      <c r="Y85" s="191"/>
-      <c r="Z85" s="191"/>
-      <c r="AA85" s="191"/>
-      <c r="AB85" s="191"/>
-      <c r="AC85" s="191"/>
-      <c r="AD85" s="191"/>
-      <c r="AE85" s="191"/>
-      <c r="AF85" s="191"/>
-      <c r="AG85" s="191"/>
-      <c r="AH85" s="191"/>
-      <c r="AI85" s="191"/>
-      <c r="AJ85" s="191"/>
-      <c r="AK85" s="191"/>
-      <c r="AL85" s="195"/>
-      <c r="AM85" s="196"/>
-      <c r="AN85" s="196"/>
-      <c r="AO85" s="196"/>
-      <c r="AP85" s="196"/>
-      <c r="AQ85" s="196"/>
-      <c r="AR85" s="196"/>
-      <c r="AS85" s="196"/>
-      <c r="AT85" s="196"/>
-      <c r="AU85" s="196"/>
-      <c r="AV85" s="196"/>
-      <c r="AW85" s="196"/>
-      <c r="AX85" s="196"/>
-      <c r="AY85" s="196"/>
-      <c r="AZ85" s="196"/>
-      <c r="BA85" s="196"/>
-      <c r="BB85" s="196"/>
-      <c r="BC85" s="196"/>
-      <c r="BD85" s="197"/>
+      <c r="C85" s="199"/>
+      <c r="D85" s="200"/>
+      <c r="E85" s="200"/>
+      <c r="F85" s="200"/>
+      <c r="G85" s="200"/>
+      <c r="H85" s="200"/>
+      <c r="I85" s="200"/>
+      <c r="J85" s="200"/>
+      <c r="K85" s="200"/>
+      <c r="L85" s="200"/>
+      <c r="M85" s="200"/>
+      <c r="N85" s="200"/>
+      <c r="O85" s="200"/>
+      <c r="P85" s="200"/>
+      <c r="Q85" s="200"/>
+      <c r="R85" s="200"/>
+      <c r="S85" s="200"/>
+      <c r="T85" s="200"/>
+      <c r="U85" s="200"/>
+      <c r="V85" s="200"/>
+      <c r="W85" s="200"/>
+      <c r="X85" s="200"/>
+      <c r="Y85" s="200"/>
+      <c r="Z85" s="200"/>
+      <c r="AA85" s="200"/>
+      <c r="AB85" s="200"/>
+      <c r="AC85" s="200"/>
+      <c r="AD85" s="200"/>
+      <c r="AE85" s="200"/>
+      <c r="AF85" s="200"/>
+      <c r="AG85" s="200"/>
+      <c r="AH85" s="200"/>
+      <c r="AI85" s="200"/>
+      <c r="AJ85" s="200"/>
+      <c r="AK85" s="200"/>
+      <c r="AL85" s="204"/>
+      <c r="AM85" s="205"/>
+      <c r="AN85" s="205"/>
+      <c r="AO85" s="205"/>
+      <c r="AP85" s="205"/>
+      <c r="AQ85" s="205"/>
+      <c r="AR85" s="205"/>
+      <c r="AS85" s="205"/>
+      <c r="AT85" s="205"/>
+      <c r="AU85" s="205"/>
+      <c r="AV85" s="205"/>
+      <c r="AW85" s="205"/>
+      <c r="AX85" s="205"/>
+      <c r="AY85" s="205"/>
+      <c r="AZ85" s="205"/>
+      <c r="BA85" s="205"/>
+      <c r="BB85" s="205"/>
+      <c r="BC85" s="205"/>
+      <c r="BD85" s="206"/>
     </row>
     <row r="86" spans="2:56" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="177" t="s">
+      <c r="C86" s="219" t="s">
         <v>68</v>
       </c>
-      <c r="D86" s="178"/>
-      <c r="E86" s="178"/>
-      <c r="F86" s="178"/>
-      <c r="G86" s="178"/>
-      <c r="H86" s="178"/>
-      <c r="I86" s="178"/>
-      <c r="J86" s="178"/>
-      <c r="K86" s="178"/>
-      <c r="L86" s="178"/>
-      <c r="M86" s="179"/>
-      <c r="N86" s="180" t="s">
+      <c r="D86" s="220"/>
+      <c r="E86" s="220"/>
+      <c r="F86" s="220"/>
+      <c r="G86" s="220"/>
+      <c r="H86" s="220"/>
+      <c r="I86" s="220"/>
+      <c r="J86" s="220"/>
+      <c r="K86" s="220"/>
+      <c r="L86" s="220"/>
+      <c r="M86" s="221"/>
+      <c r="N86" s="222" t="s">
         <v>69</v>
       </c>
-      <c r="O86" s="180"/>
-      <c r="P86" s="180"/>
-      <c r="Q86" s="180"/>
-      <c r="R86" s="180"/>
-      <c r="S86" s="180"/>
-      <c r="T86" s="180" t="s">
+      <c r="O86" s="222"/>
+      <c r="P86" s="222"/>
+      <c r="Q86" s="222"/>
+      <c r="R86" s="222"/>
+      <c r="S86" s="222"/>
+      <c r="T86" s="222" t="s">
         <v>70</v>
       </c>
-      <c r="U86" s="180"/>
-      <c r="V86" s="180"/>
-      <c r="W86" s="180"/>
-      <c r="X86" s="180" t="s">
+      <c r="U86" s="222"/>
+      <c r="V86" s="222"/>
+      <c r="W86" s="222"/>
+      <c r="X86" s="222" t="s">
         <v>71</v>
       </c>
-      <c r="Y86" s="180"/>
-      <c r="Z86" s="180"/>
-      <c r="AA86" s="180"/>
-      <c r="AB86" s="180"/>
-      <c r="AC86" s="180" t="s">
+      <c r="Y86" s="222"/>
+      <c r="Z86" s="222"/>
+      <c r="AA86" s="222"/>
+      <c r="AB86" s="222"/>
+      <c r="AC86" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="AD86" s="180"/>
-      <c r="AE86" s="180"/>
-      <c r="AF86" s="180"/>
-      <c r="AG86" s="180" t="s">
+      <c r="AD86" s="222"/>
+      <c r="AE86" s="222"/>
+      <c r="AF86" s="222"/>
+      <c r="AG86" s="222" t="s">
         <v>73</v>
       </c>
-      <c r="AH86" s="180"/>
-      <c r="AI86" s="180"/>
-      <c r="AJ86" s="180"/>
-      <c r="AK86" s="180"/>
-      <c r="AL86" s="171" t="s">
+      <c r="AH86" s="222"/>
+      <c r="AI86" s="222"/>
+      <c r="AJ86" s="222"/>
+      <c r="AK86" s="222"/>
+      <c r="AL86" s="227" t="s">
         <v>74</v>
       </c>
-      <c r="AM86" s="171"/>
-      <c r="AN86" s="171"/>
-      <c r="AO86" s="171"/>
-      <c r="AP86" s="171" t="s">
+      <c r="AM86" s="227"/>
+      <c r="AN86" s="227"/>
+      <c r="AO86" s="227"/>
+      <c r="AP86" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="AQ86" s="171"/>
-      <c r="AR86" s="171"/>
-      <c r="AS86" s="171"/>
-      <c r="AT86" s="171"/>
-      <c r="AU86" s="171"/>
-      <c r="AV86" s="172" t="s">
+      <c r="AQ86" s="227"/>
+      <c r="AR86" s="227"/>
+      <c r="AS86" s="227"/>
+      <c r="AT86" s="227"/>
+      <c r="AU86" s="227"/>
+      <c r="AV86" s="228" t="s">
         <v>76</v>
       </c>
-      <c r="AW86" s="173"/>
-      <c r="AX86" s="172" t="s">
+      <c r="AW86" s="229"/>
+      <c r="AX86" s="228" t="s">
         <v>77</v>
       </c>
-      <c r="AY86" s="173"/>
-      <c r="AZ86" s="174" t="s">
+      <c r="AY86" s="229"/>
+      <c r="AZ86" s="230" t="s">
         <v>69</v>
       </c>
-      <c r="BA86" s="174"/>
-      <c r="BB86" s="174"/>
-      <c r="BC86" s="174"/>
-      <c r="BD86" s="175"/>
+      <c r="BA86" s="230"/>
+      <c r="BB86" s="230"/>
+      <c r="BC86" s="230"/>
+      <c r="BD86" s="231"/>
     </row>
     <row r="87" spans="2:56" ht="51.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="164"/>
-      <c r="D87" s="165"/>
-      <c r="E87" s="165"/>
-      <c r="F87" s="165"/>
-      <c r="G87" s="165"/>
-      <c r="H87" s="165"/>
-      <c r="I87" s="165"/>
-      <c r="J87" s="165"/>
-      <c r="K87" s="165"/>
-      <c r="L87" s="165"/>
-      <c r="M87" s="166"/>
-      <c r="N87" s="167"/>
-      <c r="O87" s="168"/>
-      <c r="P87" s="168"/>
-      <c r="Q87" s="168"/>
-      <c r="R87" s="168"/>
-      <c r="S87" s="169"/>
-      <c r="T87" s="167"/>
-      <c r="U87" s="168"/>
-      <c r="V87" s="168"/>
-      <c r="W87" s="169"/>
-      <c r="X87" s="167"/>
-      <c r="Y87" s="168"/>
-      <c r="Z87" s="168"/>
-      <c r="AA87" s="168"/>
-      <c r="AB87" s="169"/>
-      <c r="AC87" s="176"/>
-      <c r="AD87" s="159"/>
-      <c r="AE87" s="159"/>
-      <c r="AF87" s="160"/>
-      <c r="AG87" s="158"/>
-      <c r="AH87" s="159"/>
-      <c r="AI87" s="159"/>
-      <c r="AJ87" s="159"/>
-      <c r="AK87" s="160"/>
-      <c r="AL87" s="158"/>
-      <c r="AM87" s="159"/>
-      <c r="AN87" s="159"/>
-      <c r="AO87" s="160"/>
-      <c r="AP87" s="158"/>
-      <c r="AQ87" s="159"/>
-      <c r="AR87" s="159"/>
-      <c r="AS87" s="159"/>
-      <c r="AT87" s="159"/>
-      <c r="AU87" s="160"/>
-      <c r="AV87" s="161"/>
-      <c r="AW87" s="162"/>
-      <c r="AX87" s="161"/>
-      <c r="AY87" s="162"/>
-      <c r="AZ87" s="158"/>
-      <c r="BA87" s="159"/>
-      <c r="BB87" s="159"/>
-      <c r="BC87" s="159"/>
-      <c r="BD87" s="163"/>
+      <c r="C87" s="210"/>
+      <c r="D87" s="211"/>
+      <c r="E87" s="211"/>
+      <c r="F87" s="211"/>
+      <c r="G87" s="211"/>
+      <c r="H87" s="211"/>
+      <c r="I87" s="211"/>
+      <c r="J87" s="211"/>
+      <c r="K87" s="211"/>
+      <c r="L87" s="211"/>
+      <c r="M87" s="212"/>
+      <c r="N87" s="213"/>
+      <c r="O87" s="214"/>
+      <c r="P87" s="214"/>
+      <c r="Q87" s="214"/>
+      <c r="R87" s="214"/>
+      <c r="S87" s="215"/>
+      <c r="T87" s="213"/>
+      <c r="U87" s="214"/>
+      <c r="V87" s="214"/>
+      <c r="W87" s="215"/>
+      <c r="X87" s="213"/>
+      <c r="Y87" s="214"/>
+      <c r="Z87" s="214"/>
+      <c r="AA87" s="214"/>
+      <c r="AB87" s="215"/>
+      <c r="AC87" s="216"/>
+      <c r="AD87" s="217"/>
+      <c r="AE87" s="217"/>
+      <c r="AF87" s="218"/>
+      <c r="AG87" s="223"/>
+      <c r="AH87" s="217"/>
+      <c r="AI87" s="217"/>
+      <c r="AJ87" s="217"/>
+      <c r="AK87" s="218"/>
+      <c r="AL87" s="223"/>
+      <c r="AM87" s="217"/>
+      <c r="AN87" s="217"/>
+      <c r="AO87" s="218"/>
+      <c r="AP87" s="223"/>
+      <c r="AQ87" s="217"/>
+      <c r="AR87" s="217"/>
+      <c r="AS87" s="217"/>
+      <c r="AT87" s="217"/>
+      <c r="AU87" s="218"/>
+      <c r="AV87" s="224"/>
+      <c r="AW87" s="225"/>
+      <c r="AX87" s="224"/>
+      <c r="AY87" s="225"/>
+      <c r="AZ87" s="223"/>
+      <c r="BA87" s="217"/>
+      <c r="BB87" s="217"/>
+      <c r="BC87" s="217"/>
+      <c r="BD87" s="226"/>
     </row>
     <row r="88" spans="2:56" ht="51.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="164"/>
-      <c r="D88" s="165"/>
-      <c r="E88" s="165"/>
-      <c r="F88" s="165"/>
-      <c r="G88" s="165"/>
-      <c r="H88" s="165"/>
-      <c r="I88" s="165"/>
-      <c r="J88" s="165"/>
-      <c r="K88" s="165"/>
-      <c r="L88" s="165"/>
-      <c r="M88" s="166"/>
-      <c r="N88" s="167"/>
-      <c r="O88" s="168"/>
-      <c r="P88" s="168"/>
-      <c r="Q88" s="168"/>
-      <c r="R88" s="168"/>
-      <c r="S88" s="169"/>
-      <c r="T88" s="167"/>
-      <c r="U88" s="168"/>
-      <c r="V88" s="168"/>
-      <c r="W88" s="169"/>
-      <c r="X88" s="167"/>
-      <c r="Y88" s="168"/>
-      <c r="Z88" s="168"/>
-      <c r="AA88" s="168"/>
-      <c r="AB88" s="169"/>
-      <c r="AC88" s="170"/>
-      <c r="AD88" s="159"/>
-      <c r="AE88" s="159"/>
-      <c r="AF88" s="160"/>
-      <c r="AG88" s="158"/>
-      <c r="AH88" s="159"/>
-      <c r="AI88" s="159"/>
-      <c r="AJ88" s="159"/>
-      <c r="AK88" s="160"/>
-      <c r="AL88" s="158"/>
-      <c r="AM88" s="159"/>
-      <c r="AN88" s="159"/>
-      <c r="AO88" s="160"/>
-      <c r="AP88" s="158"/>
-      <c r="AQ88" s="159"/>
-      <c r="AR88" s="159"/>
-      <c r="AS88" s="159"/>
-      <c r="AT88" s="159"/>
-      <c r="AU88" s="160"/>
+      <c r="C88" s="210"/>
+      <c r="D88" s="211"/>
+      <c r="E88" s="211"/>
+      <c r="F88" s="211"/>
+      <c r="G88" s="211"/>
+      <c r="H88" s="211"/>
+      <c r="I88" s="211"/>
+      <c r="J88" s="211"/>
+      <c r="K88" s="211"/>
+      <c r="L88" s="211"/>
+      <c r="M88" s="212"/>
+      <c r="N88" s="213"/>
+      <c r="O88" s="214"/>
+      <c r="P88" s="214"/>
+      <c r="Q88" s="214"/>
+      <c r="R88" s="214"/>
+      <c r="S88" s="215"/>
+      <c r="T88" s="213"/>
+      <c r="U88" s="214"/>
+      <c r="V88" s="214"/>
+      <c r="W88" s="215"/>
+      <c r="X88" s="213"/>
+      <c r="Y88" s="214"/>
+      <c r="Z88" s="214"/>
+      <c r="AA88" s="214"/>
+      <c r="AB88" s="215"/>
+      <c r="AC88" s="232"/>
+      <c r="AD88" s="217"/>
+      <c r="AE88" s="217"/>
+      <c r="AF88" s="218"/>
+      <c r="AG88" s="223"/>
+      <c r="AH88" s="217"/>
+      <c r="AI88" s="217"/>
+      <c r="AJ88" s="217"/>
+      <c r="AK88" s="218"/>
+      <c r="AL88" s="223"/>
+      <c r="AM88" s="217"/>
+      <c r="AN88" s="217"/>
+      <c r="AO88" s="218"/>
+      <c r="AP88" s="223"/>
+      <c r="AQ88" s="217"/>
+      <c r="AR88" s="217"/>
+      <c r="AS88" s="217"/>
+      <c r="AT88" s="217"/>
+      <c r="AU88" s="218"/>
       <c r="AV88" s="99"/>
       <c r="AW88" s="100"/>
       <c r="AX88" s="99"/>
@@ -8201,51 +8821,51 @@
       <c r="BD88" s="101"/>
     </row>
     <row r="89" spans="2:56" ht="51.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C89" s="164"/>
-      <c r="D89" s="165"/>
-      <c r="E89" s="165"/>
-      <c r="F89" s="165"/>
-      <c r="G89" s="165"/>
-      <c r="H89" s="165"/>
-      <c r="I89" s="165"/>
-      <c r="J89" s="165"/>
-      <c r="K89" s="165"/>
-      <c r="L89" s="165"/>
-      <c r="M89" s="166"/>
-      <c r="N89" s="167"/>
-      <c r="O89" s="168"/>
-      <c r="P89" s="168"/>
-      <c r="Q89" s="168"/>
-      <c r="R89" s="168"/>
-      <c r="S89" s="169"/>
-      <c r="T89" s="167"/>
-      <c r="U89" s="168"/>
-      <c r="V89" s="168"/>
-      <c r="W89" s="169"/>
-      <c r="X89" s="167"/>
-      <c r="Y89" s="168"/>
-      <c r="Z89" s="168"/>
-      <c r="AA89" s="168"/>
-      <c r="AB89" s="169"/>
-      <c r="AC89" s="170"/>
-      <c r="AD89" s="159"/>
-      <c r="AE89" s="159"/>
-      <c r="AF89" s="160"/>
-      <c r="AG89" s="158"/>
-      <c r="AH89" s="159"/>
-      <c r="AI89" s="159"/>
-      <c r="AJ89" s="159"/>
-      <c r="AK89" s="160"/>
-      <c r="AL89" s="158"/>
-      <c r="AM89" s="159"/>
-      <c r="AN89" s="159"/>
-      <c r="AO89" s="160"/>
-      <c r="AP89" s="158"/>
-      <c r="AQ89" s="159"/>
-      <c r="AR89" s="159"/>
-      <c r="AS89" s="159"/>
-      <c r="AT89" s="159"/>
-      <c r="AU89" s="160"/>
+      <c r="C89" s="210"/>
+      <c r="D89" s="211"/>
+      <c r="E89" s="211"/>
+      <c r="F89" s="211"/>
+      <c r="G89" s="211"/>
+      <c r="H89" s="211"/>
+      <c r="I89" s="211"/>
+      <c r="J89" s="211"/>
+      <c r="K89" s="211"/>
+      <c r="L89" s="211"/>
+      <c r="M89" s="212"/>
+      <c r="N89" s="213"/>
+      <c r="O89" s="214"/>
+      <c r="P89" s="214"/>
+      <c r="Q89" s="214"/>
+      <c r="R89" s="214"/>
+      <c r="S89" s="215"/>
+      <c r="T89" s="213"/>
+      <c r="U89" s="214"/>
+      <c r="V89" s="214"/>
+      <c r="W89" s="215"/>
+      <c r="X89" s="213"/>
+      <c r="Y89" s="214"/>
+      <c r="Z89" s="214"/>
+      <c r="AA89" s="214"/>
+      <c r="AB89" s="215"/>
+      <c r="AC89" s="232"/>
+      <c r="AD89" s="217"/>
+      <c r="AE89" s="217"/>
+      <c r="AF89" s="218"/>
+      <c r="AG89" s="223"/>
+      <c r="AH89" s="217"/>
+      <c r="AI89" s="217"/>
+      <c r="AJ89" s="217"/>
+      <c r="AK89" s="218"/>
+      <c r="AL89" s="223"/>
+      <c r="AM89" s="217"/>
+      <c r="AN89" s="217"/>
+      <c r="AO89" s="218"/>
+      <c r="AP89" s="223"/>
+      <c r="AQ89" s="217"/>
+      <c r="AR89" s="217"/>
+      <c r="AS89" s="217"/>
+      <c r="AT89" s="217"/>
+      <c r="AU89" s="218"/>
       <c r="AV89" s="99"/>
       <c r="AW89" s="100"/>
       <c r="AX89" s="99"/>
@@ -8260,524 +8880,524 @@
       <c r="B90" s="1">
         <v>15</v>
       </c>
-      <c r="C90" s="164"/>
-      <c r="D90" s="165"/>
-      <c r="E90" s="165"/>
-      <c r="F90" s="165"/>
-      <c r="G90" s="165"/>
-      <c r="H90" s="165"/>
-      <c r="I90" s="165"/>
-      <c r="J90" s="165"/>
-      <c r="K90" s="165"/>
-      <c r="L90" s="165"/>
-      <c r="M90" s="166"/>
-      <c r="N90" s="167"/>
-      <c r="O90" s="168"/>
-      <c r="P90" s="168"/>
-      <c r="Q90" s="168"/>
-      <c r="R90" s="168"/>
-      <c r="S90" s="169"/>
-      <c r="T90" s="167"/>
-      <c r="U90" s="168"/>
-      <c r="V90" s="168"/>
-      <c r="W90" s="169"/>
-      <c r="X90" s="167"/>
-      <c r="Y90" s="168"/>
-      <c r="Z90" s="168"/>
-      <c r="AA90" s="168"/>
-      <c r="AB90" s="169"/>
-      <c r="AC90" s="170"/>
-      <c r="AD90" s="159"/>
-      <c r="AE90" s="159"/>
-      <c r="AF90" s="160"/>
-      <c r="AG90" s="158"/>
-      <c r="AH90" s="159"/>
-      <c r="AI90" s="159"/>
-      <c r="AJ90" s="159"/>
-      <c r="AK90" s="160"/>
-      <c r="AL90" s="158"/>
-      <c r="AM90" s="159"/>
-      <c r="AN90" s="159"/>
-      <c r="AO90" s="160"/>
-      <c r="AP90" s="158"/>
-      <c r="AQ90" s="159"/>
-      <c r="AR90" s="159"/>
-      <c r="AS90" s="159"/>
-      <c r="AT90" s="159"/>
-      <c r="AU90" s="160"/>
-      <c r="AV90" s="161"/>
-      <c r="AW90" s="162"/>
-      <c r="AX90" s="161"/>
-      <c r="AY90" s="162"/>
-      <c r="AZ90" s="158"/>
-      <c r="BA90" s="159"/>
-      <c r="BB90" s="159"/>
-      <c r="BC90" s="159"/>
-      <c r="BD90" s="163"/>
+      <c r="C90" s="210"/>
+      <c r="D90" s="211"/>
+      <c r="E90" s="211"/>
+      <c r="F90" s="211"/>
+      <c r="G90" s="211"/>
+      <c r="H90" s="211"/>
+      <c r="I90" s="211"/>
+      <c r="J90" s="211"/>
+      <c r="K90" s="211"/>
+      <c r="L90" s="211"/>
+      <c r="M90" s="212"/>
+      <c r="N90" s="213"/>
+      <c r="O90" s="214"/>
+      <c r="P90" s="214"/>
+      <c r="Q90" s="214"/>
+      <c r="R90" s="214"/>
+      <c r="S90" s="215"/>
+      <c r="T90" s="213"/>
+      <c r="U90" s="214"/>
+      <c r="V90" s="214"/>
+      <c r="W90" s="215"/>
+      <c r="X90" s="213"/>
+      <c r="Y90" s="214"/>
+      <c r="Z90" s="214"/>
+      <c r="AA90" s="214"/>
+      <c r="AB90" s="215"/>
+      <c r="AC90" s="232"/>
+      <c r="AD90" s="217"/>
+      <c r="AE90" s="217"/>
+      <c r="AF90" s="218"/>
+      <c r="AG90" s="223"/>
+      <c r="AH90" s="217"/>
+      <c r="AI90" s="217"/>
+      <c r="AJ90" s="217"/>
+      <c r="AK90" s="218"/>
+      <c r="AL90" s="223"/>
+      <c r="AM90" s="217"/>
+      <c r="AN90" s="217"/>
+      <c r="AO90" s="218"/>
+      <c r="AP90" s="223"/>
+      <c r="AQ90" s="217"/>
+      <c r="AR90" s="217"/>
+      <c r="AS90" s="217"/>
+      <c r="AT90" s="217"/>
+      <c r="AU90" s="218"/>
+      <c r="AV90" s="224"/>
+      <c r="AW90" s="225"/>
+      <c r="AX90" s="224"/>
+      <c r="AY90" s="225"/>
+      <c r="AZ90" s="223"/>
+      <c r="BA90" s="217"/>
+      <c r="BB90" s="217"/>
+      <c r="BC90" s="217"/>
+      <c r="BD90" s="226"/>
     </row>
     <row r="91" spans="2:56" ht="51.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C91" s="164"/>
-      <c r="D91" s="165"/>
-      <c r="E91" s="165"/>
-      <c r="F91" s="165"/>
-      <c r="G91" s="165"/>
-      <c r="H91" s="165"/>
-      <c r="I91" s="165"/>
-      <c r="J91" s="165"/>
-      <c r="K91" s="165"/>
-      <c r="L91" s="165"/>
-      <c r="M91" s="166"/>
-      <c r="N91" s="167"/>
-      <c r="O91" s="168"/>
-      <c r="P91" s="168"/>
-      <c r="Q91" s="168"/>
-      <c r="R91" s="168"/>
-      <c r="S91" s="169"/>
-      <c r="T91" s="167"/>
-      <c r="U91" s="168"/>
-      <c r="V91" s="168"/>
-      <c r="W91" s="169"/>
-      <c r="X91" s="167"/>
-      <c r="Y91" s="168"/>
-      <c r="Z91" s="168"/>
-      <c r="AA91" s="168"/>
-      <c r="AB91" s="169"/>
-      <c r="AC91" s="170"/>
-      <c r="AD91" s="159"/>
-      <c r="AE91" s="159"/>
-      <c r="AF91" s="160"/>
-      <c r="AG91" s="158"/>
-      <c r="AH91" s="159"/>
-      <c r="AI91" s="159"/>
-      <c r="AJ91" s="159"/>
-      <c r="AK91" s="160"/>
-      <c r="AL91" s="158"/>
-      <c r="AM91" s="159"/>
-      <c r="AN91" s="159"/>
-      <c r="AO91" s="160"/>
-      <c r="AP91" s="158"/>
-      <c r="AQ91" s="159"/>
-      <c r="AR91" s="159"/>
-      <c r="AS91" s="159"/>
-      <c r="AT91" s="159"/>
-      <c r="AU91" s="160"/>
-      <c r="AV91" s="161"/>
-      <c r="AW91" s="162"/>
-      <c r="AX91" s="161"/>
-      <c r="AY91" s="162"/>
-      <c r="AZ91" s="158"/>
-      <c r="BA91" s="159"/>
-      <c r="BB91" s="159"/>
-      <c r="BC91" s="159"/>
-      <c r="BD91" s="163"/>
+      <c r="C91" s="210"/>
+      <c r="D91" s="211"/>
+      <c r="E91" s="211"/>
+      <c r="F91" s="211"/>
+      <c r="G91" s="211"/>
+      <c r="H91" s="211"/>
+      <c r="I91" s="211"/>
+      <c r="J91" s="211"/>
+      <c r="K91" s="211"/>
+      <c r="L91" s="211"/>
+      <c r="M91" s="212"/>
+      <c r="N91" s="213"/>
+      <c r="O91" s="214"/>
+      <c r="P91" s="214"/>
+      <c r="Q91" s="214"/>
+      <c r="R91" s="214"/>
+      <c r="S91" s="215"/>
+      <c r="T91" s="213"/>
+      <c r="U91" s="214"/>
+      <c r="V91" s="214"/>
+      <c r="W91" s="215"/>
+      <c r="X91" s="213"/>
+      <c r="Y91" s="214"/>
+      <c r="Z91" s="214"/>
+      <c r="AA91" s="214"/>
+      <c r="AB91" s="215"/>
+      <c r="AC91" s="232"/>
+      <c r="AD91" s="217"/>
+      <c r="AE91" s="217"/>
+      <c r="AF91" s="218"/>
+      <c r="AG91" s="223"/>
+      <c r="AH91" s="217"/>
+      <c r="AI91" s="217"/>
+      <c r="AJ91" s="217"/>
+      <c r="AK91" s="218"/>
+      <c r="AL91" s="223"/>
+      <c r="AM91" s="217"/>
+      <c r="AN91" s="217"/>
+      <c r="AO91" s="218"/>
+      <c r="AP91" s="223"/>
+      <c r="AQ91" s="217"/>
+      <c r="AR91" s="217"/>
+      <c r="AS91" s="217"/>
+      <c r="AT91" s="217"/>
+      <c r="AU91" s="218"/>
+      <c r="AV91" s="224"/>
+      <c r="AW91" s="225"/>
+      <c r="AX91" s="224"/>
+      <c r="AY91" s="225"/>
+      <c r="AZ91" s="223"/>
+      <c r="BA91" s="217"/>
+      <c r="BB91" s="217"/>
+      <c r="BC91" s="217"/>
+      <c r="BD91" s="226"/>
     </row>
     <row r="92" spans="2:56" ht="51.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C92" s="164"/>
-      <c r="D92" s="165"/>
-      <c r="E92" s="165"/>
-      <c r="F92" s="165"/>
-      <c r="G92" s="165"/>
-      <c r="H92" s="165"/>
-      <c r="I92" s="165"/>
-      <c r="J92" s="165"/>
-      <c r="K92" s="165"/>
-      <c r="L92" s="165"/>
-      <c r="M92" s="166"/>
-      <c r="N92" s="167"/>
-      <c r="O92" s="168"/>
-      <c r="P92" s="168"/>
-      <c r="Q92" s="168"/>
-      <c r="R92" s="168"/>
-      <c r="S92" s="169"/>
-      <c r="T92" s="167"/>
-      <c r="U92" s="168"/>
-      <c r="V92" s="168"/>
-      <c r="W92" s="169"/>
-      <c r="X92" s="167"/>
-      <c r="Y92" s="168"/>
-      <c r="Z92" s="168"/>
-      <c r="AA92" s="168"/>
-      <c r="AB92" s="169"/>
-      <c r="AC92" s="170"/>
-      <c r="AD92" s="159"/>
-      <c r="AE92" s="159"/>
-      <c r="AF92" s="160"/>
-      <c r="AG92" s="158"/>
-      <c r="AH92" s="159"/>
-      <c r="AI92" s="159"/>
-      <c r="AJ92" s="159"/>
-      <c r="AK92" s="160"/>
-      <c r="AL92" s="158"/>
-      <c r="AM92" s="159"/>
-      <c r="AN92" s="159"/>
-      <c r="AO92" s="160"/>
-      <c r="AP92" s="158"/>
-      <c r="AQ92" s="159"/>
-      <c r="AR92" s="159"/>
-      <c r="AS92" s="159"/>
-      <c r="AT92" s="159"/>
-      <c r="AU92" s="160"/>
-      <c r="AV92" s="161"/>
-      <c r="AW92" s="162"/>
-      <c r="AX92" s="161"/>
-      <c r="AY92" s="162"/>
-      <c r="AZ92" s="158"/>
-      <c r="BA92" s="159"/>
-      <c r="BB92" s="159"/>
-      <c r="BC92" s="159"/>
-      <c r="BD92" s="163"/>
+      <c r="C92" s="210"/>
+      <c r="D92" s="211"/>
+      <c r="E92" s="211"/>
+      <c r="F92" s="211"/>
+      <c r="G92" s="211"/>
+      <c r="H92" s="211"/>
+      <c r="I92" s="211"/>
+      <c r="J92" s="211"/>
+      <c r="K92" s="211"/>
+      <c r="L92" s="211"/>
+      <c r="M92" s="212"/>
+      <c r="N92" s="213"/>
+      <c r="O92" s="214"/>
+      <c r="P92" s="214"/>
+      <c r="Q92" s="214"/>
+      <c r="R92" s="214"/>
+      <c r="S92" s="215"/>
+      <c r="T92" s="213"/>
+      <c r="U92" s="214"/>
+      <c r="V92" s="214"/>
+      <c r="W92" s="215"/>
+      <c r="X92" s="213"/>
+      <c r="Y92" s="214"/>
+      <c r="Z92" s="214"/>
+      <c r="AA92" s="214"/>
+      <c r="AB92" s="215"/>
+      <c r="AC92" s="232"/>
+      <c r="AD92" s="217"/>
+      <c r="AE92" s="217"/>
+      <c r="AF92" s="218"/>
+      <c r="AG92" s="223"/>
+      <c r="AH92" s="217"/>
+      <c r="AI92" s="217"/>
+      <c r="AJ92" s="217"/>
+      <c r="AK92" s="218"/>
+      <c r="AL92" s="223"/>
+      <c r="AM92" s="217"/>
+      <c r="AN92" s="217"/>
+      <c r="AO92" s="218"/>
+      <c r="AP92" s="223"/>
+      <c r="AQ92" s="217"/>
+      <c r="AR92" s="217"/>
+      <c r="AS92" s="217"/>
+      <c r="AT92" s="217"/>
+      <c r="AU92" s="218"/>
+      <c r="AV92" s="224"/>
+      <c r="AW92" s="225"/>
+      <c r="AX92" s="224"/>
+      <c r="AY92" s="225"/>
+      <c r="AZ92" s="223"/>
+      <c r="BA92" s="217"/>
+      <c r="BB92" s="217"/>
+      <c r="BC92" s="217"/>
+      <c r="BD92" s="226"/>
     </row>
     <row r="93" spans="2:56" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="164"/>
-      <c r="D93" s="165"/>
-      <c r="E93" s="165"/>
-      <c r="F93" s="165"/>
-      <c r="G93" s="165"/>
-      <c r="H93" s="165"/>
-      <c r="I93" s="165"/>
-      <c r="J93" s="165"/>
-      <c r="K93" s="165"/>
-      <c r="L93" s="165"/>
-      <c r="M93" s="166"/>
-      <c r="N93" s="167"/>
-      <c r="O93" s="168"/>
-      <c r="P93" s="168"/>
-      <c r="Q93" s="168"/>
-      <c r="R93" s="168"/>
-      <c r="S93" s="169"/>
-      <c r="T93" s="167"/>
-      <c r="U93" s="168"/>
-      <c r="V93" s="168"/>
-      <c r="W93" s="169"/>
-      <c r="X93" s="167"/>
-      <c r="Y93" s="168"/>
-      <c r="Z93" s="168"/>
-      <c r="AA93" s="168"/>
-      <c r="AB93" s="169"/>
-      <c r="AC93" s="170"/>
-      <c r="AD93" s="159"/>
-      <c r="AE93" s="159"/>
-      <c r="AF93" s="160"/>
-      <c r="AG93" s="158"/>
-      <c r="AH93" s="159"/>
-      <c r="AI93" s="159"/>
-      <c r="AJ93" s="159"/>
-      <c r="AK93" s="160"/>
-      <c r="AL93" s="158"/>
-      <c r="AM93" s="159"/>
-      <c r="AN93" s="159"/>
-      <c r="AO93" s="160"/>
-      <c r="AP93" s="158"/>
-      <c r="AQ93" s="159"/>
-      <c r="AR93" s="159"/>
-      <c r="AS93" s="159"/>
-      <c r="AT93" s="159"/>
-      <c r="AU93" s="160"/>
-      <c r="AV93" s="161"/>
-      <c r="AW93" s="162"/>
-      <c r="AX93" s="161"/>
-      <c r="AY93" s="162"/>
-      <c r="AZ93" s="158"/>
-      <c r="BA93" s="159"/>
-      <c r="BB93" s="159"/>
-      <c r="BC93" s="159"/>
-      <c r="BD93" s="163"/>
+      <c r="C93" s="210"/>
+      <c r="D93" s="211"/>
+      <c r="E93" s="211"/>
+      <c r="F93" s="211"/>
+      <c r="G93" s="211"/>
+      <c r="H93" s="211"/>
+      <c r="I93" s="211"/>
+      <c r="J93" s="211"/>
+      <c r="K93" s="211"/>
+      <c r="L93" s="211"/>
+      <c r="M93" s="212"/>
+      <c r="N93" s="213"/>
+      <c r="O93" s="214"/>
+      <c r="P93" s="214"/>
+      <c r="Q93" s="214"/>
+      <c r="R93" s="214"/>
+      <c r="S93" s="215"/>
+      <c r="T93" s="213"/>
+      <c r="U93" s="214"/>
+      <c r="V93" s="214"/>
+      <c r="W93" s="215"/>
+      <c r="X93" s="213"/>
+      <c r="Y93" s="214"/>
+      <c r="Z93" s="214"/>
+      <c r="AA93" s="214"/>
+      <c r="AB93" s="215"/>
+      <c r="AC93" s="232"/>
+      <c r="AD93" s="217"/>
+      <c r="AE93" s="217"/>
+      <c r="AF93" s="218"/>
+      <c r="AG93" s="223"/>
+      <c r="AH93" s="217"/>
+      <c r="AI93" s="217"/>
+      <c r="AJ93" s="217"/>
+      <c r="AK93" s="218"/>
+      <c r="AL93" s="223"/>
+      <c r="AM93" s="217"/>
+      <c r="AN93" s="217"/>
+      <c r="AO93" s="218"/>
+      <c r="AP93" s="223"/>
+      <c r="AQ93" s="217"/>
+      <c r="AR93" s="217"/>
+      <c r="AS93" s="217"/>
+      <c r="AT93" s="217"/>
+      <c r="AU93" s="218"/>
+      <c r="AV93" s="224"/>
+      <c r="AW93" s="225"/>
+      <c r="AX93" s="224"/>
+      <c r="AY93" s="225"/>
+      <c r="AZ93" s="223"/>
+      <c r="BA93" s="217"/>
+      <c r="BB93" s="217"/>
+      <c r="BC93" s="217"/>
+      <c r="BD93" s="226"/>
     </row>
     <row r="94" spans="2:56" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="143" t="s">
+      <c r="C94" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="D94" s="144"/>
-      <c r="E94" s="144"/>
-      <c r="F94" s="144"/>
-      <c r="G94" s="144"/>
-      <c r="H94" s="144"/>
-      <c r="I94" s="144"/>
-      <c r="J94" s="144"/>
-      <c r="K94" s="144"/>
-      <c r="L94" s="144"/>
-      <c r="M94" s="144"/>
-      <c r="N94" s="144"/>
-      <c r="O94" s="144"/>
-      <c r="P94" s="144"/>
-      <c r="Q94" s="144"/>
-      <c r="R94" s="144"/>
-      <c r="S94" s="144"/>
-      <c r="T94" s="144"/>
-      <c r="U94" s="144"/>
-      <c r="V94" s="144"/>
-      <c r="W94" s="144"/>
-      <c r="X94" s="144"/>
-      <c r="Y94" s="144"/>
-      <c r="Z94" s="144"/>
-      <c r="AA94" s="144"/>
-      <c r="AB94" s="145" t="s">
+      <c r="D94" s="250"/>
+      <c r="E94" s="250"/>
+      <c r="F94" s="250"/>
+      <c r="G94" s="250"/>
+      <c r="H94" s="250"/>
+      <c r="I94" s="250"/>
+      <c r="J94" s="250"/>
+      <c r="K94" s="250"/>
+      <c r="L94" s="250"/>
+      <c r="M94" s="250"/>
+      <c r="N94" s="250"/>
+      <c r="O94" s="250"/>
+      <c r="P94" s="250"/>
+      <c r="Q94" s="250"/>
+      <c r="R94" s="250"/>
+      <c r="S94" s="250"/>
+      <c r="T94" s="250"/>
+      <c r="U94" s="250"/>
+      <c r="V94" s="250"/>
+      <c r="W94" s="250"/>
+      <c r="X94" s="250"/>
+      <c r="Y94" s="250"/>
+      <c r="Z94" s="250"/>
+      <c r="AA94" s="250"/>
+      <c r="AB94" s="251" t="s">
         <v>79</v>
       </c>
-      <c r="AC94" s="144"/>
-      <c r="AD94" s="144"/>
-      <c r="AE94" s="144"/>
-      <c r="AF94" s="144"/>
-      <c r="AG94" s="144"/>
-      <c r="AH94" s="144"/>
-      <c r="AI94" s="144"/>
-      <c r="AJ94" s="144"/>
-      <c r="AK94" s="144"/>
-      <c r="AL94" s="144"/>
-      <c r="AM94" s="144"/>
-      <c r="AN94" s="144"/>
-      <c r="AO94" s="144"/>
-      <c r="AP94" s="144"/>
-      <c r="AQ94" s="144"/>
-      <c r="AR94" s="144"/>
-      <c r="AS94" s="144"/>
-      <c r="AT94" s="144"/>
-      <c r="AU94" s="144"/>
-      <c r="AV94" s="144"/>
-      <c r="AW94" s="144"/>
-      <c r="AX94" s="144"/>
-      <c r="AY94" s="144"/>
-      <c r="AZ94" s="144"/>
-      <c r="BA94" s="144"/>
-      <c r="BB94" s="144"/>
-      <c r="BC94" s="144"/>
-      <c r="BD94" s="146"/>
+      <c r="AC94" s="250"/>
+      <c r="AD94" s="250"/>
+      <c r="AE94" s="250"/>
+      <c r="AF94" s="250"/>
+      <c r="AG94" s="250"/>
+      <c r="AH94" s="250"/>
+      <c r="AI94" s="250"/>
+      <c r="AJ94" s="250"/>
+      <c r="AK94" s="250"/>
+      <c r="AL94" s="250"/>
+      <c r="AM94" s="250"/>
+      <c r="AN94" s="250"/>
+      <c r="AO94" s="250"/>
+      <c r="AP94" s="250"/>
+      <c r="AQ94" s="250"/>
+      <c r="AR94" s="250"/>
+      <c r="AS94" s="250"/>
+      <c r="AT94" s="250"/>
+      <c r="AU94" s="250"/>
+      <c r="AV94" s="250"/>
+      <c r="AW94" s="250"/>
+      <c r="AX94" s="250"/>
+      <c r="AY94" s="250"/>
+      <c r="AZ94" s="250"/>
+      <c r="BA94" s="250"/>
+      <c r="BB94" s="250"/>
+      <c r="BC94" s="250"/>
+      <c r="BD94" s="252"/>
     </row>
     <row r="95" spans="2:56" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C95" s="147" t="s">
+      <c r="C95" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="D95" s="148"/>
-      <c r="E95" s="148"/>
-      <c r="F95" s="148"/>
-      <c r="G95" s="148"/>
-      <c r="H95" s="148"/>
-      <c r="I95" s="148"/>
-      <c r="J95" s="148"/>
-      <c r="K95" s="148"/>
-      <c r="L95" s="148"/>
-      <c r="M95" s="148"/>
-      <c r="N95" s="148"/>
-      <c r="O95" s="148"/>
-      <c r="P95" s="148"/>
-      <c r="Q95" s="149" t="s">
+      <c r="D95" s="254"/>
+      <c r="E95" s="254"/>
+      <c r="F95" s="254"/>
+      <c r="G95" s="254"/>
+      <c r="H95" s="254"/>
+      <c r="I95" s="254"/>
+      <c r="J95" s="254"/>
+      <c r="K95" s="254"/>
+      <c r="L95" s="254"/>
+      <c r="M95" s="254"/>
+      <c r="N95" s="254"/>
+      <c r="O95" s="254"/>
+      <c r="P95" s="254"/>
+      <c r="Q95" s="255" t="s">
         <v>81</v>
       </c>
-      <c r="R95" s="150"/>
-      <c r="S95" s="150"/>
-      <c r="T95" s="150"/>
-      <c r="U95" s="150"/>
-      <c r="V95" s="150"/>
-      <c r="W95" s="150"/>
-      <c r="X95" s="150"/>
-      <c r="Y95" s="150"/>
-      <c r="Z95" s="150"/>
-      <c r="AA95" s="150"/>
-      <c r="AB95" s="151" t="s">
+      <c r="R95" s="256"/>
+      <c r="S95" s="256"/>
+      <c r="T95" s="256"/>
+      <c r="U95" s="256"/>
+      <c r="V95" s="256"/>
+      <c r="W95" s="256"/>
+      <c r="X95" s="256"/>
+      <c r="Y95" s="256"/>
+      <c r="Z95" s="256"/>
+      <c r="AA95" s="256"/>
+      <c r="AB95" s="257" t="s">
         <v>82</v>
       </c>
-      <c r="AC95" s="152"/>
-      <c r="AD95" s="152"/>
-      <c r="AE95" s="152"/>
-      <c r="AF95" s="152"/>
-      <c r="AG95" s="152"/>
-      <c r="AH95" s="152"/>
-      <c r="AI95" s="152"/>
-      <c r="AJ95" s="152"/>
-      <c r="AK95" s="152"/>
-      <c r="AL95" s="152"/>
-      <c r="AM95" s="152"/>
-      <c r="AN95" s="152"/>
-      <c r="AO95" s="152"/>
-      <c r="AP95" s="152"/>
-      <c r="AQ95" s="152"/>
-      <c r="AR95" s="152"/>
-      <c r="AS95" s="152"/>
-      <c r="AT95" s="152"/>
-      <c r="AU95" s="152"/>
-      <c r="AV95" s="152"/>
-      <c r="AW95" s="152"/>
-      <c r="AX95" s="152"/>
-      <c r="AY95" s="152"/>
-      <c r="AZ95" s="152"/>
-      <c r="BA95" s="152"/>
-      <c r="BB95" s="152"/>
-      <c r="BC95" s="152"/>
-      <c r="BD95" s="153"/>
+      <c r="AC95" s="258"/>
+      <c r="AD95" s="258"/>
+      <c r="AE95" s="258"/>
+      <c r="AF95" s="258"/>
+      <c r="AG95" s="258"/>
+      <c r="AH95" s="258"/>
+      <c r="AI95" s="258"/>
+      <c r="AJ95" s="258"/>
+      <c r="AK95" s="258"/>
+      <c r="AL95" s="258"/>
+      <c r="AM95" s="258"/>
+      <c r="AN95" s="258"/>
+      <c r="AO95" s="258"/>
+      <c r="AP95" s="258"/>
+      <c r="AQ95" s="258"/>
+      <c r="AR95" s="258"/>
+      <c r="AS95" s="258"/>
+      <c r="AT95" s="258"/>
+      <c r="AU95" s="258"/>
+      <c r="AV95" s="258"/>
+      <c r="AW95" s="258"/>
+      <c r="AX95" s="258"/>
+      <c r="AY95" s="258"/>
+      <c r="AZ95" s="258"/>
+      <c r="BA95" s="258"/>
+      <c r="BB95" s="258"/>
+      <c r="BC95" s="258"/>
+      <c r="BD95" s="259"/>
     </row>
     <row r="96" spans="2:56" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C96" s="154" t="s">
+      <c r="C96" s="260" t="s">
         <v>83</v>
       </c>
-      <c r="D96" s="155"/>
-      <c r="E96" s="155"/>
-      <c r="F96" s="155"/>
-      <c r="G96" s="155"/>
-      <c r="H96" s="155"/>
-      <c r="I96" s="155"/>
-      <c r="J96" s="155"/>
-      <c r="K96" s="155"/>
-      <c r="L96" s="155"/>
-      <c r="M96" s="155"/>
-      <c r="N96" s="155"/>
-      <c r="O96" s="155"/>
-      <c r="P96" s="155"/>
-      <c r="Q96" s="155" t="s">
+      <c r="D96" s="261"/>
+      <c r="E96" s="261"/>
+      <c r="F96" s="261"/>
+      <c r="G96" s="261"/>
+      <c r="H96" s="261"/>
+      <c r="I96" s="261"/>
+      <c r="J96" s="261"/>
+      <c r="K96" s="261"/>
+      <c r="L96" s="261"/>
+      <c r="M96" s="261"/>
+      <c r="N96" s="261"/>
+      <c r="O96" s="261"/>
+      <c r="P96" s="261"/>
+      <c r="Q96" s="261" t="s">
         <v>84</v>
       </c>
-      <c r="R96" s="155"/>
-      <c r="S96" s="155"/>
-      <c r="T96" s="155"/>
-      <c r="U96" s="155"/>
-      <c r="V96" s="155"/>
-      <c r="W96" s="155"/>
-      <c r="X96" s="155"/>
-      <c r="Y96" s="155"/>
-      <c r="Z96" s="155"/>
-      <c r="AA96" s="155"/>
-      <c r="AB96" s="156" t="s">
+      <c r="R96" s="261"/>
+      <c r="S96" s="261"/>
+      <c r="T96" s="261"/>
+      <c r="U96" s="261"/>
+      <c r="V96" s="261"/>
+      <c r="W96" s="261"/>
+      <c r="X96" s="261"/>
+      <c r="Y96" s="261"/>
+      <c r="Z96" s="261"/>
+      <c r="AA96" s="261"/>
+      <c r="AB96" s="262" t="s">
         <v>85</v>
       </c>
-      <c r="AC96" s="156"/>
-      <c r="AD96" s="156"/>
-      <c r="AE96" s="156"/>
-      <c r="AF96" s="156"/>
-      <c r="AG96" s="156"/>
-      <c r="AH96" s="156"/>
-      <c r="AI96" s="156"/>
-      <c r="AJ96" s="156"/>
-      <c r="AK96" s="156"/>
-      <c r="AL96" s="156"/>
-      <c r="AM96" s="156"/>
-      <c r="AN96" s="156"/>
-      <c r="AO96" s="156"/>
-      <c r="AP96" s="156"/>
-      <c r="AQ96" s="156"/>
-      <c r="AR96" s="156"/>
-      <c r="AS96" s="156"/>
-      <c r="AT96" s="156"/>
-      <c r="AU96" s="156"/>
-      <c r="AV96" s="156"/>
-      <c r="AW96" s="156"/>
-      <c r="AX96" s="156"/>
-      <c r="AY96" s="156"/>
-      <c r="AZ96" s="156"/>
-      <c r="BA96" s="156"/>
-      <c r="BB96" s="156"/>
-      <c r="BC96" s="156"/>
-      <c r="BD96" s="157"/>
+      <c r="AC96" s="262"/>
+      <c r="AD96" s="262"/>
+      <c r="AE96" s="262"/>
+      <c r="AF96" s="262"/>
+      <c r="AG96" s="262"/>
+      <c r="AH96" s="262"/>
+      <c r="AI96" s="262"/>
+      <c r="AJ96" s="262"/>
+      <c r="AK96" s="262"/>
+      <c r="AL96" s="262"/>
+      <c r="AM96" s="262"/>
+      <c r="AN96" s="262"/>
+      <c r="AO96" s="262"/>
+      <c r="AP96" s="262"/>
+      <c r="AQ96" s="262"/>
+      <c r="AR96" s="262"/>
+      <c r="AS96" s="262"/>
+      <c r="AT96" s="262"/>
+      <c r="AU96" s="262"/>
+      <c r="AV96" s="262"/>
+      <c r="AW96" s="262"/>
+      <c r="AX96" s="262"/>
+      <c r="AY96" s="262"/>
+      <c r="AZ96" s="262"/>
+      <c r="BA96" s="262"/>
+      <c r="BB96" s="262"/>
+      <c r="BC96" s="262"/>
+      <c r="BD96" s="263"/>
     </row>
     <row r="97" spans="3:56" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="128" t="s">
+      <c r="C97" s="233" t="s">
         <v>86</v>
       </c>
-      <c r="D97" s="129"/>
-      <c r="E97" s="129"/>
-      <c r="F97" s="129"/>
-      <c r="G97" s="129"/>
-      <c r="H97" s="129"/>
-      <c r="I97" s="129"/>
-      <c r="J97" s="129"/>
-      <c r="K97" s="129"/>
-      <c r="L97" s="129"/>
-      <c r="M97" s="129"/>
-      <c r="N97" s="129"/>
-      <c r="O97" s="129"/>
-      <c r="P97" s="129"/>
-      <c r="Q97" s="130"/>
-      <c r="R97" s="131"/>
-      <c r="S97" s="131"/>
-      <c r="T97" s="131"/>
-      <c r="U97" s="131"/>
-      <c r="V97" s="131"/>
-      <c r="W97" s="131"/>
-      <c r="X97" s="131"/>
-      <c r="Y97" s="131"/>
-      <c r="Z97" s="131"/>
-      <c r="AA97" s="132"/>
-      <c r="AB97" s="133" t="s">
+      <c r="D97" s="234"/>
+      <c r="E97" s="234"/>
+      <c r="F97" s="234"/>
+      <c r="G97" s="234"/>
+      <c r="H97" s="234"/>
+      <c r="I97" s="234"/>
+      <c r="J97" s="234"/>
+      <c r="K97" s="234"/>
+      <c r="L97" s="234"/>
+      <c r="M97" s="234"/>
+      <c r="N97" s="234"/>
+      <c r="O97" s="234"/>
+      <c r="P97" s="234"/>
+      <c r="Q97" s="235"/>
+      <c r="R97" s="236"/>
+      <c r="S97" s="236"/>
+      <c r="T97" s="236"/>
+      <c r="U97" s="236"/>
+      <c r="V97" s="236"/>
+      <c r="W97" s="236"/>
+      <c r="X97" s="236"/>
+      <c r="Y97" s="236"/>
+      <c r="Z97" s="236"/>
+      <c r="AA97" s="237"/>
+      <c r="AB97" s="238" t="s">
         <v>87</v>
       </c>
-      <c r="AC97" s="133"/>
-      <c r="AD97" s="133"/>
-      <c r="AE97" s="133"/>
-      <c r="AF97" s="133"/>
-      <c r="AG97" s="133"/>
-      <c r="AH97" s="133"/>
-      <c r="AI97" s="133"/>
-      <c r="AJ97" s="133"/>
-      <c r="AK97" s="133"/>
-      <c r="AL97" s="133"/>
-      <c r="AM97" s="133"/>
-      <c r="AN97" s="133"/>
-      <c r="AO97" s="133"/>
-      <c r="AP97" s="133"/>
-      <c r="AQ97" s="133"/>
-      <c r="AR97" s="133"/>
-      <c r="AS97" s="133"/>
-      <c r="AT97" s="133"/>
-      <c r="AU97" s="133"/>
-      <c r="AV97" s="133"/>
-      <c r="AW97" s="133"/>
-      <c r="AX97" s="133"/>
-      <c r="AY97" s="133"/>
-      <c r="AZ97" s="133"/>
-      <c r="BA97" s="133"/>
-      <c r="BB97" s="133"/>
-      <c r="BC97" s="133"/>
-      <c r="BD97" s="134"/>
+      <c r="AC97" s="238"/>
+      <c r="AD97" s="238"/>
+      <c r="AE97" s="238"/>
+      <c r="AF97" s="238"/>
+      <c r="AG97" s="238"/>
+      <c r="AH97" s="238"/>
+      <c r="AI97" s="238"/>
+      <c r="AJ97" s="238"/>
+      <c r="AK97" s="238"/>
+      <c r="AL97" s="238"/>
+      <c r="AM97" s="238"/>
+      <c r="AN97" s="238"/>
+      <c r="AO97" s="238"/>
+      <c r="AP97" s="238"/>
+      <c r="AQ97" s="238"/>
+      <c r="AR97" s="238"/>
+      <c r="AS97" s="238"/>
+      <c r="AT97" s="238"/>
+      <c r="AU97" s="238"/>
+      <c r="AV97" s="238"/>
+      <c r="AW97" s="238"/>
+      <c r="AX97" s="238"/>
+      <c r="AY97" s="238"/>
+      <c r="AZ97" s="238"/>
+      <c r="BA97" s="238"/>
+      <c r="BB97" s="238"/>
+      <c r="BC97" s="238"/>
+      <c r="BD97" s="239"/>
     </row>
     <row r="98" spans="3:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C98" s="102"/>
-      <c r="D98" s="109" t="s">
+      <c r="D98" s="240" t="s">
         <v>88</v>
       </c>
-      <c r="E98" s="109"/>
-      <c r="F98" s="109"/>
-      <c r="G98" s="109"/>
-      <c r="H98" s="109"/>
-      <c r="I98" s="109"/>
-      <c r="J98" s="109"/>
-      <c r="K98" s="109"/>
-      <c r="L98" s="109"/>
-      <c r="M98" s="109"/>
-      <c r="N98" s="109"/>
-      <c r="O98" s="109"/>
-      <c r="P98" s="109"/>
-      <c r="Q98" s="109"/>
-      <c r="R98" s="109"/>
-      <c r="S98" s="109"/>
-      <c r="T98" s="109"/>
-      <c r="U98" s="109"/>
-      <c r="V98" s="109"/>
-      <c r="W98" s="109"/>
-      <c r="X98" s="109"/>
-      <c r="Y98" s="109"/>
-      <c r="Z98" s="109"/>
-      <c r="AA98" s="109"/>
-      <c r="AB98" s="109"/>
-      <c r="AC98" s="109"/>
-      <c r="AD98" s="109"/>
-      <c r="AE98" s="109"/>
-      <c r="AF98" s="109"/>
-      <c r="AG98" s="109"/>
-      <c r="AH98" s="109"/>
-      <c r="AI98" s="109"/>
-      <c r="AJ98" s="109"/>
-      <c r="AK98" s="109"/>
-      <c r="AL98" s="109"/>
-      <c r="AM98" s="109"/>
-      <c r="AN98" s="109"/>
-      <c r="AO98" s="109"/>
-      <c r="AP98" s="109"/>
-      <c r="AQ98" s="109"/>
-      <c r="AR98" s="109"/>
-      <c r="AS98" s="109"/>
-      <c r="AT98" s="109"/>
-      <c r="AU98" s="109"/>
-      <c r="AV98" s="109"/>
-      <c r="AW98" s="109"/>
-      <c r="AX98" s="109"/>
+      <c r="E98" s="240"/>
+      <c r="F98" s="240"/>
+      <c r="G98" s="240"/>
+      <c r="H98" s="240"/>
+      <c r="I98" s="240"/>
+      <c r="J98" s="240"/>
+      <c r="K98" s="240"/>
+      <c r="L98" s="240"/>
+      <c r="M98" s="240"/>
+      <c r="N98" s="240"/>
+      <c r="O98" s="240"/>
+      <c r="P98" s="240"/>
+      <c r="Q98" s="240"/>
+      <c r="R98" s="240"/>
+      <c r="S98" s="240"/>
+      <c r="T98" s="240"/>
+      <c r="U98" s="240"/>
+      <c r="V98" s="240"/>
+      <c r="W98" s="240"/>
+      <c r="X98" s="240"/>
+      <c r="Y98" s="240"/>
+      <c r="Z98" s="240"/>
+      <c r="AA98" s="240"/>
+      <c r="AB98" s="240"/>
+      <c r="AC98" s="240"/>
+      <c r="AD98" s="240"/>
+      <c r="AE98" s="240"/>
+      <c r="AF98" s="240"/>
+      <c r="AG98" s="240"/>
+      <c r="AH98" s="240"/>
+      <c r="AI98" s="240"/>
+      <c r="AJ98" s="240"/>
+      <c r="AK98" s="240"/>
+      <c r="AL98" s="240"/>
+      <c r="AM98" s="240"/>
+      <c r="AN98" s="240"/>
+      <c r="AO98" s="240"/>
+      <c r="AP98" s="240"/>
+      <c r="AQ98" s="240"/>
+      <c r="AR98" s="240"/>
+      <c r="AS98" s="240"/>
+      <c r="AT98" s="240"/>
+      <c r="AU98" s="240"/>
+      <c r="AV98" s="240"/>
+      <c r="AW98" s="240"/>
+      <c r="AX98" s="240"/>
       <c r="AY98" s="103"/>
       <c r="AZ98" s="103"/>
       <c r="BA98" s="103"/>
@@ -8786,634 +9406,463 @@
       <c r="BD98" s="104"/>
     </row>
     <row r="99" spans="3:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C99" s="135" t="s">
+      <c r="C99" s="241" t="s">
         <v>89</v>
       </c>
-      <c r="D99" s="136"/>
-      <c r="E99" s="136"/>
-      <c r="F99" s="136"/>
-      <c r="G99" s="136"/>
-      <c r="H99" s="136"/>
-      <c r="I99" s="136"/>
-      <c r="J99" s="136"/>
-      <c r="K99" s="136"/>
-      <c r="L99" s="136"/>
-      <c r="M99" s="136"/>
-      <c r="N99" s="136"/>
-      <c r="O99" s="136"/>
-      <c r="P99" s="136"/>
-      <c r="Q99" s="136"/>
-      <c r="R99" s="136"/>
-      <c r="S99" s="136"/>
-      <c r="T99" s="136"/>
-      <c r="U99" s="136"/>
-      <c r="V99" s="137" t="s">
+      <c r="D99" s="242"/>
+      <c r="E99" s="242"/>
+      <c r="F99" s="242"/>
+      <c r="G99" s="242"/>
+      <c r="H99" s="242"/>
+      <c r="I99" s="242"/>
+      <c r="J99" s="242"/>
+      <c r="K99" s="242"/>
+      <c r="L99" s="242"/>
+      <c r="M99" s="242"/>
+      <c r="N99" s="242"/>
+      <c r="O99" s="242"/>
+      <c r="P99" s="242"/>
+      <c r="Q99" s="242"/>
+      <c r="R99" s="242"/>
+      <c r="S99" s="242"/>
+      <c r="T99" s="242"/>
+      <c r="U99" s="242"/>
+      <c r="V99" s="243" t="s">
         <v>90</v>
       </c>
-      <c r="W99" s="138"/>
-      <c r="X99" s="138"/>
-      <c r="Y99" s="138"/>
-      <c r="Z99" s="138"/>
-      <c r="AA99" s="138"/>
-      <c r="AB99" s="138"/>
-      <c r="AC99" s="138"/>
-      <c r="AD99" s="138"/>
-      <c r="AE99" s="138"/>
-      <c r="AF99" s="138"/>
-      <c r="AG99" s="138"/>
-      <c r="AH99" s="138"/>
-      <c r="AI99" s="138"/>
-      <c r="AJ99" s="138"/>
-      <c r="AK99" s="138"/>
-      <c r="AL99" s="138"/>
-      <c r="AM99" s="139"/>
-      <c r="AN99" s="140" t="s">
+      <c r="W99" s="244"/>
+      <c r="X99" s="244"/>
+      <c r="Y99" s="244"/>
+      <c r="Z99" s="244"/>
+      <c r="AA99" s="244"/>
+      <c r="AB99" s="244"/>
+      <c r="AC99" s="244"/>
+      <c r="AD99" s="244"/>
+      <c r="AE99" s="244"/>
+      <c r="AF99" s="244"/>
+      <c r="AG99" s="244"/>
+      <c r="AH99" s="244"/>
+      <c r="AI99" s="244"/>
+      <c r="AJ99" s="244"/>
+      <c r="AK99" s="244"/>
+      <c r="AL99" s="244"/>
+      <c r="AM99" s="245"/>
+      <c r="AN99" s="246" t="s">
         <v>91</v>
       </c>
-      <c r="AO99" s="141"/>
-      <c r="AP99" s="141"/>
-      <c r="AQ99" s="141"/>
-      <c r="AR99" s="141"/>
-      <c r="AS99" s="141"/>
-      <c r="AT99" s="141"/>
-      <c r="AU99" s="141"/>
-      <c r="AV99" s="141"/>
-      <c r="AW99" s="141"/>
-      <c r="AX99" s="141"/>
-      <c r="AY99" s="141"/>
-      <c r="AZ99" s="141"/>
-      <c r="BA99" s="141"/>
-      <c r="BB99" s="141"/>
-      <c r="BC99" s="141"/>
-      <c r="BD99" s="142"/>
+      <c r="AO99" s="247"/>
+      <c r="AP99" s="247"/>
+      <c r="AQ99" s="247"/>
+      <c r="AR99" s="247"/>
+      <c r="AS99" s="247"/>
+      <c r="AT99" s="247"/>
+      <c r="AU99" s="247"/>
+      <c r="AV99" s="247"/>
+      <c r="AW99" s="247"/>
+      <c r="AX99" s="247"/>
+      <c r="AY99" s="247"/>
+      <c r="AZ99" s="247"/>
+      <c r="BA99" s="247"/>
+      <c r="BB99" s="247"/>
+      <c r="BC99" s="247"/>
+      <c r="BD99" s="248"/>
     </row>
     <row r="100" spans="3:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C100" s="117" t="s">
+      <c r="C100" s="264" t="s">
         <v>92</v>
       </c>
-      <c r="D100" s="118"/>
-      <c r="E100" s="118"/>
-      <c r="F100" s="118"/>
-      <c r="G100" s="118"/>
-      <c r="H100" s="118"/>
-      <c r="I100" s="118"/>
-      <c r="J100" s="118"/>
-      <c r="K100" s="119"/>
-      <c r="L100" s="120" t="s">
+      <c r="D100" s="265"/>
+      <c r="E100" s="265"/>
+      <c r="F100" s="265"/>
+      <c r="G100" s="265"/>
+      <c r="H100" s="265"/>
+      <c r="I100" s="265"/>
+      <c r="J100" s="265"/>
+      <c r="K100" s="266"/>
+      <c r="L100" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="M100" s="118"/>
-      <c r="N100" s="118"/>
-      <c r="O100" s="118"/>
-      <c r="P100" s="118"/>
-      <c r="Q100" s="118"/>
-      <c r="R100" s="119"/>
-      <c r="S100" s="120" t="s">
+      <c r="M100" s="265"/>
+      <c r="N100" s="265"/>
+      <c r="O100" s="265"/>
+      <c r="P100" s="265"/>
+      <c r="Q100" s="265"/>
+      <c r="R100" s="266"/>
+      <c r="S100" s="267" t="s">
         <v>94</v>
       </c>
-      <c r="T100" s="118"/>
-      <c r="U100" s="118"/>
-      <c r="V100" s="117" t="s">
+      <c r="T100" s="265"/>
+      <c r="U100" s="265"/>
+      <c r="V100" s="264" t="s">
         <v>92</v>
       </c>
-      <c r="W100" s="118"/>
-      <c r="X100" s="118"/>
-      <c r="Y100" s="118"/>
-      <c r="Z100" s="118"/>
-      <c r="AA100" s="118"/>
-      <c r="AB100" s="118"/>
-      <c r="AC100" s="119"/>
-      <c r="AD100" s="120" t="s">
+      <c r="W100" s="265"/>
+      <c r="X100" s="265"/>
+      <c r="Y100" s="265"/>
+      <c r="Z100" s="265"/>
+      <c r="AA100" s="265"/>
+      <c r="AB100" s="265"/>
+      <c r="AC100" s="266"/>
+      <c r="AD100" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="AE100" s="118"/>
-      <c r="AF100" s="118"/>
-      <c r="AG100" s="118"/>
-      <c r="AH100" s="119"/>
-      <c r="AI100" s="120" t="s">
+      <c r="AE100" s="265"/>
+      <c r="AF100" s="265"/>
+      <c r="AG100" s="265"/>
+      <c r="AH100" s="266"/>
+      <c r="AI100" s="267" t="s">
         <v>94</v>
       </c>
-      <c r="AJ100" s="118"/>
-      <c r="AK100" s="118"/>
-      <c r="AL100" s="118"/>
-      <c r="AM100" s="124"/>
-      <c r="AN100" s="117" t="s">
+      <c r="AJ100" s="265"/>
+      <c r="AK100" s="265"/>
+      <c r="AL100" s="265"/>
+      <c r="AM100" s="268"/>
+      <c r="AN100" s="264" t="s">
         <v>92</v>
       </c>
-      <c r="AO100" s="118"/>
-      <c r="AP100" s="118"/>
-      <c r="AQ100" s="118"/>
-      <c r="AR100" s="118"/>
-      <c r="AS100" s="118"/>
-      <c r="AT100" s="118"/>
-      <c r="AU100" s="119"/>
-      <c r="AV100" s="120" t="s">
+      <c r="AO100" s="265"/>
+      <c r="AP100" s="265"/>
+      <c r="AQ100" s="265"/>
+      <c r="AR100" s="265"/>
+      <c r="AS100" s="265"/>
+      <c r="AT100" s="265"/>
+      <c r="AU100" s="266"/>
+      <c r="AV100" s="267" t="s">
         <v>93</v>
       </c>
-      <c r="AW100" s="118"/>
-      <c r="AX100" s="118"/>
-      <c r="AY100" s="118"/>
-      <c r="AZ100" s="119"/>
-      <c r="BA100" s="120" t="s">
+      <c r="AW100" s="265"/>
+      <c r="AX100" s="265"/>
+      <c r="AY100" s="265"/>
+      <c r="AZ100" s="266"/>
+      <c r="BA100" s="267" t="s">
         <v>94</v>
       </c>
-      <c r="BB100" s="118"/>
-      <c r="BC100" s="118"/>
-      <c r="BD100" s="124"/>
+      <c r="BB100" s="265"/>
+      <c r="BC100" s="265"/>
+      <c r="BD100" s="268"/>
     </row>
     <row r="101" spans="3:56" ht="21.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C101" s="117"/>
-      <c r="D101" s="118"/>
-      <c r="E101" s="118"/>
-      <c r="F101" s="118"/>
-      <c r="G101" s="118"/>
-      <c r="H101" s="118"/>
-      <c r="I101" s="118"/>
-      <c r="J101" s="118"/>
-      <c r="K101" s="119"/>
-      <c r="L101" s="120"/>
-      <c r="M101" s="118"/>
-      <c r="N101" s="118"/>
-      <c r="O101" s="118"/>
-      <c r="P101" s="118"/>
-      <c r="Q101" s="118"/>
-      <c r="R101" s="119"/>
-      <c r="S101" s="120"/>
-      <c r="T101" s="118"/>
-      <c r="U101" s="118"/>
-      <c r="V101" s="117"/>
-      <c r="W101" s="118"/>
-      <c r="X101" s="118"/>
-      <c r="Y101" s="118"/>
-      <c r="Z101" s="118"/>
-      <c r="AA101" s="118"/>
-      <c r="AB101" s="118"/>
-      <c r="AC101" s="119"/>
-      <c r="AD101" s="121"/>
-      <c r="AE101" s="122"/>
-      <c r="AF101" s="122"/>
-      <c r="AG101" s="122"/>
-      <c r="AH101" s="123"/>
-      <c r="AI101" s="120"/>
-      <c r="AJ101" s="118"/>
-      <c r="AK101" s="118"/>
-      <c r="AL101" s="118"/>
-      <c r="AM101" s="124"/>
-      <c r="AN101" s="125"/>
-      <c r="AO101" s="115"/>
-      <c r="AP101" s="115"/>
-      <c r="AQ101" s="115"/>
-      <c r="AR101" s="115"/>
-      <c r="AS101" s="115"/>
-      <c r="AT101" s="115"/>
-      <c r="AU101" s="115"/>
-      <c r="AV101" s="126"/>
-      <c r="AW101" s="115"/>
-      <c r="AX101" s="115"/>
-      <c r="AY101" s="115"/>
-      <c r="AZ101" s="127"/>
-      <c r="BA101" s="115"/>
-      <c r="BB101" s="115"/>
-      <c r="BC101" s="115"/>
-      <c r="BD101" s="116"/>
+      <c r="C101" s="264"/>
+      <c r="D101" s="265"/>
+      <c r="E101" s="265"/>
+      <c r="F101" s="265"/>
+      <c r="G101" s="265"/>
+      <c r="H101" s="265"/>
+      <c r="I101" s="265"/>
+      <c r="J101" s="265"/>
+      <c r="K101" s="266"/>
+      <c r="L101" s="267"/>
+      <c r="M101" s="265"/>
+      <c r="N101" s="265"/>
+      <c r="O101" s="265"/>
+      <c r="P101" s="265"/>
+      <c r="Q101" s="265"/>
+      <c r="R101" s="266"/>
+      <c r="S101" s="267"/>
+      <c r="T101" s="265"/>
+      <c r="U101" s="265"/>
+      <c r="V101" s="264"/>
+      <c r="W101" s="265"/>
+      <c r="X101" s="265"/>
+      <c r="Y101" s="265"/>
+      <c r="Z101" s="265"/>
+      <c r="AA101" s="265"/>
+      <c r="AB101" s="265"/>
+      <c r="AC101" s="266"/>
+      <c r="AD101" s="269"/>
+      <c r="AE101" s="270"/>
+      <c r="AF101" s="270"/>
+      <c r="AG101" s="270"/>
+      <c r="AH101" s="271"/>
+      <c r="AI101" s="267"/>
+      <c r="AJ101" s="265"/>
+      <c r="AK101" s="265"/>
+      <c r="AL101" s="265"/>
+      <c r="AM101" s="268"/>
+      <c r="AN101" s="272"/>
+      <c r="AO101" s="273"/>
+      <c r="AP101" s="273"/>
+      <c r="AQ101" s="273"/>
+      <c r="AR101" s="273"/>
+      <c r="AS101" s="273"/>
+      <c r="AT101" s="273"/>
+      <c r="AU101" s="273"/>
+      <c r="AV101" s="274"/>
+      <c r="AW101" s="273"/>
+      <c r="AX101" s="273"/>
+      <c r="AY101" s="273"/>
+      <c r="AZ101" s="275"/>
+      <c r="BA101" s="273"/>
+      <c r="BB101" s="273"/>
+      <c r="BC101" s="273"/>
+      <c r="BD101" s="276"/>
     </row>
     <row r="102" spans="3:56" ht="21.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C102" s="117"/>
-      <c r="D102" s="118"/>
-      <c r="E102" s="118"/>
-      <c r="F102" s="118"/>
-      <c r="G102" s="118"/>
-      <c r="H102" s="118"/>
-      <c r="I102" s="118"/>
-      <c r="J102" s="118"/>
-      <c r="K102" s="119"/>
-      <c r="L102" s="120"/>
-      <c r="M102" s="118"/>
-      <c r="N102" s="118"/>
-      <c r="O102" s="118"/>
-      <c r="P102" s="118"/>
-      <c r="Q102" s="118"/>
-      <c r="R102" s="119"/>
-      <c r="S102" s="120"/>
-      <c r="T102" s="118"/>
-      <c r="U102" s="118"/>
-      <c r="V102" s="117"/>
-      <c r="W102" s="118"/>
-      <c r="X102" s="118"/>
-      <c r="Y102" s="118"/>
-      <c r="Z102" s="118"/>
-      <c r="AA102" s="118"/>
-      <c r="AB102" s="118"/>
-      <c r="AC102" s="119"/>
-      <c r="AD102" s="121"/>
-      <c r="AE102" s="122"/>
-      <c r="AF102" s="122"/>
-      <c r="AG102" s="122"/>
-      <c r="AH102" s="123"/>
-      <c r="AI102" s="120"/>
-      <c r="AJ102" s="118"/>
-      <c r="AK102" s="118"/>
-      <c r="AL102" s="118"/>
-      <c r="AM102" s="124"/>
-      <c r="AN102" s="125"/>
-      <c r="AO102" s="115"/>
-      <c r="AP102" s="115"/>
-      <c r="AQ102" s="115"/>
-      <c r="AR102" s="115"/>
-      <c r="AS102" s="115"/>
-      <c r="AT102" s="115"/>
-      <c r="AU102" s="115"/>
-      <c r="AV102" s="126"/>
-      <c r="AW102" s="115"/>
-      <c r="AX102" s="115"/>
-      <c r="AY102" s="115"/>
-      <c r="AZ102" s="127"/>
-      <c r="BA102" s="115"/>
-      <c r="BB102" s="115"/>
-      <c r="BC102" s="115"/>
-      <c r="BD102" s="116"/>
+      <c r="C102" s="264"/>
+      <c r="D102" s="265"/>
+      <c r="E102" s="265"/>
+      <c r="F102" s="265"/>
+      <c r="G102" s="265"/>
+      <c r="H102" s="265"/>
+      <c r="I102" s="265"/>
+      <c r="J102" s="265"/>
+      <c r="K102" s="266"/>
+      <c r="L102" s="267"/>
+      <c r="M102" s="265"/>
+      <c r="N102" s="265"/>
+      <c r="O102" s="265"/>
+      <c r="P102" s="265"/>
+      <c r="Q102" s="265"/>
+      <c r="R102" s="266"/>
+      <c r="S102" s="267"/>
+      <c r="T102" s="265"/>
+      <c r="U102" s="265"/>
+      <c r="V102" s="264"/>
+      <c r="W102" s="265"/>
+      <c r="X102" s="265"/>
+      <c r="Y102" s="265"/>
+      <c r="Z102" s="265"/>
+      <c r="AA102" s="265"/>
+      <c r="AB102" s="265"/>
+      <c r="AC102" s="266"/>
+      <c r="AD102" s="269"/>
+      <c r="AE102" s="270"/>
+      <c r="AF102" s="270"/>
+      <c r="AG102" s="270"/>
+      <c r="AH102" s="271"/>
+      <c r="AI102" s="267"/>
+      <c r="AJ102" s="265"/>
+      <c r="AK102" s="265"/>
+      <c r="AL102" s="265"/>
+      <c r="AM102" s="268"/>
+      <c r="AN102" s="272"/>
+      <c r="AO102" s="273"/>
+      <c r="AP102" s="273"/>
+      <c r="AQ102" s="273"/>
+      <c r="AR102" s="273"/>
+      <c r="AS102" s="273"/>
+      <c r="AT102" s="273"/>
+      <c r="AU102" s="273"/>
+      <c r="AV102" s="274"/>
+      <c r="AW102" s="273"/>
+      <c r="AX102" s="273"/>
+      <c r="AY102" s="273"/>
+      <c r="AZ102" s="275"/>
+      <c r="BA102" s="273"/>
+      <c r="BB102" s="273"/>
+      <c r="BC102" s="273"/>
+      <c r="BD102" s="276"/>
     </row>
     <row r="103" spans="3:56" ht="21.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="117"/>
-      <c r="D103" s="118"/>
-      <c r="E103" s="118"/>
-      <c r="F103" s="118"/>
-      <c r="G103" s="118"/>
-      <c r="H103" s="118"/>
-      <c r="I103" s="118"/>
-      <c r="J103" s="118"/>
-      <c r="K103" s="119"/>
-      <c r="L103" s="120"/>
-      <c r="M103" s="118"/>
-      <c r="N103" s="118"/>
-      <c r="O103" s="118"/>
-      <c r="P103" s="118"/>
-      <c r="Q103" s="118"/>
-      <c r="R103" s="119"/>
-      <c r="S103" s="120"/>
-      <c r="T103" s="118"/>
-      <c r="U103" s="118"/>
-      <c r="V103" s="117"/>
-      <c r="W103" s="118"/>
-      <c r="X103" s="118"/>
-      <c r="Y103" s="118"/>
-      <c r="Z103" s="118"/>
-      <c r="AA103" s="118"/>
-      <c r="AB103" s="118"/>
-      <c r="AC103" s="119"/>
-      <c r="AD103" s="121"/>
-      <c r="AE103" s="122"/>
-      <c r="AF103" s="122"/>
-      <c r="AG103" s="122"/>
-      <c r="AH103" s="123"/>
-      <c r="AI103" s="120"/>
-      <c r="AJ103" s="118"/>
-      <c r="AK103" s="118"/>
-      <c r="AL103" s="118"/>
-      <c r="AM103" s="124"/>
-      <c r="AN103" s="125"/>
-      <c r="AO103" s="115"/>
-      <c r="AP103" s="115"/>
-      <c r="AQ103" s="115"/>
-      <c r="AR103" s="115"/>
-      <c r="AS103" s="115"/>
-      <c r="AT103" s="115"/>
-      <c r="AU103" s="115"/>
-      <c r="AV103" s="126"/>
-      <c r="AW103" s="115"/>
-      <c r="AX103" s="115"/>
-      <c r="AY103" s="115"/>
-      <c r="AZ103" s="127"/>
-      <c r="BA103" s="115"/>
-      <c r="BB103" s="115"/>
-      <c r="BC103" s="115"/>
-      <c r="BD103" s="116"/>
+      <c r="C103" s="264"/>
+      <c r="D103" s="265"/>
+      <c r="E103" s="265"/>
+      <c r="F103" s="265"/>
+      <c r="G103" s="265"/>
+      <c r="H103" s="265"/>
+      <c r="I103" s="265"/>
+      <c r="J103" s="265"/>
+      <c r="K103" s="266"/>
+      <c r="L103" s="267"/>
+      <c r="M103" s="265"/>
+      <c r="N103" s="265"/>
+      <c r="O103" s="265"/>
+      <c r="P103" s="265"/>
+      <c r="Q103" s="265"/>
+      <c r="R103" s="266"/>
+      <c r="S103" s="267"/>
+      <c r="T103" s="265"/>
+      <c r="U103" s="265"/>
+      <c r="V103" s="264"/>
+      <c r="W103" s="265"/>
+      <c r="X103" s="265"/>
+      <c r="Y103" s="265"/>
+      <c r="Z103" s="265"/>
+      <c r="AA103" s="265"/>
+      <c r="AB103" s="265"/>
+      <c r="AC103" s="266"/>
+      <c r="AD103" s="269"/>
+      <c r="AE103" s="270"/>
+      <c r="AF103" s="270"/>
+      <c r="AG103" s="270"/>
+      <c r="AH103" s="271"/>
+      <c r="AI103" s="267"/>
+      <c r="AJ103" s="265"/>
+      <c r="AK103" s="265"/>
+      <c r="AL103" s="265"/>
+      <c r="AM103" s="268"/>
+      <c r="AN103" s="272"/>
+      <c r="AO103" s="273"/>
+      <c r="AP103" s="273"/>
+      <c r="AQ103" s="273"/>
+      <c r="AR103" s="273"/>
+      <c r="AS103" s="273"/>
+      <c r="AT103" s="273"/>
+      <c r="AU103" s="273"/>
+      <c r="AV103" s="274"/>
+      <c r="AW103" s="273"/>
+      <c r="AX103" s="273"/>
+      <c r="AY103" s="273"/>
+      <c r="AZ103" s="275"/>
+      <c r="BA103" s="273"/>
+      <c r="BB103" s="273"/>
+      <c r="BC103" s="273"/>
+      <c r="BD103" s="276"/>
     </row>
     <row r="104" spans="3:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C104" s="108" t="s">
+      <c r="C104" s="277" t="s">
         <v>95</v>
       </c>
-      <c r="D104" s="109"/>
-      <c r="E104" s="109"/>
-      <c r="F104" s="109"/>
-      <c r="G104" s="109"/>
-      <c r="H104" s="109"/>
-      <c r="I104" s="109"/>
-      <c r="J104" s="109"/>
-      <c r="K104" s="109"/>
-      <c r="L104" s="109"/>
-      <c r="M104" s="109"/>
-      <c r="N104" s="109"/>
-      <c r="O104" s="109"/>
-      <c r="P104" s="109"/>
-      <c r="Q104" s="109"/>
-      <c r="R104" s="109"/>
-      <c r="S104" s="109"/>
-      <c r="T104" s="109"/>
-      <c r="U104" s="109"/>
-      <c r="V104" s="109"/>
-      <c r="W104" s="109"/>
-      <c r="X104" s="109"/>
-      <c r="Y104" s="109"/>
-      <c r="Z104" s="109"/>
-      <c r="AA104" s="109"/>
-      <c r="AB104" s="109"/>
-      <c r="AC104" s="109"/>
-      <c r="AD104" s="109"/>
-      <c r="AE104" s="109"/>
-      <c r="AF104" s="109"/>
-      <c r="AG104" s="109"/>
-      <c r="AH104" s="109"/>
-      <c r="AI104" s="109"/>
-      <c r="AJ104" s="109"/>
-      <c r="AK104" s="109"/>
-      <c r="AL104" s="109"/>
-      <c r="AM104" s="109"/>
-      <c r="AN104" s="109"/>
-      <c r="AO104" s="109"/>
-      <c r="AP104" s="109"/>
-      <c r="AQ104" s="109"/>
-      <c r="AR104" s="109"/>
-      <c r="AS104" s="109"/>
-      <c r="AT104" s="109"/>
-      <c r="AU104" s="109"/>
-      <c r="AV104" s="109"/>
-      <c r="AW104" s="109"/>
-      <c r="AX104" s="109"/>
-      <c r="AY104" s="109"/>
-      <c r="AZ104" s="109"/>
-      <c r="BA104" s="109"/>
-      <c r="BB104" s="109"/>
-      <c r="BC104" s="109"/>
-      <c r="BD104" s="110"/>
+      <c r="D104" s="240"/>
+      <c r="E104" s="240"/>
+      <c r="F104" s="240"/>
+      <c r="G104" s="240"/>
+      <c r="H104" s="240"/>
+      <c r="I104" s="240"/>
+      <c r="J104" s="240"/>
+      <c r="K104" s="240"/>
+      <c r="L104" s="240"/>
+      <c r="M104" s="240"/>
+      <c r="N104" s="240"/>
+      <c r="O104" s="240"/>
+      <c r="P104" s="240"/>
+      <c r="Q104" s="240"/>
+      <c r="R104" s="240"/>
+      <c r="S104" s="240"/>
+      <c r="T104" s="240"/>
+      <c r="U104" s="240"/>
+      <c r="V104" s="240"/>
+      <c r="W104" s="240"/>
+      <c r="X104" s="240"/>
+      <c r="Y104" s="240"/>
+      <c r="Z104" s="240"/>
+      <c r="AA104" s="240"/>
+      <c r="AB104" s="240"/>
+      <c r="AC104" s="240"/>
+      <c r="AD104" s="240"/>
+      <c r="AE104" s="240"/>
+      <c r="AF104" s="240"/>
+      <c r="AG104" s="240"/>
+      <c r="AH104" s="240"/>
+      <c r="AI104" s="240"/>
+      <c r="AJ104" s="240"/>
+      <c r="AK104" s="240"/>
+      <c r="AL104" s="240"/>
+      <c r="AM104" s="240"/>
+      <c r="AN104" s="240"/>
+      <c r="AO104" s="240"/>
+      <c r="AP104" s="240"/>
+      <c r="AQ104" s="240"/>
+      <c r="AR104" s="240"/>
+      <c r="AS104" s="240"/>
+      <c r="AT104" s="240"/>
+      <c r="AU104" s="240"/>
+      <c r="AV104" s="240"/>
+      <c r="AW104" s="240"/>
+      <c r="AX104" s="240"/>
+      <c r="AY104" s="240"/>
+      <c r="AZ104" s="240"/>
+      <c r="BA104" s="240"/>
+      <c r="BB104" s="240"/>
+      <c r="BC104" s="240"/>
+      <c r="BD104" s="278"/>
     </row>
     <row r="105" spans="3:56" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C105" s="111"/>
-      <c r="D105" s="112"/>
-      <c r="E105" s="112"/>
-      <c r="F105" s="112"/>
-      <c r="G105" s="112"/>
-      <c r="H105" s="112"/>
-      <c r="I105" s="112"/>
-      <c r="J105" s="112"/>
-      <c r="K105" s="112"/>
-      <c r="L105" s="112"/>
-      <c r="M105" s="112"/>
-      <c r="N105" s="112"/>
-      <c r="O105" s="112"/>
-      <c r="P105" s="112"/>
-      <c r="Q105" s="112"/>
-      <c r="R105" s="112"/>
-      <c r="S105" s="112"/>
-      <c r="T105" s="112"/>
-      <c r="U105" s="112"/>
-      <c r="V105" s="112"/>
-      <c r="W105" s="112"/>
-      <c r="X105" s="112"/>
-      <c r="Y105" s="112"/>
-      <c r="Z105" s="112"/>
-      <c r="AA105" s="112"/>
-      <c r="AB105" s="112"/>
-      <c r="AC105" s="112"/>
-      <c r="AD105" s="112"/>
-      <c r="AE105" s="112"/>
-      <c r="AF105" s="112"/>
-      <c r="AG105" s="112"/>
-      <c r="AH105" s="112"/>
-      <c r="AI105" s="112"/>
-      <c r="AJ105" s="112"/>
-      <c r="AK105" s="112"/>
-      <c r="AL105" s="112"/>
-      <c r="AM105" s="112"/>
-      <c r="AN105" s="112"/>
-      <c r="AO105" s="112"/>
-      <c r="AP105" s="112"/>
-      <c r="AQ105" s="112"/>
-      <c r="AR105" s="112"/>
-      <c r="AS105" s="112"/>
-      <c r="AT105" s="112"/>
-      <c r="AU105" s="112"/>
-      <c r="AV105" s="112"/>
-      <c r="AW105" s="112"/>
-      <c r="AX105" s="112"/>
-      <c r="AY105" s="112"/>
-      <c r="AZ105" s="112"/>
-      <c r="BA105" s="112"/>
-      <c r="BB105" s="112"/>
-      <c r="BC105" s="112"/>
-      <c r="BD105" s="113"/>
+      <c r="C105" s="279"/>
+      <c r="D105" s="280"/>
+      <c r="E105" s="280"/>
+      <c r="F105" s="280"/>
+      <c r="G105" s="280"/>
+      <c r="H105" s="280"/>
+      <c r="I105" s="280"/>
+      <c r="J105" s="280"/>
+      <c r="K105" s="280"/>
+      <c r="L105" s="280"/>
+      <c r="M105" s="280"/>
+      <c r="N105" s="280"/>
+      <c r="O105" s="280"/>
+      <c r="P105" s="280"/>
+      <c r="Q105" s="280"/>
+      <c r="R105" s="280"/>
+      <c r="S105" s="280"/>
+      <c r="T105" s="280"/>
+      <c r="U105" s="280"/>
+      <c r="V105" s="280"/>
+      <c r="W105" s="280"/>
+      <c r="X105" s="280"/>
+      <c r="Y105" s="280"/>
+      <c r="Z105" s="280"/>
+      <c r="AA105" s="280"/>
+      <c r="AB105" s="280"/>
+      <c r="AC105" s="280"/>
+      <c r="AD105" s="280"/>
+      <c r="AE105" s="280"/>
+      <c r="AF105" s="280"/>
+      <c r="AG105" s="280"/>
+      <c r="AH105" s="280"/>
+      <c r="AI105" s="280"/>
+      <c r="AJ105" s="280"/>
+      <c r="AK105" s="280"/>
+      <c r="AL105" s="280"/>
+      <c r="AM105" s="280"/>
+      <c r="AN105" s="280"/>
+      <c r="AO105" s="280"/>
+      <c r="AP105" s="280"/>
+      <c r="AQ105" s="280"/>
+      <c r="AR105" s="280"/>
+      <c r="AS105" s="280"/>
+      <c r="AT105" s="280"/>
+      <c r="AU105" s="280"/>
+      <c r="AV105" s="280"/>
+      <c r="AW105" s="280"/>
+      <c r="AX105" s="280"/>
+      <c r="AY105" s="280"/>
+      <c r="AZ105" s="280"/>
+      <c r="BA105" s="280"/>
+      <c r="BB105" s="280"/>
+      <c r="BC105" s="280"/>
+      <c r="BD105" s="281"/>
     </row>
     <row r="106" spans="3:56" s="106" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="105" t="s">
         <v>96</v>
       </c>
       <c r="G106" s="105"/>
-      <c r="AB106" s="114" t="s">
+      <c r="AB106" s="282" t="s">
         <v>97</v>
       </c>
-      <c r="AC106" s="114"/>
-      <c r="AD106" s="114"/>
-      <c r="AE106" s="114"/>
-      <c r="AF106" s="114"/>
-      <c r="AG106" s="114"/>
+      <c r="AC106" s="282"/>
+      <c r="AD106" s="282"/>
+      <c r="AE106" s="282"/>
+      <c r="AF106" s="282"/>
+      <c r="AG106" s="282"/>
       <c r="AH106" s="107"/>
     </row>
     <row r="107" spans="3:56" ht="13.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="231">
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="C7:BD7"/>
-    <mergeCell ref="G9:BB9"/>
-    <mergeCell ref="I13:Y13"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="AL13:AQ13"/>
-    <mergeCell ref="AV13:BB13"/>
-    <mergeCell ref="N2:AU3"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="O4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AN4:BD4"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="V15:AE15"/>
-    <mergeCell ref="AL15:BB15"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="AB17:AC17"/>
-    <mergeCell ref="AL17:AP17"/>
-    <mergeCell ref="AX17:BB17"/>
-    <mergeCell ref="I23:P23"/>
-    <mergeCell ref="AC23:AL23"/>
-    <mergeCell ref="AN23:AV23"/>
-    <mergeCell ref="AW23:BB23"/>
-    <mergeCell ref="K25:U25"/>
-    <mergeCell ref="AG25:BB25"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="X19:AG19"/>
-    <mergeCell ref="AH19:AN19"/>
-    <mergeCell ref="I21:T21"/>
-    <mergeCell ref="Z21:AL21"/>
-    <mergeCell ref="AS21:BB21"/>
-    <mergeCell ref="C28:BD31"/>
-    <mergeCell ref="C55:BD57"/>
-    <mergeCell ref="C58:BD58"/>
-    <mergeCell ref="C59:BD59"/>
-    <mergeCell ref="D61:F62"/>
-    <mergeCell ref="H61:J62"/>
-    <mergeCell ref="N61:P62"/>
-    <mergeCell ref="R61:T62"/>
-    <mergeCell ref="W61:AH62"/>
-    <mergeCell ref="AJ61:AK62"/>
-    <mergeCell ref="AL61:AM62"/>
-    <mergeCell ref="AO61:AP62"/>
-    <mergeCell ref="AQ61:AR62"/>
-    <mergeCell ref="AT61:BC61"/>
-    <mergeCell ref="C64:BD64"/>
-    <mergeCell ref="AJ65:BC66"/>
-    <mergeCell ref="D66:F67"/>
-    <mergeCell ref="H66:J67"/>
-    <mergeCell ref="N66:P67"/>
-    <mergeCell ref="R66:T67"/>
-    <mergeCell ref="W66:AH67"/>
-    <mergeCell ref="AJ67:BC67"/>
-    <mergeCell ref="Z69:BD69"/>
-    <mergeCell ref="D71:F72"/>
-    <mergeCell ref="H71:J72"/>
-    <mergeCell ref="N71:P72"/>
-    <mergeCell ref="R71:T72"/>
-    <mergeCell ref="AI71:AK72"/>
-    <mergeCell ref="AM71:AO72"/>
-    <mergeCell ref="AS71:AU72"/>
-    <mergeCell ref="AW71:AY72"/>
-    <mergeCell ref="AA74:BD74"/>
-    <mergeCell ref="D76:F77"/>
-    <mergeCell ref="N76:P77"/>
-    <mergeCell ref="R76:T77"/>
-    <mergeCell ref="AB76:AH77"/>
-    <mergeCell ref="AI76:AO77"/>
-    <mergeCell ref="AP76:AV77"/>
-    <mergeCell ref="AW76:AY77"/>
-    <mergeCell ref="BA76:BC77"/>
-    <mergeCell ref="AI81:AK82"/>
-    <mergeCell ref="AN81:AP82"/>
-    <mergeCell ref="AR81:AT82"/>
-    <mergeCell ref="AW81:AY82"/>
-    <mergeCell ref="BA81:BC82"/>
-    <mergeCell ref="C84:AK85"/>
-    <mergeCell ref="AL84:BD85"/>
-    <mergeCell ref="H77:M77"/>
-    <mergeCell ref="V79:AK79"/>
-    <mergeCell ref="AN79:BC79"/>
-    <mergeCell ref="D81:F82"/>
-    <mergeCell ref="H81:J82"/>
-    <mergeCell ref="L81:P82"/>
-    <mergeCell ref="R81:T82"/>
-    <mergeCell ref="V81:Y82"/>
-    <mergeCell ref="Z81:AB82"/>
-    <mergeCell ref="AD81:AH82"/>
-    <mergeCell ref="C87:M87"/>
-    <mergeCell ref="N87:S87"/>
-    <mergeCell ref="T87:W87"/>
-    <mergeCell ref="X87:AB87"/>
-    <mergeCell ref="AC87:AF87"/>
-    <mergeCell ref="C86:M86"/>
-    <mergeCell ref="N86:S86"/>
-    <mergeCell ref="T86:W86"/>
-    <mergeCell ref="X86:AB86"/>
-    <mergeCell ref="AC86:AF86"/>
-    <mergeCell ref="AG87:AK87"/>
-    <mergeCell ref="AL87:AO87"/>
-    <mergeCell ref="AP87:AU87"/>
-    <mergeCell ref="AV87:AW87"/>
-    <mergeCell ref="AX87:AY87"/>
-    <mergeCell ref="AZ87:BD87"/>
-    <mergeCell ref="AL86:AO86"/>
-    <mergeCell ref="AP86:AU86"/>
-    <mergeCell ref="AV86:AW86"/>
-    <mergeCell ref="AX86:AY86"/>
-    <mergeCell ref="AZ86:BD86"/>
-    <mergeCell ref="AG86:AK86"/>
-    <mergeCell ref="AL88:AO88"/>
-    <mergeCell ref="AP88:AU88"/>
-    <mergeCell ref="C89:M89"/>
-    <mergeCell ref="N89:S89"/>
-    <mergeCell ref="T89:W89"/>
-    <mergeCell ref="X89:AB89"/>
-    <mergeCell ref="AC89:AF89"/>
-    <mergeCell ref="AG89:AK89"/>
-    <mergeCell ref="AL89:AO89"/>
-    <mergeCell ref="AP89:AU89"/>
-    <mergeCell ref="C88:M88"/>
-    <mergeCell ref="N88:S88"/>
-    <mergeCell ref="T88:W88"/>
-    <mergeCell ref="X88:AB88"/>
-    <mergeCell ref="AC88:AF88"/>
-    <mergeCell ref="AG88:AK88"/>
-    <mergeCell ref="C91:M91"/>
-    <mergeCell ref="N91:S91"/>
-    <mergeCell ref="T91:W91"/>
-    <mergeCell ref="X91:AB91"/>
-    <mergeCell ref="AC91:AF91"/>
-    <mergeCell ref="C90:M90"/>
-    <mergeCell ref="N90:S90"/>
-    <mergeCell ref="T90:W90"/>
-    <mergeCell ref="X90:AB90"/>
-    <mergeCell ref="AC90:AF90"/>
-    <mergeCell ref="AG91:AK91"/>
-    <mergeCell ref="AL91:AO91"/>
-    <mergeCell ref="AP91:AU91"/>
-    <mergeCell ref="AV91:AW91"/>
-    <mergeCell ref="AX91:AY91"/>
-    <mergeCell ref="AZ91:BD91"/>
-    <mergeCell ref="AL90:AO90"/>
-    <mergeCell ref="AP90:AU90"/>
-    <mergeCell ref="AV90:AW90"/>
-    <mergeCell ref="AX90:AY90"/>
-    <mergeCell ref="AZ90:BD90"/>
-    <mergeCell ref="AG90:AK90"/>
-    <mergeCell ref="C93:M93"/>
-    <mergeCell ref="N93:S93"/>
-    <mergeCell ref="T93:W93"/>
-    <mergeCell ref="X93:AB93"/>
-    <mergeCell ref="AC93:AF93"/>
-    <mergeCell ref="C92:M92"/>
-    <mergeCell ref="N92:S92"/>
-    <mergeCell ref="T92:W92"/>
-    <mergeCell ref="X92:AB92"/>
-    <mergeCell ref="AC92:AF92"/>
-    <mergeCell ref="AG93:AK93"/>
-    <mergeCell ref="AL93:AO93"/>
-    <mergeCell ref="AP93:AU93"/>
-    <mergeCell ref="AV93:AW93"/>
-    <mergeCell ref="AX93:AY93"/>
-    <mergeCell ref="AZ93:BD93"/>
-    <mergeCell ref="AL92:AO92"/>
-    <mergeCell ref="AP92:AU92"/>
-    <mergeCell ref="AV92:AW92"/>
-    <mergeCell ref="AX92:AY92"/>
-    <mergeCell ref="AZ92:BD92"/>
-    <mergeCell ref="AG92:AK92"/>
-    <mergeCell ref="C97:P97"/>
-    <mergeCell ref="Q97:AA97"/>
-    <mergeCell ref="AB97:BD97"/>
-    <mergeCell ref="D98:AX98"/>
-    <mergeCell ref="C99:U99"/>
-    <mergeCell ref="V99:AM99"/>
-    <mergeCell ref="AN99:BD99"/>
-    <mergeCell ref="C94:AA94"/>
-    <mergeCell ref="AB94:BD94"/>
-    <mergeCell ref="C95:P95"/>
-    <mergeCell ref="Q95:AA95"/>
-    <mergeCell ref="AB95:BD95"/>
-    <mergeCell ref="C96:P96"/>
-    <mergeCell ref="Q96:AA96"/>
-    <mergeCell ref="AB96:BD96"/>
+  <mergeCells count="232">
+    <mergeCell ref="C105:BD105"/>
+    <mergeCell ref="AB106:AG106"/>
+    <mergeCell ref="BA102:BD102"/>
+    <mergeCell ref="C103:K103"/>
+    <mergeCell ref="L103:R103"/>
+    <mergeCell ref="S103:U103"/>
+    <mergeCell ref="V103:AC103"/>
+    <mergeCell ref="AD103:AH103"/>
+    <mergeCell ref="AI103:AM103"/>
+    <mergeCell ref="AN103:AU103"/>
+    <mergeCell ref="AV103:AZ103"/>
+    <mergeCell ref="BA103:BD103"/>
+    <mergeCell ref="C102:K102"/>
+    <mergeCell ref="L102:R102"/>
+    <mergeCell ref="S102:U102"/>
+    <mergeCell ref="V102:AC102"/>
+    <mergeCell ref="AD102:AH102"/>
+    <mergeCell ref="AI102:AM102"/>
+    <mergeCell ref="AN102:AU102"/>
+    <mergeCell ref="AV102:AZ102"/>
+    <mergeCell ref="C104:BD104"/>
     <mergeCell ref="AN100:AU100"/>
     <mergeCell ref="AV100:AZ100"/>
     <mergeCell ref="BA100:BD100"/>
@@ -9432,27 +9881,199 @@
     <mergeCell ref="AI100:AM100"/>
     <mergeCell ref="AV101:AZ101"/>
     <mergeCell ref="BA101:BD101"/>
-    <mergeCell ref="C102:K102"/>
-    <mergeCell ref="L102:R102"/>
-    <mergeCell ref="S102:U102"/>
-    <mergeCell ref="V102:AC102"/>
-    <mergeCell ref="AD102:AH102"/>
-    <mergeCell ref="AI102:AM102"/>
-    <mergeCell ref="AN102:AU102"/>
-    <mergeCell ref="AV102:AZ102"/>
-    <mergeCell ref="C104:BD104"/>
-    <mergeCell ref="C105:BD105"/>
-    <mergeCell ref="AB106:AG106"/>
-    <mergeCell ref="BA102:BD102"/>
-    <mergeCell ref="C103:K103"/>
-    <mergeCell ref="L103:R103"/>
-    <mergeCell ref="S103:U103"/>
-    <mergeCell ref="V103:AC103"/>
-    <mergeCell ref="AD103:AH103"/>
-    <mergeCell ref="AI103:AM103"/>
-    <mergeCell ref="AN103:AU103"/>
-    <mergeCell ref="AV103:AZ103"/>
-    <mergeCell ref="BA103:BD103"/>
+    <mergeCell ref="C97:P97"/>
+    <mergeCell ref="Q97:AA97"/>
+    <mergeCell ref="AB97:BD97"/>
+    <mergeCell ref="D98:AX98"/>
+    <mergeCell ref="C99:U99"/>
+    <mergeCell ref="V99:AM99"/>
+    <mergeCell ref="AN99:BD99"/>
+    <mergeCell ref="C94:AA94"/>
+    <mergeCell ref="AB94:BD94"/>
+    <mergeCell ref="C95:P95"/>
+    <mergeCell ref="Q95:AA95"/>
+    <mergeCell ref="AB95:BD95"/>
+    <mergeCell ref="C96:P96"/>
+    <mergeCell ref="Q96:AA96"/>
+    <mergeCell ref="AB96:BD96"/>
+    <mergeCell ref="AG93:AK93"/>
+    <mergeCell ref="AL93:AO93"/>
+    <mergeCell ref="AP93:AU93"/>
+    <mergeCell ref="AV93:AW93"/>
+    <mergeCell ref="AX93:AY93"/>
+    <mergeCell ref="AZ93:BD93"/>
+    <mergeCell ref="AL92:AO92"/>
+    <mergeCell ref="AP92:AU92"/>
+    <mergeCell ref="AV92:AW92"/>
+    <mergeCell ref="AX92:AY92"/>
+    <mergeCell ref="AZ92:BD92"/>
+    <mergeCell ref="AG92:AK92"/>
+    <mergeCell ref="C93:M93"/>
+    <mergeCell ref="N93:S93"/>
+    <mergeCell ref="T93:W93"/>
+    <mergeCell ref="X93:AB93"/>
+    <mergeCell ref="AC93:AF93"/>
+    <mergeCell ref="C92:M92"/>
+    <mergeCell ref="N92:S92"/>
+    <mergeCell ref="T92:W92"/>
+    <mergeCell ref="X92:AB92"/>
+    <mergeCell ref="AC92:AF92"/>
+    <mergeCell ref="AG91:AK91"/>
+    <mergeCell ref="AL91:AO91"/>
+    <mergeCell ref="AP91:AU91"/>
+    <mergeCell ref="AV91:AW91"/>
+    <mergeCell ref="AX91:AY91"/>
+    <mergeCell ref="AZ91:BD91"/>
+    <mergeCell ref="AL90:AO90"/>
+    <mergeCell ref="AP90:AU90"/>
+    <mergeCell ref="AV90:AW90"/>
+    <mergeCell ref="AX90:AY90"/>
+    <mergeCell ref="AZ90:BD90"/>
+    <mergeCell ref="AG90:AK90"/>
+    <mergeCell ref="C91:M91"/>
+    <mergeCell ref="N91:S91"/>
+    <mergeCell ref="T91:W91"/>
+    <mergeCell ref="X91:AB91"/>
+    <mergeCell ref="AC91:AF91"/>
+    <mergeCell ref="C90:M90"/>
+    <mergeCell ref="N90:S90"/>
+    <mergeCell ref="T90:W90"/>
+    <mergeCell ref="X90:AB90"/>
+    <mergeCell ref="AC90:AF90"/>
+    <mergeCell ref="AL88:AO88"/>
+    <mergeCell ref="AP88:AU88"/>
+    <mergeCell ref="C89:M89"/>
+    <mergeCell ref="N89:S89"/>
+    <mergeCell ref="T89:W89"/>
+    <mergeCell ref="X89:AB89"/>
+    <mergeCell ref="AC89:AF89"/>
+    <mergeCell ref="AG89:AK89"/>
+    <mergeCell ref="AL89:AO89"/>
+    <mergeCell ref="AP89:AU89"/>
+    <mergeCell ref="C88:M88"/>
+    <mergeCell ref="N88:S88"/>
+    <mergeCell ref="T88:W88"/>
+    <mergeCell ref="X88:AB88"/>
+    <mergeCell ref="AC88:AF88"/>
+    <mergeCell ref="AG88:AK88"/>
+    <mergeCell ref="AG87:AK87"/>
+    <mergeCell ref="AL87:AO87"/>
+    <mergeCell ref="AP87:AU87"/>
+    <mergeCell ref="AV87:AW87"/>
+    <mergeCell ref="AX87:AY87"/>
+    <mergeCell ref="AZ87:BD87"/>
+    <mergeCell ref="AL86:AO86"/>
+    <mergeCell ref="AP86:AU86"/>
+    <mergeCell ref="AV86:AW86"/>
+    <mergeCell ref="AX86:AY86"/>
+    <mergeCell ref="AZ86:BD86"/>
+    <mergeCell ref="AG86:AK86"/>
+    <mergeCell ref="C87:M87"/>
+    <mergeCell ref="N87:S87"/>
+    <mergeCell ref="T87:W87"/>
+    <mergeCell ref="X87:AB87"/>
+    <mergeCell ref="AC87:AF87"/>
+    <mergeCell ref="C86:M86"/>
+    <mergeCell ref="N86:S86"/>
+    <mergeCell ref="T86:W86"/>
+    <mergeCell ref="X86:AB86"/>
+    <mergeCell ref="AC86:AF86"/>
+    <mergeCell ref="C84:AK85"/>
+    <mergeCell ref="AL84:BD85"/>
+    <mergeCell ref="H77:M77"/>
+    <mergeCell ref="V79:AK79"/>
+    <mergeCell ref="AN79:BC79"/>
+    <mergeCell ref="D81:F82"/>
+    <mergeCell ref="H81:J82"/>
+    <mergeCell ref="L81:P82"/>
+    <mergeCell ref="R81:T82"/>
+    <mergeCell ref="V81:Y82"/>
+    <mergeCell ref="Z81:AB82"/>
+    <mergeCell ref="AD81:AH82"/>
+    <mergeCell ref="D76:F77"/>
+    <mergeCell ref="N76:P77"/>
+    <mergeCell ref="R76:T77"/>
+    <mergeCell ref="AB76:AH77"/>
+    <mergeCell ref="AI76:AO77"/>
+    <mergeCell ref="AP76:AV77"/>
+    <mergeCell ref="AW76:AY77"/>
+    <mergeCell ref="BA76:BC77"/>
+    <mergeCell ref="AI81:AK82"/>
+    <mergeCell ref="AN81:AP82"/>
+    <mergeCell ref="AR81:AT82"/>
+    <mergeCell ref="AW81:AY82"/>
+    <mergeCell ref="BA81:BC82"/>
+    <mergeCell ref="D71:F72"/>
+    <mergeCell ref="H71:J72"/>
+    <mergeCell ref="N71:P72"/>
+    <mergeCell ref="R71:T72"/>
+    <mergeCell ref="AI71:AK72"/>
+    <mergeCell ref="AM71:AO72"/>
+    <mergeCell ref="AS71:AU72"/>
+    <mergeCell ref="AW71:AY72"/>
+    <mergeCell ref="AA74:BD74"/>
+    <mergeCell ref="C64:BD64"/>
+    <mergeCell ref="AJ65:BC66"/>
+    <mergeCell ref="D66:F67"/>
+    <mergeCell ref="H66:J67"/>
+    <mergeCell ref="N66:P67"/>
+    <mergeCell ref="R66:T67"/>
+    <mergeCell ref="W66:AH67"/>
+    <mergeCell ref="AJ67:BC67"/>
+    <mergeCell ref="Z69:BD69"/>
+    <mergeCell ref="C28:BD31"/>
+    <mergeCell ref="C55:BD57"/>
+    <mergeCell ref="C58:BD58"/>
+    <mergeCell ref="C59:BD59"/>
+    <mergeCell ref="D61:F62"/>
+    <mergeCell ref="H61:J62"/>
+    <mergeCell ref="N61:P62"/>
+    <mergeCell ref="R61:T62"/>
+    <mergeCell ref="W61:AH62"/>
+    <mergeCell ref="AJ61:AK62"/>
+    <mergeCell ref="AL61:AM62"/>
+    <mergeCell ref="AO61:AP62"/>
+    <mergeCell ref="AQ61:AR62"/>
+    <mergeCell ref="AT61:BC61"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="I23:P23"/>
+    <mergeCell ref="AC23:AL23"/>
+    <mergeCell ref="AN23:AV23"/>
+    <mergeCell ref="AW23:BB23"/>
+    <mergeCell ref="K25:U25"/>
+    <mergeCell ref="AG25:BB25"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="X19:AG19"/>
+    <mergeCell ref="AH19:AN19"/>
+    <mergeCell ref="I21:T21"/>
+    <mergeCell ref="Z21:AL21"/>
+    <mergeCell ref="AS21:BB21"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="V15:AE15"/>
+    <mergeCell ref="AL15:BB15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="AB17:AC17"/>
+    <mergeCell ref="AL17:AP17"/>
+    <mergeCell ref="AX17:BB17"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="C7:BD7"/>
+    <mergeCell ref="G9:BB9"/>
+    <mergeCell ref="I13:Y13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="AL13:AQ13"/>
+    <mergeCell ref="AV13:BB13"/>
+    <mergeCell ref="N2:AU3"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="O4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AN4:BD4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
